--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.8</v>
+        <v>45.36559904899498</v>
       </c>
       <c r="M2" t="n">
-        <v>107</v>
+        <v>100.2865764021453</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93956479877609</v>
+        <v>88.10656008326848</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84429988108484</v>
+        <v>45.93659827790729</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228569382094831</v>
+        <v>2.228927750783344</v>
       </c>
       <c r="E3" t="n">
-        <v>5.653526239907536</v>
+        <v>5.715311306176599</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742856460698277</v>
+        <v>0.7429759169277814</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94471585836577</v>
+        <v>33.97501780870142</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17139719212074</v>
+        <v>34.17689217867794</v>
       </c>
       <c r="I3" t="n">
-        <v>6.555646786224704</v>
+        <v>6.623835641202756</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642852879364232</v>
+        <v>4.643599480798634</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06043520122391</v>
+        <v>11.89343991673153</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8599337913141</v>
+        <v>48.93222110196243</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646688736229</v>
+        <v>106.7622592966013</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.91827676125622</v>
+        <v>87.34268085989952</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4588864016333</v>
+        <v>42.81833073160945</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178718859539558</v>
+        <v>2.192930429682955</v>
       </c>
       <c r="E4" t="n">
-        <v>6.439481481899138</v>
+        <v>6.544927955531278</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444160766970495</v>
+        <v>0.7445443684937322</v>
       </c>
       <c r="G4" t="n">
-        <v>33.18541177875071</v>
+        <v>33.42631916872917</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24313952806428</v>
+        <v>34.24904095071167</v>
       </c>
       <c r="I4" t="n">
-        <v>5.474508556948929</v>
+        <v>5.53151568366488</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652600479356559</v>
+        <v>4.653402303085826</v>
       </c>
       <c r="K4" t="n">
-        <v>13.08172323874378</v>
+        <v>12.6573191401005</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27728906000556</v>
+        <v>44.3403546938122</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81789870038264</v>
+        <v>99.81600456552215</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.72989675191164</v>
+        <v>86.46614298826572</v>
       </c>
       <c r="C5" t="n">
-        <v>42.11999659822925</v>
+        <v>42.80045011797903</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120544392192913</v>
+        <v>2.151164978061954</v>
       </c>
       <c r="E5" t="n">
-        <v>7.02923895459226</v>
+        <v>7.189910276639981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457388856539657</v>
+        <v>0.7458698039557672</v>
       </c>
       <c r="G5" t="n">
-        <v>32.29932055800648</v>
+        <v>32.7896982813481</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30398874008242</v>
+        <v>34.31001098196528</v>
       </c>
       <c r="I5" t="n">
-        <v>4.570197186046318</v>
+        <v>4.617802391571093</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660868035337287</v>
+        <v>4.661686274723545</v>
       </c>
       <c r="K5" t="n">
-        <v>14.27010324808834</v>
+        <v>13.53385701173429</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45783047154494</v>
+        <v>43.51203965685157</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84793031786255</v>
+        <v>99.84634678656488</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.34699965306788</v>
+        <v>85.29519428184342</v>
       </c>
       <c r="C6" t="n">
-        <v>41.44669530077495</v>
+        <v>42.34705607685727</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052884880662795</v>
+        <v>2.094527117232247</v>
       </c>
       <c r="E6" t="n">
-        <v>7.440665747566799</v>
+        <v>7.642935085737941</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468629825114828</v>
+        <v>0.7469931793760921</v>
       </c>
       <c r="G6" t="n">
-        <v>31.26875677459542</v>
+        <v>31.92638078276173</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35569719552821</v>
+        <v>34.36168625130023</v>
       </c>
       <c r="I6" t="n">
-        <v>3.814238431506404</v>
+        <v>3.853964494334611</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667893640696768</v>
+        <v>4.668707371100576</v>
       </c>
       <c r="K6" t="n">
-        <v>15.65300034693212</v>
+        <v>14.70480571815658</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77335443045831</v>
+        <v>42.8198659163314</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87305007816538</v>
+        <v>99.87172771134526</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.77129479754856</v>
+        <v>83.96418854972951</v>
       </c>
       <c r="C7" t="n">
-        <v>40.4632208675264</v>
+        <v>41.61510327942946</v>
       </c>
       <c r="D7" t="n">
-        <v>1.976058154139615</v>
+        <v>2.030203234970436</v>
       </c>
       <c r="E7" t="n">
-        <v>7.692642175495632</v>
+        <v>7.944173258353709</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478202268261381</v>
+        <v>0.7479468136023361</v>
       </c>
       <c r="G7" t="n">
-        <v>30.09856148109895</v>
+        <v>30.94590707983358</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39973043400236</v>
+        <v>34.40555342570745</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182605908322502</v>
+        <v>3.215737152247382</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673876417663364</v>
+        <v>4.674667585014601</v>
       </c>
       <c r="K7" t="n">
-        <v>17.22870520245144</v>
+        <v>16.03581145027049</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20212286248032</v>
+        <v>42.24203070101298</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89404893245816</v>
+        <v>99.89294543071293</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.54540365964834</v>
+        <v>88.73388733482771</v>
       </c>
       <c r="C8" t="n">
-        <v>42.71076763773277</v>
+        <v>43.82321215384395</v>
       </c>
       <c r="D8" t="n">
-        <v>1.980261814737073</v>
+        <v>2.034515567092449</v>
       </c>
       <c r="E8" t="n">
-        <v>9.486302662288079</v>
+        <v>9.714884587807047</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494110617997475</v>
+        <v>0.7495355191143246</v>
       </c>
       <c r="G8" t="n">
-        <v>30.58565054385283</v>
+        <v>31.4173608775917</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47290884278839</v>
+        <v>34.47863387925893</v>
       </c>
       <c r="I8" t="n">
-        <v>5.587049597933796</v>
+        <v>5.654359909498742</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683819136248423</v>
+        <v>4.684596994464529</v>
       </c>
       <c r="K8" t="n">
-        <v>12.45459634035166</v>
+        <v>11.26611266517227</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64879637126235</v>
+        <v>44.72259601420113</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81416034934678</v>
+        <v>99.81192083321736</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.48771030510295</v>
+        <v>87.01075020427717</v>
       </c>
       <c r="C9" t="n">
-        <v>41.51991183895647</v>
+        <v>42.97848718626312</v>
       </c>
       <c r="D9" t="n">
-        <v>1.886789217548855</v>
+        <v>1.956833810518817</v>
       </c>
       <c r="E9" t="n">
-        <v>9.815919265833458</v>
+        <v>10.13069936830193</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507740295568816</v>
+        <v>0.7508909735352486</v>
       </c>
       <c r="G9" t="n">
-        <v>29.1419423575165</v>
+        <v>30.21778500835082</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53560535961656</v>
+        <v>34.54098478262143</v>
       </c>
       <c r="I9" t="n">
-        <v>4.664342390300175</v>
+        <v>4.720487676353633</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692337684730511</v>
+        <v>4.693068584595304</v>
       </c>
       <c r="K9" t="n">
-        <v>14.51228969489706</v>
+        <v>12.98924979572283</v>
       </c>
       <c r="L9" t="n">
-        <v>43.81260264398165</v>
+        <v>43.87519746497241</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84480417783519</v>
+        <v>99.84293444695837</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.11898080848559</v>
+        <v>85.12674247223273</v>
       </c>
       <c r="C10" t="n">
-        <v>39.87452070582448</v>
+        <v>41.82782471704483</v>
       </c>
       <c r="D10" t="n">
-        <v>1.78014233380931</v>
+        <v>1.872573385561282</v>
       </c>
       <c r="E10" t="n">
-        <v>9.909931330516674</v>
+        <v>10.35111052990723</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519461559794984</v>
+        <v>0.7520493899852824</v>
       </c>
       <c r="G10" t="n">
-        <v>27.49475394365431</v>
+        <v>28.91662014069964</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58952317505694</v>
+        <v>34.59427193932299</v>
       </c>
       <c r="I10" t="n">
-        <v>3.893020394596988</v>
+        <v>3.9398083993483</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699663474871866</v>
+        <v>4.700308687408016</v>
       </c>
       <c r="K10" t="n">
-        <v>16.8810191915144</v>
+        <v>14.87325752776727</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11489503626388</v>
+        <v>43.16779309751143</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87043493360278</v>
+        <v>99.86887534232352</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.75678199528573</v>
+        <v>82.96060961716587</v>
       </c>
       <c r="C11" t="n">
-        <v>38.11527222778729</v>
+        <v>40.27341620210716</v>
       </c>
       <c r="D11" t="n">
-        <v>1.675072160358432</v>
+        <v>1.776321303423409</v>
       </c>
       <c r="E11" t="n">
-        <v>9.866435101745632</v>
+        <v>10.36697185116685</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529544190480512</v>
+        <v>0.7530427812023581</v>
       </c>
       <c r="G11" t="n">
-        <v>25.87191822373348</v>
+        <v>27.43027791326375</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63590327621036</v>
+        <v>34.63996793530847</v>
       </c>
       <c r="I11" t="n">
-        <v>3.248533695139458</v>
+        <v>3.28751045028629</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705965119050321</v>
+        <v>4.706517382514739</v>
       </c>
       <c r="K11" t="n">
-        <v>19.24321800471427</v>
+        <v>17.03939038283414</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53337031209296</v>
+        <v>42.57775429285459</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89186054459452</v>
+        <v>99.89056087779588</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.33112651684354</v>
+        <v>80.76139250572197</v>
       </c>
       <c r="C12" t="n">
-        <v>36.19190966187944</v>
+        <v>38.58399541126334</v>
       </c>
       <c r="D12" t="n">
-        <v>1.568277472574487</v>
+        <v>1.679505097203104</v>
       </c>
       <c r="E12" t="n">
-        <v>9.689103407319061</v>
+        <v>10.25904836103786</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538228189835149</v>
+        <v>0.7538952369478128</v>
       </c>
       <c r="G12" t="n">
-        <v>24.22244693857752</v>
+        <v>25.93522437874124</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67584967324169</v>
+        <v>34.67918089959939</v>
       </c>
       <c r="I12" t="n">
-        <v>2.710233587500295</v>
+        <v>2.742693301268747</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711392618646968</v>
+        <v>4.711845230923831</v>
       </c>
       <c r="K12" t="n">
-        <v>21.66887348315645</v>
+        <v>19.23860749427804</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0489798078769</v>
+        <v>42.08607735972845</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90976295291279</v>
+        <v>99.90868026526982</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.64900424799364</v>
+        <v>78.59656642953392</v>
       </c>
       <c r="C13" t="n">
-        <v>33.92794970020194</v>
+        <v>36.8437766229182</v>
       </c>
       <c r="D13" t="n">
-        <v>1.45116661580183</v>
+        <v>1.585042745952187</v>
       </c>
       <c r="E13" t="n">
-        <v>9.34236754948174</v>
+        <v>10.06333604629508</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545737545981148</v>
+        <v>0.7546267184515636</v>
       </c>
       <c r="G13" t="n">
-        <v>22.41363978313819</v>
+        <v>24.47651950245605</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71039271151329</v>
+        <v>34.71282904877192</v>
       </c>
       <c r="I13" t="n">
-        <v>2.260777867222248</v>
+        <v>2.287795377284842</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716085966238218</v>
+        <v>4.716416990322273</v>
       </c>
       <c r="K13" t="n">
-        <v>24.35099575200637</v>
+        <v>21.40343357046608</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64577028147224</v>
+        <v>41.6766038815805</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92471573368054</v>
+        <v>99.92381407496478</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.80199897140749</v>
+        <v>84.62108911008343</v>
       </c>
       <c r="C14" t="n">
-        <v>38.41336427606915</v>
+        <v>40.53600134612643</v>
       </c>
       <c r="D14" t="n">
-        <v>1.452851254440122</v>
+        <v>1.586903313818272</v>
       </c>
       <c r="E14" t="n">
-        <v>11.82191431714693</v>
+        <v>12.15385942868275</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554497285135804</v>
+        <v>0.7555125205706709</v>
       </c>
       <c r="G14" t="n">
-        <v>24.42774250298435</v>
+        <v>26.08730838436288</v>
       </c>
       <c r="H14" t="n">
-        <v>36.73877055654707</v>
+        <v>36.33563359944089</v>
       </c>
       <c r="I14" t="n">
-        <v>2.883709808565556</v>
+        <v>2.979918609641276</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721560803209877</v>
+        <v>4.721953253566694</v>
       </c>
       <c r="K14" t="n">
-        <v>17.19800102859252</v>
+        <v>15.37891088991656</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29262249424843</v>
+        <v>43.98587360401394</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90398779891009</v>
+        <v>99.90078584005694</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.85099960525768</v>
+        <v>83.96643028846054</v>
       </c>
       <c r="C15" t="n">
-        <v>37.90747368812485</v>
+        <v>40.34280241048407</v>
       </c>
       <c r="D15" t="n">
-        <v>1.417592188692855</v>
+        <v>1.562359392264641</v>
       </c>
       <c r="E15" t="n">
-        <v>11.93591735151151</v>
+        <v>12.38016713277459</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561897696541913</v>
+        <v>0.7562580524577954</v>
       </c>
       <c r="G15" t="n">
-        <v>23.8349086692813</v>
+        <v>25.6838276902615</v>
       </c>
       <c r="H15" t="n">
-        <v>36.77475998197291</v>
+        <v>36.37148922426468</v>
       </c>
       <c r="I15" t="n">
-        <v>2.405445583806221</v>
+        <v>2.48571596857612</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726186060338696</v>
+        <v>4.726612827861222</v>
       </c>
       <c r="K15" t="n">
-        <v>18.14900039474232</v>
+        <v>16.03356971153946</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86342286689491</v>
+        <v>43.54085236104198</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91989694976208</v>
+        <v>99.91722448306552</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.21404490660485</v>
+        <v>81.71675542417897</v>
       </c>
       <c r="C16" t="n">
-        <v>35.64174294490455</v>
+        <v>38.47817573244586</v>
       </c>
       <c r="D16" t="n">
-        <v>1.318185529282946</v>
+        <v>1.474907072285382</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4332996372013</v>
+        <v>12.03272348619216</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568281626744892</v>
+        <v>0.7568976032142536</v>
       </c>
       <c r="G16" t="n">
-        <v>22.16351920547629</v>
+        <v>24.2461877153738</v>
       </c>
       <c r="H16" t="n">
-        <v>36.80580609108168</v>
+        <v>36.40224779056528</v>
       </c>
       <c r="I16" t="n">
-        <v>2.00623026417259</v>
+        <v>2.073181736458997</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730176016715558</v>
+        <v>4.730610020089086</v>
       </c>
       <c r="K16" t="n">
-        <v>20.78595509339517</v>
+        <v>18.28324457582103</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50548402881679</v>
+        <v>43.16953202593933</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93318206711649</v>
+        <v>99.93095233420622</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.83759053754891</v>
+        <v>83.15090228801975</v>
       </c>
       <c r="C17" t="n">
-        <v>36.83094951045027</v>
+        <v>39.54510401730781</v>
       </c>
       <c r="D17" t="n">
-        <v>1.319268432250885</v>
+        <v>1.476125287253042</v>
       </c>
       <c r="E17" t="n">
-        <v>12.18874909140458</v>
+        <v>12.73198169229183</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574499047930101</v>
+        <v>0.7575227707292435</v>
       </c>
       <c r="G17" t="n">
-        <v>22.59573908577771</v>
+        <v>24.61213696051235</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25005476063438</v>
+        <v>36.77823746103613</v>
       </c>
       <c r="I17" t="n">
-        <v>1.992267357732019</v>
+        <v>2.060380799139373</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734061904956314</v>
+        <v>4.734517317057773</v>
       </c>
       <c r="K17" t="n">
-        <v>19.16240946245109</v>
+        <v>16.84909771198025</v>
       </c>
       <c r="L17" t="n">
-        <v>43.94028662599712</v>
+        <v>43.5371755903633</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93364559889848</v>
+        <v>99.93137731965136</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.33359393048221</v>
+        <v>80.96361749034307</v>
       </c>
       <c r="C18" t="n">
-        <v>34.6339137068445</v>
+        <v>37.67664591299025</v>
       </c>
       <c r="D18" t="n">
-        <v>1.228637821017916</v>
+        <v>1.393939968764482</v>
       </c>
       <c r="E18" t="n">
-        <v>11.62831036986576</v>
+        <v>12.309477420064</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579854028610894</v>
+        <v>0.7580586388116008</v>
       </c>
       <c r="G18" t="n">
-        <v>21.04346542065958</v>
+        <v>23.24182216931466</v>
       </c>
       <c r="H18" t="n">
-        <v>37.27638961424509</v>
+        <v>36.80425421504309</v>
       </c>
       <c r="I18" t="n">
-        <v>1.661396533950952</v>
+        <v>1.71819858577273</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73740876788181</v>
+        <v>4.737866492572507</v>
       </c>
       <c r="K18" t="n">
-        <v>21.66640606951779</v>
+        <v>19.03638250965693</v>
       </c>
       <c r="L18" t="n">
-        <v>43.64433946370071</v>
+        <v>43.22973877737672</v>
       </c>
       <c r="M18" t="n">
-        <v>99.944659240063</v>
+        <v>99.94276720002389</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.32496597409313</v>
+        <v>80.05196657217947</v>
       </c>
       <c r="C19" t="n">
-        <v>33.87315719613002</v>
+        <v>37.03028597125959</v>
       </c>
       <c r="D19" t="n">
-        <v>1.192488025864411</v>
+        <v>1.360354532564949</v>
       </c>
       <c r="E19" t="n">
-        <v>11.51825090967247</v>
+        <v>12.25167528179433</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584403930678116</v>
+        <v>0.7585108701558836</v>
       </c>
       <c r="G19" t="n">
-        <v>20.42431065327137</v>
+        <v>22.6818362638095</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29876523276285</v>
+        <v>36.82621034944594</v>
       </c>
       <c r="I19" t="n">
-        <v>1.392458302780393</v>
+        <v>1.432686335934607</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740252456673824</v>
+        <v>4.740692938474274</v>
       </c>
       <c r="K19" t="n">
-        <v>22.67503402590688</v>
+        <v>19.94803342782052</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40542134583935</v>
+        <v>42.9739528624262</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95361256787625</v>
+        <v>99.95227226150632</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.62734908479486</v>
+        <v>77.70668911645836</v>
       </c>
       <c r="C20" t="n">
-        <v>31.38927007907508</v>
+        <v>34.90608370592779</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09597228969887</v>
+        <v>1.273101637013193</v>
       </c>
       <c r="E20" t="n">
-        <v>10.77950195637531</v>
+        <v>11.66494120191864</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588336970027703</v>
+        <v>0.7588995343199235</v>
       </c>
       <c r="G20" t="n">
-        <v>18.7712396491032</v>
+        <v>21.22702735696028</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31810722887649</v>
+        <v>36.84508025470819</v>
       </c>
       <c r="I20" t="n">
-        <v>1.160983657470907</v>
+        <v>1.194517042038616</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742710606267315</v>
+        <v>4.743122089499524</v>
       </c>
       <c r="K20" t="n">
-        <v>25.37265091520514</v>
+        <v>22.29331088354164</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19939960842033</v>
+        <v>42.76080856786572</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96132060270055</v>
+        <v>99.96020315733514</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.79028011568126</v>
+        <v>82.87532570743767</v>
       </c>
       <c r="C21" t="n">
-        <v>35.26608175851025</v>
+        <v>38.03199602998055</v>
       </c>
       <c r="D21" t="n">
-        <v>1.096702518835455</v>
+        <v>1.274019207281624</v>
       </c>
       <c r="E21" t="n">
-        <v>12.85281059850934</v>
+        <v>13.37780982001719</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593392959860497</v>
+        <v>0.7594465005865381</v>
       </c>
       <c r="G21" t="n">
-        <v>20.58072658199398</v>
+        <v>22.64813153338415</v>
       </c>
       <c r="H21" t="n">
-        <v>39.13995164856362</v>
+        <v>38.27744092517236</v>
       </c>
       <c r="I21" t="n">
-        <v>1.614878871879999</v>
+        <v>1.791937092329934</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745870599912812</v>
+        <v>4.746540628665865</v>
       </c>
       <c r="K21" t="n">
-        <v>19.20971988431874</v>
+        <v>17.12467429256233</v>
       </c>
       <c r="L21" t="n">
-        <v>45.47040490317584</v>
+        <v>44.78364146049694</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94620654600483</v>
+        <v>99.94031178303982</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.36559904899498</v>
+        <v>45.64793290219151</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2865764021453</v>
+        <v>99.70491021209955</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10656008326848</v>
+        <v>87.96339181555815</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93659827790729</v>
+        <v>45.91916121149524</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228927750783344</v>
+        <v>2.228573772030776</v>
       </c>
       <c r="E3" t="n">
-        <v>5.715311306176599</v>
+        <v>5.69733235488383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429759169277814</v>
+        <v>0.7428579240102587</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97501780870142</v>
+        <v>33.97050191140482</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17689217867794</v>
+        <v>34.1714645044719</v>
       </c>
       <c r="I3" t="n">
-        <v>6.623835641202756</v>
+        <v>6.509799323692453</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643599480798634</v>
+        <v>4.642862025064117</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89343991673153</v>
+        <v>12.03660818444184</v>
       </c>
       <c r="L3" t="n">
-        <v>48.93222110196243</v>
+        <v>48.81054574586734</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7622592966013</v>
+        <v>106.7663151418044</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.34268085989952</v>
+        <v>86.94500347674385</v>
       </c>
       <c r="C4" t="n">
-        <v>42.81833073160945</v>
+        <v>42.52501641847267</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192930429682955</v>
+        <v>2.178934909816361</v>
       </c>
       <c r="E4" t="n">
-        <v>6.544927955531278</v>
+        <v>6.476454108094079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445443684937322</v>
+        <v>0.7444061359599095</v>
       </c>
       <c r="G4" t="n">
-        <v>33.42631916872917</v>
+        <v>33.2138488964148</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24904095071167</v>
+        <v>34.24268225415583</v>
       </c>
       <c r="I4" t="n">
-        <v>5.53151568366488</v>
+        <v>5.436138822553424</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653402303085826</v>
+        <v>4.652538349749434</v>
       </c>
       <c r="K4" t="n">
-        <v>12.6573191401005</v>
+        <v>13.05499652325615</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3403546938122</v>
+        <v>44.23915929927973</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81600456552215</v>
+        <v>99.81917224100854</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.46614298826572</v>
+        <v>85.57283949617714</v>
       </c>
       <c r="C5" t="n">
-        <v>42.80045011797903</v>
+        <v>41.99649935062866</v>
       </c>
       <c r="D5" t="n">
-        <v>2.151164978061954</v>
+        <v>2.111251101109302</v>
       </c>
       <c r="E5" t="n">
-        <v>7.189910276639981</v>
+        <v>7.03163130195593</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458698039557672</v>
+        <v>0.7457220547323561</v>
       </c>
       <c r="G5" t="n">
-        <v>32.7896982813481</v>
+        <v>32.18213391263882</v>
       </c>
       <c r="H5" t="n">
-        <v>34.31001098196528</v>
+        <v>34.30321451768837</v>
       </c>
       <c r="I5" t="n">
-        <v>4.617802391571093</v>
+        <v>4.538123765975148</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661686274723545</v>
+        <v>4.660762842077225</v>
       </c>
       <c r="K5" t="n">
-        <v>13.53385701173429</v>
+        <v>14.42716050382283</v>
       </c>
       <c r="L5" t="n">
-        <v>43.51203965685157</v>
+        <v>43.42533628936646</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84634678656488</v>
+        <v>99.84899614381796</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.29519428184342</v>
+        <v>83.99534372746164</v>
       </c>
       <c r="C6" t="n">
-        <v>42.34705607685727</v>
+        <v>41.12353756921743</v>
       </c>
       <c r="D6" t="n">
-        <v>2.094527117232247</v>
+        <v>2.033710684720036</v>
       </c>
       <c r="E6" t="n">
-        <v>7.642935085737941</v>
+        <v>7.40462125000689</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469931793760921</v>
+        <v>0.7468429057321947</v>
       </c>
       <c r="G6" t="n">
-        <v>31.92638078276173</v>
+        <v>31.00017310154915</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36168625130023</v>
+        <v>34.35477366368095</v>
       </c>
       <c r="I6" t="n">
-        <v>3.853964494334611</v>
+        <v>3.78745396094621</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668707371100576</v>
+        <v>4.667768160826216</v>
       </c>
       <c r="K6" t="n">
-        <v>14.70480571815658</v>
+        <v>16.00465627253836</v>
       </c>
       <c r="L6" t="n">
-        <v>42.8198659163314</v>
+        <v>42.74574716474489</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87172771134526</v>
+        <v>99.87394100650067</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.96418854972951</v>
+        <v>82.25455040935788</v>
       </c>
       <c r="C7" t="n">
-        <v>41.61510327942946</v>
+        <v>39.97058989625815</v>
       </c>
       <c r="D7" t="n">
-        <v>2.030203234970436</v>
+        <v>1.948656094197766</v>
       </c>
       <c r="E7" t="n">
-        <v>7.944173258353709</v>
+        <v>7.621651432962746</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479468136023361</v>
+        <v>0.7477993728085656</v>
       </c>
       <c r="G7" t="n">
-        <v>30.94590707983358</v>
+        <v>29.7036725476197</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40555342570745</v>
+        <v>34.39877114919401</v>
       </c>
       <c r="I7" t="n">
-        <v>3.215737152247382</v>
+        <v>3.160253732521554</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674667585014601</v>
+        <v>4.673746080053534</v>
       </c>
       <c r="K7" t="n">
-        <v>16.03581145027049</v>
+        <v>17.74544959064212</v>
       </c>
       <c r="L7" t="n">
-        <v>42.24203070101298</v>
+        <v>42.178753458629</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89294543071293</v>
+        <v>99.89479294552928</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.73388733482771</v>
+        <v>87.26173183440972</v>
       </c>
       <c r="C8" t="n">
-        <v>43.82321215384395</v>
+        <v>42.31012094337629</v>
       </c>
       <c r="D8" t="n">
-        <v>2.034515567092449</v>
+        <v>1.952900383197781</v>
       </c>
       <c r="E8" t="n">
-        <v>9.714884587807047</v>
+        <v>9.483904349590601</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495355191143246</v>
+        <v>0.7494281243680018</v>
       </c>
       <c r="G8" t="n">
-        <v>31.4173608775917</v>
+        <v>30.21604204886317</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47863387925893</v>
+        <v>34.47369372092808</v>
       </c>
       <c r="I8" t="n">
-        <v>5.654359909498742</v>
+        <v>5.701837430162068</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684596994464529</v>
+        <v>4.68392577730001</v>
       </c>
       <c r="K8" t="n">
-        <v>11.26611266517227</v>
+        <v>12.7382681655903</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72259601420113</v>
+        <v>44.76196270839515</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81192083321736</v>
+        <v>99.81035181736173</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.01075020427717</v>
+        <v>85.15787355149348</v>
       </c>
       <c r="C9" t="n">
-        <v>42.97848718626312</v>
+        <v>41.09033848840365</v>
       </c>
       <c r="D9" t="n">
-        <v>1.956833810518817</v>
+        <v>1.857715800243703</v>
       </c>
       <c r="E9" t="n">
-        <v>10.13069936830193</v>
+        <v>9.815055289833253</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508909735352486</v>
+        <v>0.7508245763323471</v>
       </c>
       <c r="G9" t="n">
-        <v>30.21778500835082</v>
+        <v>28.74330878213379</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54098478262143</v>
+        <v>34.53793051128796</v>
       </c>
       <c r="I9" t="n">
-        <v>4.720487676353633</v>
+        <v>4.760384989585247</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693068584595304</v>
+        <v>4.692653602077169</v>
       </c>
       <c r="K9" t="n">
-        <v>12.98924979572283</v>
+        <v>14.8421264485065</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87519746497241</v>
+        <v>43.90915069002981</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84293444695837</v>
+        <v>99.84161562693997</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.12674247223273</v>
+        <v>82.79156029237164</v>
       </c>
       <c r="C10" t="n">
-        <v>41.82782471704483</v>
+        <v>39.4617557713081</v>
       </c>
       <c r="D10" t="n">
-        <v>1.872573385561282</v>
+        <v>1.751746608806791</v>
       </c>
       <c r="E10" t="n">
-        <v>10.35111052990723</v>
+        <v>9.917399954041949</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520493899852824</v>
+        <v>0.7520256957530826</v>
       </c>
       <c r="G10" t="n">
-        <v>28.91662014069964</v>
+        <v>27.1037118155447</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59427193932299</v>
+        <v>34.5931820046418</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9398083993483</v>
+        <v>3.97333361512657</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700308687408016</v>
+        <v>4.700160598456765</v>
       </c>
       <c r="K10" t="n">
-        <v>14.87325752776727</v>
+        <v>17.20843970762834</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16779309751143</v>
+        <v>43.19757160468617</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86887534232352</v>
+        <v>99.86776708362262</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.96060961716587</v>
+        <v>80.35355239328821</v>
       </c>
       <c r="C11" t="n">
-        <v>40.27341620210716</v>
+        <v>37.63872806605289</v>
       </c>
       <c r="D11" t="n">
-        <v>1.776321303423409</v>
+        <v>1.643856045887973</v>
       </c>
       <c r="E11" t="n">
-        <v>10.36697185116685</v>
+        <v>9.859195455772655</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530427812023581</v>
+        <v>0.7530600684981621</v>
       </c>
       <c r="G11" t="n">
-        <v>27.43027791326375</v>
+        <v>25.43438663445565</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63996793530847</v>
+        <v>34.64076315091545</v>
       </c>
       <c r="I11" t="n">
-        <v>3.28751045028629</v>
+        <v>3.315665609644828</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706517382514739</v>
+        <v>4.706625428113512</v>
       </c>
       <c r="K11" t="n">
-        <v>17.03939038283414</v>
+        <v>19.64644760671177</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57775429285459</v>
+        <v>42.60445394903736</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89056087779588</v>
+        <v>99.88962962180203</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.76139250572197</v>
+        <v>77.87238562575432</v>
       </c>
       <c r="C12" t="n">
-        <v>38.58399541126334</v>
+        <v>35.66984054953121</v>
       </c>
       <c r="D12" t="n">
-        <v>1.679505097203104</v>
+        <v>1.535250500546825</v>
       </c>
       <c r="E12" t="n">
-        <v>10.25904836103786</v>
+        <v>9.668876958275648</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538952369478128</v>
+        <v>0.7539517881134912</v>
       </c>
       <c r="G12" t="n">
-        <v>25.93522437874124</v>
+        <v>23.75399896440237</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67918089959939</v>
+        <v>34.68178225322058</v>
       </c>
       <c r="I12" t="n">
-        <v>2.742693301268747</v>
+        <v>2.766326485486095</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711845230923831</v>
+        <v>4.712198675709319</v>
       </c>
       <c r="K12" t="n">
-        <v>19.23860749427804</v>
+        <v>22.12761437424567</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08607735972845</v>
+        <v>42.11044325373298</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90868026526982</v>
+        <v>99.90789817750985</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.59656642953392</v>
+        <v>75.38045929924013</v>
       </c>
       <c r="C13" t="n">
-        <v>36.8437766229182</v>
+        <v>33.60436389669721</v>
       </c>
       <c r="D13" t="n">
-        <v>1.585042745952187</v>
+        <v>1.427267915424669</v>
       </c>
       <c r="E13" t="n">
-        <v>10.06333604629508</v>
+        <v>9.373415904646976</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546267184515636</v>
+        <v>0.7547211464665251</v>
       </c>
       <c r="G13" t="n">
-        <v>24.47651950245605</v>
+        <v>22.08324997962655</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71282904877192</v>
+        <v>34.71717273746015</v>
       </c>
       <c r="I13" t="n">
-        <v>2.287795377284842</v>
+        <v>2.307624450199487</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716416990322273</v>
+        <v>4.71700716541578</v>
       </c>
       <c r="K13" t="n">
-        <v>21.40343357046608</v>
+        <v>24.61954070075987</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6766038815805</v>
+        <v>41.69925300016831</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92381407496478</v>
+        <v>99.92315759762539</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.62108911008343</v>
+        <v>82.60750493371917</v>
       </c>
       <c r="C14" t="n">
-        <v>40.53600134612643</v>
+        <v>38.1354672848438</v>
       </c>
       <c r="D14" t="n">
-        <v>1.586903313818272</v>
+        <v>1.428960985107854</v>
       </c>
       <c r="E14" t="n">
-        <v>12.15385942868275</v>
+        <v>11.8805872337316</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555125205706709</v>
+        <v>0.7556164202119319</v>
       </c>
       <c r="G14" t="n">
-        <v>26.08730838436288</v>
+        <v>24.11554012560702</v>
       </c>
       <c r="H14" t="n">
-        <v>36.33563359944089</v>
+        <v>36.76444963636193</v>
       </c>
       <c r="I14" t="n">
-        <v>2.979918609641276</v>
+        <v>2.939747906374245</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721953253566694</v>
+        <v>4.722602626324573</v>
       </c>
       <c r="K14" t="n">
-        <v>15.37891088991656</v>
+        <v>17.39249506628085</v>
       </c>
       <c r="L14" t="n">
-        <v>43.98587360401394</v>
+        <v>44.37416215495745</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90078584005694</v>
+        <v>99.9021245060821</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.96643028846054</v>
+        <v>81.80152933844069</v>
       </c>
       <c r="C15" t="n">
-        <v>40.34280241048407</v>
+        <v>37.7685074411639</v>
       </c>
       <c r="D15" t="n">
-        <v>1.562359392264641</v>
+        <v>1.397919591533687</v>
       </c>
       <c r="E15" t="n">
-        <v>12.38016713277459</v>
+        <v>12.04574549696031</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562580524577954</v>
+        <v>0.7563714799456671</v>
       </c>
       <c r="G15" t="n">
-        <v>25.6838276902615</v>
+        <v>23.60621155491335</v>
       </c>
       <c r="H15" t="n">
-        <v>36.37148922426468</v>
+        <v>36.81572155836432</v>
       </c>
       <c r="I15" t="n">
-        <v>2.48571596857612</v>
+        <v>2.452237907062924</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726612827861222</v>
+        <v>4.727321749660418</v>
       </c>
       <c r="K15" t="n">
-        <v>16.03356971153946</v>
+        <v>18.19847066155932</v>
       </c>
       <c r="L15" t="n">
-        <v>43.54085236104198</v>
+        <v>43.95136223321085</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91722448306552</v>
+        <v>99.91834033593406</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.71675542417897</v>
+        <v>79.20501282772577</v>
       </c>
       <c r="C16" t="n">
-        <v>38.47817573244586</v>
+        <v>35.55032021084129</v>
       </c>
       <c r="D16" t="n">
-        <v>1.474907072285382</v>
+        <v>1.301070022472495</v>
       </c>
       <c r="E16" t="n">
-        <v>12.03272348619216</v>
+        <v>11.55208336483778</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568976032142536</v>
+        <v>0.7570225327870093</v>
       </c>
       <c r="G16" t="n">
-        <v>24.2461877153738</v>
+        <v>21.97074451510143</v>
       </c>
       <c r="H16" t="n">
-        <v>36.40224779056528</v>
+        <v>36.84741098712009</v>
       </c>
       <c r="I16" t="n">
-        <v>2.073181736458997</v>
+        <v>2.045290575488164</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730610020089086</v>
+        <v>4.731390829918807</v>
       </c>
       <c r="K16" t="n">
-        <v>18.28324457582103</v>
+        <v>20.79498717227424</v>
       </c>
       <c r="L16" t="n">
-        <v>43.16953202593933</v>
+        <v>43.58657489724384</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93095233420622</v>
+        <v>99.93188228035936</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.15090228801975</v>
+        <v>81.13566877551233</v>
       </c>
       <c r="C17" t="n">
-        <v>39.54510401730781</v>
+        <v>36.95045137489896</v>
       </c>
       <c r="D17" t="n">
-        <v>1.476125287253042</v>
+        <v>1.302152152302052</v>
       </c>
       <c r="E17" t="n">
-        <v>12.73198169229183</v>
+        <v>12.41573250250095</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575227707292435</v>
+        <v>0.7576521658199947</v>
       </c>
       <c r="G17" t="n">
-        <v>24.61213696051235</v>
+        <v>22.50564709361493</v>
       </c>
       <c r="H17" t="n">
-        <v>36.77823746103613</v>
+        <v>37.39468683092731</v>
       </c>
       <c r="I17" t="n">
-        <v>2.060380799139373</v>
+        <v>2.024471993972124</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734517317057773</v>
+        <v>4.735326036374966</v>
       </c>
       <c r="K17" t="n">
-        <v>16.84909771198025</v>
+        <v>18.86433122448768</v>
       </c>
       <c r="L17" t="n">
-        <v>43.5371755903633</v>
+        <v>44.11779108083357</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93137731965136</v>
+        <v>99.9325736802202</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.96361749034307</v>
+        <v>78.65281901399507</v>
       </c>
       <c r="C18" t="n">
-        <v>37.67664591299025</v>
+        <v>34.77951081855016</v>
       </c>
       <c r="D18" t="n">
-        <v>1.393939968764482</v>
+        <v>1.213767269689063</v>
       </c>
       <c r="E18" t="n">
-        <v>12.309477420064</v>
+        <v>11.85438005924568</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580586388116008</v>
+        <v>0.7581942609082718</v>
       </c>
       <c r="G18" t="n">
-        <v>23.24182216931466</v>
+        <v>20.9780537375068</v>
       </c>
       <c r="H18" t="n">
-        <v>36.80425421504309</v>
+        <v>37.42144248077985</v>
       </c>
       <c r="I18" t="n">
-        <v>1.71819858577273</v>
+        <v>1.688267075188724</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737866492572507</v>
+        <v>4.738714130676698</v>
       </c>
       <c r="K18" t="n">
-        <v>19.03638250965693</v>
+        <v>21.3471809860049</v>
       </c>
       <c r="L18" t="n">
-        <v>43.22973877737672</v>
+        <v>43.81707286227904</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94276720002389</v>
+        <v>99.94376466683411</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.05196657217947</v>
+        <v>77.72142514949911</v>
       </c>
       <c r="C19" t="n">
-        <v>37.03028597125959</v>
+        <v>34.10203866463904</v>
       </c>
       <c r="D19" t="n">
-        <v>1.360354532564949</v>
+        <v>1.181052430135981</v>
       </c>
       <c r="E19" t="n">
-        <v>12.25167528179433</v>
+        <v>11.77036957874404</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585108701558836</v>
+        <v>0.7586537390597954</v>
       </c>
       <c r="G19" t="n">
-        <v>22.6818362638095</v>
+        <v>20.41262931117977</v>
       </c>
       <c r="H19" t="n">
-        <v>36.82621034944594</v>
+        <v>37.44412048838943</v>
       </c>
       <c r="I19" t="n">
-        <v>1.432686335934607</v>
+        <v>1.413013732866377</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740692938474274</v>
+        <v>4.74158586912372</v>
       </c>
       <c r="K19" t="n">
-        <v>19.94803342782052</v>
+        <v>22.27857485050089</v>
       </c>
       <c r="L19" t="n">
-        <v>42.9739528624262</v>
+        <v>43.57231455345995</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95227226150632</v>
+        <v>99.95292806859987</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.70668911645836</v>
+        <v>75.17005921570248</v>
       </c>
       <c r="C20" t="n">
-        <v>34.90608370592779</v>
+        <v>31.76759103266552</v>
       </c>
       <c r="D20" t="n">
-        <v>1.273101637013193</v>
+        <v>1.091306582118227</v>
       </c>
       <c r="E20" t="n">
-        <v>11.66494120191864</v>
+        <v>11.07231681153693</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588995343199235</v>
+        <v>0.7590500804425468</v>
       </c>
       <c r="G20" t="n">
-        <v>21.22702735696028</v>
+        <v>18.86151381362902</v>
       </c>
       <c r="H20" t="n">
-        <v>36.84508025470819</v>
+        <v>37.46368231709494</v>
       </c>
       <c r="I20" t="n">
-        <v>1.194517042038616</v>
+        <v>1.178126608114904</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743122089499524</v>
+        <v>4.744063002765917</v>
       </c>
       <c r="K20" t="n">
-        <v>22.29331088354164</v>
+        <v>24.8299407842975</v>
       </c>
       <c r="L20" t="n">
-        <v>42.76080856786572</v>
+        <v>43.36321780156846</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96020315733514</v>
+        <v>99.96074961853149</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.87532570743767</v>
+        <v>81.49889579112954</v>
       </c>
       <c r="C21" t="n">
-        <v>38.03199602998055</v>
+        <v>35.75766984566097</v>
       </c>
       <c r="D21" t="n">
-        <v>1.274019207281624</v>
+        <v>1.092033786729524</v>
       </c>
       <c r="E21" t="n">
-        <v>13.37780982001719</v>
+        <v>13.2035294443228</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594465005865381</v>
+        <v>0.7595558821372749</v>
       </c>
       <c r="G21" t="n">
-        <v>22.64813153338415</v>
+        <v>20.72637826437402</v>
       </c>
       <c r="H21" t="n">
-        <v>38.27744092517236</v>
+        <v>39.34094253538822</v>
       </c>
       <c r="I21" t="n">
-        <v>1.791937092329934</v>
+        <v>1.629231614819731</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746540628665865</v>
+        <v>4.747224263357967</v>
       </c>
       <c r="K21" t="n">
-        <v>17.12467429256233</v>
+        <v>18.50110420887044</v>
       </c>
       <c r="L21" t="n">
-        <v>44.78364146049694</v>
+        <v>45.68695438944611</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94031178303982</v>
+        <v>99.94572844397753</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.64793290219151</v>
+        <v>45.8</v>
       </c>
       <c r="M2" t="n">
-        <v>99.70491021209955</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96339181555815</v>
+        <v>81.53737598736153</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91916121149524</v>
+        <v>43.29293154291709</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228573772030776</v>
+        <v>2.183377891902308</v>
       </c>
       <c r="E3" t="n">
-        <v>5.69733235488383</v>
+        <v>4.157479792166488</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428579240102587</v>
+        <v>0.7376756315691528</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97050191140482</v>
+        <v>32.84164245736388</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1714645044719</v>
+        <v>33.93307905218103</v>
       </c>
       <c r="I3" t="n">
-        <v>6.509799323692453</v>
+        <v>3.07364846487147</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642862025064117</v>
+        <v>4.610472697307205</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03660818444184</v>
+        <v>18.46262401263846</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81054574586734</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7663151418044</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.94500347674385</v>
+        <v>88.66533479325497</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52501641847267</v>
+        <v>42.86399755813849</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178934909816361</v>
+        <v>2.18915839664503</v>
       </c>
       <c r="E4" t="n">
-        <v>6.476454108094079</v>
+        <v>6.52746704178519</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444061359599095</v>
+        <v>0.7396286317816635</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2138488964148</v>
+        <v>33.52122615260679</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24268225415583</v>
+        <v>34.02291706195652</v>
       </c>
       <c r="I4" t="n">
-        <v>5.436138822553424</v>
+        <v>7.042258559844385</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652538349749434</v>
+        <v>4.622678948635397</v>
       </c>
       <c r="K4" t="n">
-        <v>13.05499652325615</v>
+        <v>11.33466520674503</v>
       </c>
       <c r="L4" t="n">
-        <v>44.23915929927973</v>
+        <v>45.56721512267686</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81917224100854</v>
+        <v>99.76587788756038</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.57283949617714</v>
+        <v>87.67283672419101</v>
       </c>
       <c r="C5" t="n">
-        <v>41.99649935062866</v>
+        <v>42.96307362039977</v>
       </c>
       <c r="D5" t="n">
-        <v>2.111251101109302</v>
+        <v>2.142498321025822</v>
       </c>
       <c r="E5" t="n">
-        <v>7.03163130195593</v>
+        <v>7.368618249268256</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457220547323561</v>
+        <v>0.7412826040185694</v>
       </c>
       <c r="G5" t="n">
-        <v>32.18213391263882</v>
+        <v>32.80674932465032</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30321451768837</v>
+        <v>34.09899978485419</v>
       </c>
       <c r="I5" t="n">
-        <v>4.538123765975148</v>
+        <v>5.881672165257802</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660762842077225</v>
+        <v>4.633016275116059</v>
       </c>
       <c r="K5" t="n">
-        <v>14.42716050382283</v>
+        <v>12.32716327580899</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42533628936646</v>
+        <v>44.51414481046224</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84899614381796</v>
+        <v>99.80438170667099</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.99534372746164</v>
+        <v>86.44674140934451</v>
       </c>
       <c r="C6" t="n">
-        <v>41.12353756921743</v>
+        <v>42.64995209595781</v>
       </c>
       <c r="D6" t="n">
-        <v>2.033710684720036</v>
+        <v>2.084362049769781</v>
       </c>
       <c r="E6" t="n">
-        <v>7.40462125000689</v>
+        <v>7.987117971032526</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468429057321947</v>
+        <v>0.7426862418490185</v>
       </c>
       <c r="G6" t="n">
-        <v>31.00017310154915</v>
+        <v>31.91654462341461</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35477366368095</v>
+        <v>34.16356712505485</v>
       </c>
       <c r="I6" t="n">
-        <v>3.78745396094621</v>
+        <v>4.910674386667371</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667768160826216</v>
+        <v>4.641789011556367</v>
       </c>
       <c r="K6" t="n">
-        <v>16.00465627253836</v>
+        <v>13.55325859065549</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74574716474489</v>
+        <v>43.63340953101842</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87394100650067</v>
+        <v>99.83662021763172</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.25455040935788</v>
+        <v>85.04434733900784</v>
       </c>
       <c r="C7" t="n">
-        <v>39.97058989625815</v>
+        <v>42.01035492498862</v>
       </c>
       <c r="D7" t="n">
-        <v>1.948656094197766</v>
+        <v>2.017981411680983</v>
       </c>
       <c r="E7" t="n">
-        <v>7.621651432962746</v>
+        <v>8.415886206422417</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477993728085656</v>
+        <v>0.7438793936834664</v>
       </c>
       <c r="G7" t="n">
-        <v>29.7036725476197</v>
+        <v>30.90009904097566</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39877114919401</v>
+        <v>34.21845210943946</v>
       </c>
       <c r="I7" t="n">
-        <v>3.160253732521554</v>
+        <v>4.098802966284185</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673746080053534</v>
+        <v>4.649246210521667</v>
       </c>
       <c r="K7" t="n">
-        <v>17.74544959064212</v>
+        <v>14.95565266099216</v>
       </c>
       <c r="L7" t="n">
-        <v>42.178753458629</v>
+        <v>42.89758479216736</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89479294552928</v>
+        <v>99.86359237814814</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.26173183440972</v>
+        <v>83.46700466116393</v>
       </c>
       <c r="C8" t="n">
-        <v>42.31012094337629</v>
+        <v>41.06978156468031</v>
       </c>
       <c r="D8" t="n">
-        <v>1.952900383197781</v>
+        <v>1.943624619578064</v>
       </c>
       <c r="E8" t="n">
-        <v>9.483904349590601</v>
+        <v>8.675840875124321</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494281243680018</v>
+        <v>0.7448954904227011</v>
       </c>
       <c r="G8" t="n">
-        <v>30.21604204886317</v>
+        <v>29.76151955404397</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47369372092808</v>
+        <v>34.26519255944426</v>
       </c>
       <c r="I8" t="n">
-        <v>5.701837430162068</v>
+        <v>3.420334747408732</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68392577730001</v>
+        <v>4.655596815141883</v>
       </c>
       <c r="K8" t="n">
-        <v>12.7382681655903</v>
+        <v>16.53299533883607</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76196270839515</v>
+        <v>42.28336745853128</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81035181736173</v>
+        <v>99.88614436204766</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.15787355149348</v>
+        <v>81.70909087920319</v>
       </c>
       <c r="C9" t="n">
-        <v>41.09033848840365</v>
+        <v>39.843013249904</v>
       </c>
       <c r="D9" t="n">
-        <v>1.857715800243703</v>
+        <v>1.861176536420848</v>
       </c>
       <c r="E9" t="n">
-        <v>9.815055289833253</v>
+        <v>8.78341332544238</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508245763323471</v>
+        <v>0.7457626446767138</v>
       </c>
       <c r="G9" t="n">
-        <v>28.74330878213379</v>
+        <v>28.49904314046077</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53793051128796</v>
+        <v>34.30508165512884</v>
       </c>
       <c r="I9" t="n">
-        <v>4.760384989585247</v>
+        <v>2.853597047844181</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692653602077169</v>
+        <v>4.661016529229462</v>
       </c>
       <c r="K9" t="n">
-        <v>14.8421264485065</v>
+        <v>18.29090912079678</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90915069002981</v>
+        <v>41.77106833076009</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84161562693997</v>
+        <v>99.90499070146087</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.79156029237164</v>
+        <v>86.21190327256794</v>
       </c>
       <c r="C10" t="n">
-        <v>39.4617557713081</v>
+        <v>42.94465578104482</v>
       </c>
       <c r="D10" t="n">
-        <v>1.751746608806791</v>
+        <v>1.863279816796127</v>
       </c>
       <c r="E10" t="n">
-        <v>9.917399954041949</v>
+        <v>10.56626180758633</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520256957530826</v>
+        <v>0.746605416925595</v>
       </c>
       <c r="G10" t="n">
-        <v>27.1037118155447</v>
+        <v>29.8170396823743</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5931820046418</v>
+        <v>35.62963949127053</v>
       </c>
       <c r="I10" t="n">
-        <v>3.97333361512657</v>
+        <v>2.922793201830086</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700160598456765</v>
+        <v>4.666283855784969</v>
       </c>
       <c r="K10" t="n">
-        <v>17.20843970762834</v>
+        <v>13.78809672743207</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19757160468617</v>
+        <v>43.16993102695668</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86776708362262</v>
+        <v>99.90268353543357</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.35355239328821</v>
+        <v>86.03306811076233</v>
       </c>
       <c r="C11" t="n">
-        <v>37.63872806605289</v>
+        <v>43.13667361059092</v>
       </c>
       <c r="D11" t="n">
-        <v>1.643856045887973</v>
+        <v>1.850503689840492</v>
       </c>
       <c r="E11" t="n">
-        <v>9.859195455772655</v>
+        <v>10.93838353640897</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530600684981621</v>
+        <v>0.7473258371901558</v>
       </c>
       <c r="G11" t="n">
-        <v>25.43438663445565</v>
+        <v>29.64208431937463</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64076315091545</v>
+        <v>35.69351347135333</v>
       </c>
       <c r="I11" t="n">
-        <v>3.315665609644828</v>
+        <v>2.490470774156282</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706625428113512</v>
+        <v>4.670786482438474</v>
       </c>
       <c r="K11" t="n">
-        <v>19.64644760671177</v>
+        <v>13.96693188923767</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60445394903736</v>
+        <v>42.81345883462241</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88962962180203</v>
+        <v>99.917064334451</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.87238562575432</v>
+        <v>84.23245446388029</v>
       </c>
       <c r="C12" t="n">
-        <v>35.66984054953121</v>
+        <v>41.72358245456503</v>
       </c>
       <c r="D12" t="n">
-        <v>1.535250500546825</v>
+        <v>1.773431662599704</v>
       </c>
       <c r="E12" t="n">
-        <v>9.668876958275648</v>
+        <v>10.82899147886582</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539517881134912</v>
+        <v>0.7479401171129481</v>
       </c>
       <c r="G12" t="n">
-        <v>23.75399896440237</v>
+        <v>28.40751475721748</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68178225322058</v>
+        <v>35.72285249271221</v>
       </c>
       <c r="I12" t="n">
-        <v>2.766326485486095</v>
+        <v>2.077098223416186</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712198675709319</v>
+        <v>4.674625731955925</v>
       </c>
       <c r="K12" t="n">
-        <v>22.12761437424567</v>
+        <v>15.76754553611971</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11044325373298</v>
+        <v>42.4396922655887</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90789817750985</v>
+        <v>99.93082025627345</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.38045929924013</v>
+        <v>85.34782784815214</v>
       </c>
       <c r="C13" t="n">
-        <v>33.60436389669721</v>
+        <v>42.67259156097493</v>
       </c>
       <c r="D13" t="n">
-        <v>1.427267915424669</v>
+        <v>1.774759880731973</v>
       </c>
       <c r="E13" t="n">
-        <v>9.373415904646976</v>
+        <v>11.45460512310792</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547211464665251</v>
+        <v>0.7485002896001947</v>
       </c>
       <c r="G13" t="n">
-        <v>22.08324997962655</v>
+        <v>28.72668606111329</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71717273746015</v>
+        <v>36.04750264557009</v>
       </c>
       <c r="I13" t="n">
-        <v>2.307624450199487</v>
+        <v>1.917647038027451</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71700716541578</v>
+        <v>4.678126810001216</v>
       </c>
       <c r="K13" t="n">
-        <v>24.61954070075987</v>
+        <v>14.65217215184786</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69925300016831</v>
+        <v>42.61136255770634</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92315759762539</v>
+        <v>99.93612627052913</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.60750493371917</v>
+        <v>83.52760869961629</v>
       </c>
       <c r="C14" t="n">
-        <v>38.1354672848438</v>
+        <v>41.15067207241024</v>
       </c>
       <c r="D14" t="n">
-        <v>1.428960985107854</v>
+        <v>1.698847193913517</v>
       </c>
       <c r="E14" t="n">
-        <v>11.8805872337316</v>
+        <v>11.23116143018068</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556164202119319</v>
+        <v>0.7489779345037478</v>
       </c>
       <c r="G14" t="n">
-        <v>24.11554012560702</v>
+        <v>27.49794523483882</v>
       </c>
       <c r="H14" t="n">
-        <v>36.76444963636193</v>
+        <v>36.07050585099794</v>
       </c>
       <c r="I14" t="n">
-        <v>2.939747906374245</v>
+        <v>1.599058964533161</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722602626324573</v>
+        <v>4.681112090648424</v>
       </c>
       <c r="K14" t="n">
-        <v>17.39249506628085</v>
+        <v>16.47239130038371</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37416215495745</v>
+        <v>42.32366865392752</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9021245060821</v>
+        <v>99.94673202672146</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.80152933844069</v>
+        <v>82.73546592949067</v>
       </c>
       <c r="C15" t="n">
-        <v>37.7685074411639</v>
+        <v>40.5877154674376</v>
       </c>
       <c r="D15" t="n">
-        <v>1.397919591533687</v>
+        <v>1.665531469174643</v>
       </c>
       <c r="E15" t="n">
-        <v>12.04574549696031</v>
+        <v>11.23621486158472</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563714799456671</v>
+        <v>0.7493858580040494</v>
       </c>
       <c r="G15" t="n">
-        <v>23.60621155491335</v>
+        <v>26.95868898059141</v>
       </c>
       <c r="H15" t="n">
-        <v>36.81572155836432</v>
+        <v>36.09015129891642</v>
       </c>
       <c r="I15" t="n">
-        <v>2.452237907062924</v>
+        <v>1.351831848694106</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727321749660418</v>
+        <v>4.683661612525309</v>
       </c>
       <c r="K15" t="n">
-        <v>18.19847066155932</v>
+        <v>17.26453407050932</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95136223321085</v>
+        <v>42.10271392913673</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91834033593406</v>
+        <v>99.95496346708366</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.20501282772577</v>
+        <v>80.52572856181787</v>
       </c>
       <c r="C16" t="n">
-        <v>35.55032021084129</v>
+        <v>38.58783822511177</v>
       </c>
       <c r="D16" t="n">
-        <v>1.301070022472495</v>
+        <v>1.5739335936634</v>
       </c>
       <c r="E16" t="n">
-        <v>11.55208336483778</v>
+        <v>10.80610793728125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570225327870093</v>
+        <v>0.7497354758330439</v>
       </c>
       <c r="G16" t="n">
-        <v>21.97074451510143</v>
+        <v>25.47606395495066</v>
       </c>
       <c r="H16" t="n">
-        <v>36.84741098712009</v>
+        <v>36.10698876683824</v>
       </c>
       <c r="I16" t="n">
-        <v>2.045290575488164</v>
+        <v>1.127052109294745</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731390829918807</v>
+        <v>4.685846723956524</v>
       </c>
       <c r="K16" t="n">
-        <v>20.79498717227424</v>
+        <v>19.47427143818213</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58657489724384</v>
+        <v>41.90033945202016</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93188228035936</v>
+        <v>99.96244911531404</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.13566877551233</v>
+        <v>84.85543228708715</v>
       </c>
       <c r="C17" t="n">
-        <v>36.95045137489896</v>
+        <v>41.43459232602062</v>
       </c>
       <c r="D17" t="n">
-        <v>1.302152152302052</v>
+        <v>1.574723845954148</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41573250250095</v>
+        <v>12.33313148796285</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576521658199947</v>
+        <v>0.7501119085997233</v>
       </c>
       <c r="G17" t="n">
-        <v>22.50564709361493</v>
+        <v>26.79742887194433</v>
       </c>
       <c r="H17" t="n">
-        <v>37.39468683092731</v>
+        <v>37.43369133766889</v>
       </c>
       <c r="I17" t="n">
-        <v>2.024471993972124</v>
+        <v>1.278145406208945</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735326036374966</v>
+        <v>4.68819942874827</v>
       </c>
       <c r="K17" t="n">
-        <v>18.86433122448768</v>
+        <v>15.14456771291285</v>
       </c>
       <c r="L17" t="n">
-        <v>44.11779108083357</v>
+        <v>43.3782564948165</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9325736802202</v>
+        <v>99.95741653374998</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.65281901399507</v>
+        <v>86.42749506842053</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77951081855016</v>
+        <v>42.14361035267844</v>
       </c>
       <c r="D18" t="n">
-        <v>1.213767269689063</v>
+        <v>1.575995578685461</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85438005924568</v>
+        <v>12.91860174107889</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581942609082718</v>
+        <v>0.7507176921907731</v>
       </c>
       <c r="G18" t="n">
-        <v>20.9780537375068</v>
+        <v>26.9323301391668</v>
       </c>
       <c r="H18" t="n">
-        <v>37.42144248077985</v>
+        <v>37.46392244812695</v>
       </c>
       <c r="I18" t="n">
-        <v>1.688267075188724</v>
+        <v>2.093941892979323</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738714130676698</v>
+        <v>4.691985576192331</v>
       </c>
       <c r="K18" t="n">
-        <v>21.3471809860049</v>
+        <v>13.57250493157947</v>
       </c>
       <c r="L18" t="n">
-        <v>43.81707286227904</v>
+        <v>44.21414297544128</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94376466683411</v>
+        <v>99.9302582596992</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.72142514949911</v>
+        <v>83.91340609495417</v>
       </c>
       <c r="C19" t="n">
-        <v>34.10203866463904</v>
+        <v>39.95438144056936</v>
       </c>
       <c r="D19" t="n">
-        <v>1.181052430135981</v>
+        <v>1.481379465992306</v>
       </c>
       <c r="E19" t="n">
-        <v>11.77036957874404</v>
+        <v>12.43405049035953</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586537390597954</v>
+        <v>0.7512384173535454</v>
       </c>
       <c r="G19" t="n">
-        <v>20.41262931117977</v>
+        <v>25.31542688258397</v>
       </c>
       <c r="H19" t="n">
-        <v>37.44412048838943</v>
+        <v>37.48990879068663</v>
       </c>
       <c r="I19" t="n">
-        <v>1.413013732866377</v>
+        <v>1.746161939518547</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74158586912372</v>
+        <v>4.695240108459657</v>
       </c>
       <c r="K19" t="n">
-        <v>22.27857485050089</v>
+        <v>16.08659390504583</v>
       </c>
       <c r="L19" t="n">
-        <v>43.57231455345995</v>
+        <v>43.90085960180205</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95292806859987</v>
+        <v>99.94183494741723</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.17005921570248</v>
+        <v>81.38713363247811</v>
       </c>
       <c r="C20" t="n">
-        <v>31.76759103266552</v>
+        <v>37.69834528541308</v>
       </c>
       <c r="D20" t="n">
-        <v>1.091306582118227</v>
+        <v>1.3868124832278</v>
       </c>
       <c r="E20" t="n">
-        <v>11.07231681153693</v>
+        <v>11.88296376571993</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590500804425468</v>
+        <v>0.7516864018221832</v>
       </c>
       <c r="G20" t="n">
-        <v>18.86151381362902</v>
+        <v>23.69936321176901</v>
       </c>
       <c r="H20" t="n">
-        <v>37.46368231709494</v>
+        <v>37.51226507130396</v>
       </c>
       <c r="I20" t="n">
-        <v>1.178126608114904</v>
+        <v>1.456002687246564</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744063002765917</v>
+        <v>4.698040011388644</v>
       </c>
       <c r="K20" t="n">
-        <v>24.8299407842975</v>
+        <v>18.6128663675219</v>
       </c>
       <c r="L20" t="n">
-        <v>43.36321780156846</v>
+        <v>43.64028384874508</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96074961853149</v>
+        <v>99.95149550168006</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.49889579112954</v>
+        <v>78.90708185191798</v>
       </c>
       <c r="C21" t="n">
-        <v>35.75766984566097</v>
+        <v>35.44299667742972</v>
       </c>
       <c r="D21" t="n">
-        <v>1.092033786729524</v>
+        <v>1.294442506234133</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2035294443228</v>
+        <v>11.29381385425014</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595558821372749</v>
+        <v>0.7520718828830788</v>
       </c>
       <c r="G21" t="n">
-        <v>20.72637826437402</v>
+        <v>22.12084437010087</v>
       </c>
       <c r="H21" t="n">
-        <v>39.34094253538822</v>
+        <v>37.5315021729746</v>
       </c>
       <c r="I21" t="n">
-        <v>1.629231614819731</v>
+        <v>1.213957797455918</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747224263357967</v>
+        <v>4.700449268019241</v>
       </c>
       <c r="K21" t="n">
-        <v>18.50110420887044</v>
+        <v>21.09291814808202</v>
       </c>
       <c r="L21" t="n">
-        <v>45.68695438944611</v>
+        <v>43.42364065539807</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94572844397753</v>
+        <v>99.95955548090981</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,34 +541,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>81.53737598736153</v>
+        <v>81.7718764244507</v>
       </c>
       <c r="C3" t="n">
-        <v>43.29293154291709</v>
+        <v>43.52743198000626</v>
       </c>
       <c r="D3" t="n">
-        <v>2.183377891902308</v>
+        <v>2.193676824842777</v>
       </c>
       <c r="E3" t="n">
-        <v>4.157479792166488</v>
+        <v>4.217303454067029</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7376756315691528</v>
+        <v>0.7378404744011169</v>
       </c>
       <c r="G3" t="n">
-        <v>32.84164245736388</v>
+        <v>32.99655557367677</v>
       </c>
       <c r="H3" t="n">
-        <v>33.93307905218103</v>
+        <v>33.94066182245137</v>
       </c>
       <c r="I3" t="n">
-        <v>3.07364846487147</v>
+        <v>3.074335310004654</v>
       </c>
       <c r="J3" t="n">
-        <v>4.610472697307205</v>
+        <v>4.61150296500698</v>
       </c>
       <c r="K3" t="n">
-        <v>18.46262401263846</v>
+        <v>18.2281235755493</v>
       </c>
       <c r="L3" t="n">
         <v>45.13333333333333</v>
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>88.66533479325497</v>
+        <v>89.03675555353047</v>
       </c>
       <c r="C4" t="n">
-        <v>42.86399755813849</v>
+        <v>43.14851201716499</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18915839664503</v>
+        <v>2.199522860294318</v>
       </c>
       <c r="E4" t="n">
-        <v>6.52746704178519</v>
+        <v>6.631432203584481</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7396286317816635</v>
+        <v>0.7398067811615671</v>
       </c>
       <c r="G4" t="n">
-        <v>33.52122615260679</v>
+        <v>33.69273872835906</v>
       </c>
       <c r="H4" t="n">
-        <v>34.02291706195652</v>
+        <v>34.03111193343207</v>
       </c>
       <c r="I4" t="n">
-        <v>7.042258559844385</v>
+        <v>7.118350664439177</v>
       </c>
       <c r="J4" t="n">
-        <v>4.622678948635397</v>
+        <v>4.623792382259793</v>
       </c>
       <c r="K4" t="n">
-        <v>11.33466520674503</v>
+        <v>10.96324444646954</v>
       </c>
       <c r="L4" t="n">
-        <v>45.56721512267686</v>
+        <v>45.65159583478781</v>
       </c>
       <c r="M4" t="n">
-        <v>99.76587788756038</v>
+        <v>99.76335229842235</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>87.67283672419101</v>
+        <v>88.31485036002323</v>
       </c>
       <c r="C5" t="n">
-        <v>42.96307362039977</v>
+        <v>43.53025519439764</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142498321025822</v>
+        <v>2.167034439963116</v>
       </c>
       <c r="E5" t="n">
-        <v>7.368618249268256</v>
+        <v>7.524359860098404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7412826040185694</v>
+        <v>0.7414668836441215</v>
       </c>
       <c r="G5" t="n">
-        <v>32.80674932465032</v>
+        <v>33.19507449504899</v>
       </c>
       <c r="H5" t="n">
-        <v>34.09899978485419</v>
+        <v>34.10747664762957</v>
       </c>
       <c r="I5" t="n">
-        <v>5.881672165257802</v>
+        <v>5.945270010863267</v>
       </c>
       <c r="J5" t="n">
-        <v>4.633016275116059</v>
+        <v>4.634168022775759</v>
       </c>
       <c r="K5" t="n">
-        <v>12.32716327580899</v>
+        <v>11.68514963997676</v>
       </c>
       <c r="L5" t="n">
-        <v>44.51414481046224</v>
+        <v>44.58686320272452</v>
       </c>
       <c r="M5" t="n">
-        <v>99.80438170667099</v>
+        <v>99.80226803709891</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>86.44674140934451</v>
+        <v>87.41001199430458</v>
       </c>
       <c r="C6" t="n">
-        <v>42.64995209595781</v>
+        <v>43.54882925898922</v>
       </c>
       <c r="D6" t="n">
-        <v>2.084362049769781</v>
+        <v>2.125328802816831</v>
       </c>
       <c r="E6" t="n">
-        <v>7.987117971032526</v>
+        <v>8.206844855799275</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7426862418490185</v>
+        <v>0.7428704112636436</v>
       </c>
       <c r="G6" t="n">
-        <v>31.91654462341461</v>
+        <v>32.55621905906525</v>
       </c>
       <c r="H6" t="n">
-        <v>34.16356712505485</v>
+        <v>34.17203891812759</v>
       </c>
       <c r="I6" t="n">
-        <v>4.910674386667371</v>
+        <v>4.963769876834221</v>
       </c>
       <c r="J6" t="n">
-        <v>4.641789011556367</v>
+        <v>4.642940070397772</v>
       </c>
       <c r="K6" t="n">
-        <v>13.55325859065549</v>
+        <v>12.58998800569541</v>
       </c>
       <c r="L6" t="n">
-        <v>43.63340953101842</v>
+        <v>43.69603634612472</v>
       </c>
       <c r="M6" t="n">
-        <v>99.83662021763172</v>
+        <v>99.83485361080935</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85.04434733900784</v>
+        <v>86.27707241325342</v>
       </c>
       <c r="C7" t="n">
-        <v>42.01035492498862</v>
+        <v>43.18773603078748</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017981411680983</v>
+        <v>2.072498261230683</v>
       </c>
       <c r="E7" t="n">
-        <v>8.415886206422417</v>
+        <v>8.693358532791295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7438793936834664</v>
+        <v>0.7440595195782052</v>
       </c>
       <c r="G7" t="n">
-        <v>30.90009904097566</v>
+        <v>31.74695007319911</v>
       </c>
       <c r="H7" t="n">
-        <v>34.21845210943946</v>
+        <v>34.22673790059742</v>
       </c>
       <c r="I7" t="n">
-        <v>4.098802966284185</v>
+        <v>4.143096128492946</v>
       </c>
       <c r="J7" t="n">
-        <v>4.649246210521667</v>
+        <v>4.650371997363782</v>
       </c>
       <c r="K7" t="n">
-        <v>14.95565266099216</v>
+        <v>13.72292758674656</v>
       </c>
       <c r="L7" t="n">
-        <v>42.89758479216736</v>
+        <v>42.95145388588721</v>
       </c>
       <c r="M7" t="n">
-        <v>99.86359237814814</v>
+        <v>99.86211750342126</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83.46700466116393</v>
+        <v>85.06703861155759</v>
       </c>
       <c r="C8" t="n">
-        <v>41.06978156468031</v>
+        <v>42.62226260294969</v>
       </c>
       <c r="D8" t="n">
-        <v>1.943624619578064</v>
+        <v>2.016236882557138</v>
       </c>
       <c r="E8" t="n">
-        <v>8.675840875124321</v>
+        <v>9.0335725612765</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7448954904227011</v>
+        <v>0.7450675109650666</v>
       </c>
       <c r="G8" t="n">
-        <v>29.76151955404397</v>
+        <v>30.88512682672857</v>
       </c>
       <c r="H8" t="n">
-        <v>34.26519255944426</v>
+        <v>34.27310550439304</v>
       </c>
       <c r="I8" t="n">
-        <v>3.420334747408732</v>
+        <v>3.457257382105609</v>
       </c>
       <c r="J8" t="n">
-        <v>4.655596815141883</v>
+        <v>4.656671943531665</v>
       </c>
       <c r="K8" t="n">
-        <v>16.53299533883607</v>
+        <v>14.93296138844241</v>
       </c>
       <c r="L8" t="n">
-        <v>42.28336745853128</v>
+        <v>42.32969000503866</v>
       </c>
       <c r="M8" t="n">
-        <v>99.88614436204766</v>
+        <v>99.88491399643075</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81.70909087920319</v>
+        <v>83.67296800117144</v>
       </c>
       <c r="C9" t="n">
-        <v>39.843013249904</v>
+        <v>41.76610780754471</v>
       </c>
       <c r="D9" t="n">
-        <v>1.861176536420848</v>
+        <v>1.951449555910762</v>
       </c>
       <c r="E9" t="n">
-        <v>8.78341332544238</v>
+        <v>9.224025010993481</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7457626446767138</v>
+        <v>0.7459236383868695</v>
       </c>
       <c r="G9" t="n">
-        <v>28.49904314046077</v>
+        <v>29.89270137436791</v>
       </c>
       <c r="H9" t="n">
-        <v>34.30508165512884</v>
+        <v>34.31248736579598</v>
       </c>
       <c r="I9" t="n">
-        <v>2.853597047844181</v>
+        <v>2.884358315798526</v>
       </c>
       <c r="J9" t="n">
-        <v>4.661016529229462</v>
+        <v>4.662022739917933</v>
       </c>
       <c r="K9" t="n">
-        <v>18.29090912079678</v>
+        <v>16.32703199882854</v>
       </c>
       <c r="L9" t="n">
-        <v>41.77106833076009</v>
+        <v>41.81082526634605</v>
       </c>
       <c r="M9" t="n">
-        <v>99.90499070146087</v>
+        <v>99.9039650727193</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>86.21190327256794</v>
+        <v>87.42535325249402</v>
       </c>
       <c r="C10" t="n">
-        <v>42.94465578104482</v>
+        <v>44.46016313372951</v>
       </c>
       <c r="D10" t="n">
-        <v>1.863279816796127</v>
+        <v>1.953541108845207</v>
       </c>
       <c r="E10" t="n">
-        <v>10.56626180758633</v>
+        <v>10.79261610134723</v>
       </c>
       <c r="F10" t="n">
-        <v>0.746605416925595</v>
+        <v>0.7467231152526765</v>
       </c>
       <c r="G10" t="n">
-        <v>29.8170396823743</v>
+        <v>31.01493496736101</v>
       </c>
       <c r="H10" t="n">
-        <v>35.62963949127053</v>
+        <v>35.43945806118151</v>
       </c>
       <c r="I10" t="n">
-        <v>2.922793201830086</v>
+        <v>2.811060428177159</v>
       </c>
       <c r="J10" t="n">
-        <v>4.666283855784969</v>
+        <v>4.667019470329228</v>
       </c>
       <c r="K10" t="n">
-        <v>13.78809672743207</v>
+        <v>12.57464674750597</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16993102695668</v>
+        <v>42.87158842627275</v>
       </c>
       <c r="M10" t="n">
-        <v>99.90268353543357</v>
+        <v>99.90639830750823</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>86.03306811076233</v>
+        <v>87.37728688489409</v>
       </c>
       <c r="C11" t="n">
-        <v>43.13667361059092</v>
+        <v>44.74690530720401</v>
       </c>
       <c r="D11" t="n">
-        <v>1.850503689840492</v>
+        <v>1.945133771573062</v>
       </c>
       <c r="E11" t="n">
-        <v>10.93838353640897</v>
+        <v>11.18120644568875</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7473258371901558</v>
+        <v>0.747410470200187</v>
       </c>
       <c r="G11" t="n">
-        <v>29.64208431937463</v>
+        <v>30.91434392555088</v>
       </c>
       <c r="H11" t="n">
-        <v>35.69351347135333</v>
+        <v>35.50496597446245</v>
       </c>
       <c r="I11" t="n">
-        <v>2.490470774156282</v>
+        <v>2.412910858667607</v>
       </c>
       <c r="J11" t="n">
-        <v>4.670786482438474</v>
+        <v>4.671315438751169</v>
       </c>
       <c r="K11" t="n">
-        <v>13.96693188923767</v>
+        <v>12.6227131151059</v>
       </c>
       <c r="L11" t="n">
-        <v>42.81345883462241</v>
+        <v>42.55002518339943</v>
       </c>
       <c r="M11" t="n">
-        <v>99.917064334451</v>
+        <v>99.91964360570934</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>84.23245446388029</v>
+        <v>85.87209093969696</v>
       </c>
       <c r="C12" t="n">
-        <v>41.72358245456503</v>
+        <v>43.61802517596404</v>
       </c>
       <c r="D12" t="n">
-        <v>1.773431662599704</v>
+        <v>1.880121644164072</v>
       </c>
       <c r="E12" t="n">
-        <v>10.82899147886582</v>
+        <v>11.14288572173434</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7479401171129481</v>
+        <v>0.7479942983440593</v>
       </c>
       <c r="G12" t="n">
-        <v>28.40751475721748</v>
+        <v>29.8810950583391</v>
       </c>
       <c r="H12" t="n">
-        <v>35.72285249271221</v>
+        <v>35.53270013020363</v>
       </c>
       <c r="I12" t="n">
-        <v>2.077098223416186</v>
+        <v>2.012329722261392</v>
       </c>
       <c r="J12" t="n">
-        <v>4.674625731955925</v>
+        <v>4.67496436465037</v>
       </c>
       <c r="K12" t="n">
-        <v>15.76754553611971</v>
+        <v>14.12790906030302</v>
       </c>
       <c r="L12" t="n">
-        <v>42.4396922655887</v>
+        <v>42.1870404621033</v>
       </c>
       <c r="M12" t="n">
-        <v>99.93082025627345</v>
+        <v>99.93297469837036</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>85.34782784815214</v>
+        <v>86.90181665425033</v>
       </c>
       <c r="C13" t="n">
-        <v>42.67259156097493</v>
+        <v>44.52013625654193</v>
       </c>
       <c r="D13" t="n">
-        <v>1.774759880731973</v>
+        <v>1.88144344413053</v>
       </c>
       <c r="E13" t="n">
-        <v>11.45460512310792</v>
+        <v>11.73778305749966</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7485002896001947</v>
+        <v>0.7485201679554915</v>
       </c>
       <c r="G13" t="n">
-        <v>28.72668606111329</v>
+        <v>30.18368900568975</v>
       </c>
       <c r="H13" t="n">
-        <v>36.04750264557009</v>
+        <v>35.83926737971674</v>
       </c>
       <c r="I13" t="n">
-        <v>1.917647038027451</v>
+        <v>1.83286254953633</v>
       </c>
       <c r="J13" t="n">
-        <v>4.678126810001216</v>
+        <v>4.678251049721822</v>
       </c>
       <c r="K13" t="n">
-        <v>14.65217215184786</v>
+        <v>13.09818334574967</v>
       </c>
       <c r="L13" t="n">
-        <v>42.61136255770634</v>
+        <v>42.32062790171279</v>
       </c>
       <c r="M13" t="n">
-        <v>99.93612627052913</v>
+        <v>99.9389475040044</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.52760869961629</v>
+        <v>85.3530212935076</v>
       </c>
       <c r="C14" t="n">
-        <v>41.15067207241024</v>
+        <v>43.25720455752386</v>
       </c>
       <c r="D14" t="n">
-        <v>1.698847193913517</v>
+        <v>1.816002097192363</v>
       </c>
       <c r="E14" t="n">
-        <v>11.23116143018068</v>
+        <v>11.58422954712634</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7489779345037478</v>
+        <v>0.7489669247201083</v>
       </c>
       <c r="G14" t="n">
-        <v>27.49794523483882</v>
+        <v>29.13382419563807</v>
       </c>
       <c r="H14" t="n">
-        <v>36.07050585099794</v>
+        <v>35.86065816626633</v>
       </c>
       <c r="I14" t="n">
-        <v>1.599058964533161</v>
+        <v>1.528297083063709</v>
       </c>
       <c r="J14" t="n">
-        <v>4.681112090648424</v>
+        <v>4.681043279500677</v>
       </c>
       <c r="K14" t="n">
-        <v>16.47239130038371</v>
+        <v>14.6469787064924</v>
       </c>
       <c r="L14" t="n">
-        <v>42.32366865392752</v>
+        <v>42.0449038873855</v>
       </c>
       <c r="M14" t="n">
-        <v>99.94673202672146</v>
+        <v>99.94908715140176</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.73546592949067</v>
+        <v>84.68769087433955</v>
       </c>
       <c r="C15" t="n">
-        <v>40.5877154674376</v>
+        <v>42.80838137805146</v>
       </c>
       <c r="D15" t="n">
-        <v>1.665531469174643</v>
+        <v>1.787436658678919</v>
       </c>
       <c r="E15" t="n">
-        <v>11.23621486158472</v>
+        <v>11.61786457907161</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7493858580040494</v>
+        <v>0.7493487202670204</v>
       </c>
       <c r="G15" t="n">
-        <v>26.95868898059141</v>
+        <v>28.67555354440444</v>
       </c>
       <c r="H15" t="n">
-        <v>36.09015129891642</v>
+        <v>35.87893859914704</v>
       </c>
       <c r="I15" t="n">
-        <v>1.351831848694106</v>
+        <v>1.295119271101636</v>
       </c>
       <c r="J15" t="n">
-        <v>4.683661612525309</v>
+        <v>4.683429501668877</v>
       </c>
       <c r="K15" t="n">
-        <v>17.26453407050932</v>
+        <v>15.31230912566046</v>
       </c>
       <c r="L15" t="n">
-        <v>42.10271392913673</v>
+        <v>41.83616084949708</v>
       </c>
       <c r="M15" t="n">
-        <v>99.95496346708366</v>
+        <v>99.956851353209</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.52572856181787</v>
+        <v>82.80042817508068</v>
       </c>
       <c r="C16" t="n">
-        <v>38.58783822511177</v>
+        <v>41.12281847970502</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5739335936634</v>
+        <v>1.70801493431724</v>
       </c>
       <c r="E16" t="n">
-        <v>10.80610793728125</v>
+        <v>11.28160028352971</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7497354758330439</v>
+        <v>0.7496744424881482</v>
       </c>
       <c r="G16" t="n">
-        <v>25.47606395495066</v>
+        <v>27.40140382924446</v>
       </c>
       <c r="H16" t="n">
-        <v>36.10698876683824</v>
+        <v>35.89453423206953</v>
       </c>
       <c r="I16" t="n">
-        <v>1.127052109294745</v>
+        <v>1.079735187880664</v>
       </c>
       <c r="J16" t="n">
-        <v>4.685846723956524</v>
+        <v>4.685465265550926</v>
       </c>
       <c r="K16" t="n">
-        <v>19.47427143818213</v>
+        <v>17.19957182491931</v>
       </c>
       <c r="L16" t="n">
-        <v>41.90033945202016</v>
+        <v>41.64163416006728</v>
       </c>
       <c r="M16" t="n">
-        <v>99.96244911531404</v>
+        <v>99.96402446469162</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>84.85543228708715</v>
+        <v>86.60850971012957</v>
       </c>
       <c r="C17" t="n">
-        <v>41.43459232602062</v>
+        <v>43.67321930740078</v>
       </c>
       <c r="D17" t="n">
-        <v>1.574723845954148</v>
+        <v>1.708768839857284</v>
       </c>
       <c r="E17" t="n">
-        <v>12.33313148796285</v>
+        <v>12.64897266655574</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7501119085997233</v>
+        <v>0.7500053434094843</v>
       </c>
       <c r="G17" t="n">
-        <v>26.79742887194433</v>
+        <v>28.58474950330305</v>
       </c>
       <c r="H17" t="n">
-        <v>37.43369133766889</v>
+        <v>37.08162871296486</v>
       </c>
       <c r="I17" t="n">
-        <v>1.278145406208945</v>
+        <v>1.14685124772988</v>
       </c>
       <c r="J17" t="n">
-        <v>4.68819942874827</v>
+        <v>4.687533396309277</v>
       </c>
       <c r="K17" t="n">
-        <v>15.14456771291285</v>
+        <v>13.39149028987045</v>
       </c>
       <c r="L17" t="n">
-        <v>43.3782564948165</v>
+        <v>42.89707889409026</v>
       </c>
       <c r="M17" t="n">
-        <v>99.95741653374998</v>
+        <v>99.96178849136147</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>86.42749506842053</v>
+        <v>88.10587130864678</v>
       </c>
       <c r="C18" t="n">
-        <v>42.14361035267844</v>
+        <v>44.37528716727153</v>
       </c>
       <c r="D18" t="n">
-        <v>1.575995578685461</v>
+        <v>1.709996843948977</v>
       </c>
       <c r="E18" t="n">
-        <v>12.91860174107889</v>
+        <v>13.21911241264621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7507176921907731</v>
+        <v>0.7505443335929518</v>
       </c>
       <c r="G18" t="n">
-        <v>26.9323301391668</v>
+        <v>28.72752380877559</v>
       </c>
       <c r="H18" t="n">
-        <v>37.46392244812695</v>
+        <v>37.10827736825632</v>
       </c>
       <c r="I18" t="n">
-        <v>2.093941892979323</v>
+        <v>1.899514456470797</v>
       </c>
       <c r="J18" t="n">
-        <v>4.691985576192331</v>
+        <v>4.690902084955949</v>
       </c>
       <c r="K18" t="n">
-        <v>13.57250493157947</v>
+        <v>11.89412869135321</v>
       </c>
       <c r="L18" t="n">
-        <v>44.21414297544128</v>
+        <v>43.6673124629204</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9302582596992</v>
+        <v>99.93672832154515</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>83.91340609495417</v>
+        <v>86.05467637773279</v>
       </c>
       <c r="C19" t="n">
-        <v>39.95438144056936</v>
+        <v>42.61980392033735</v>
       </c>
       <c r="D19" t="n">
-        <v>1.481379465992306</v>
+        <v>1.630652943541486</v>
       </c>
       <c r="E19" t="n">
-        <v>12.43405049035953</v>
+        <v>12.86972854778341</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7512384173535454</v>
+        <v>0.7510048110202298</v>
       </c>
       <c r="G19" t="n">
-        <v>25.31542688258397</v>
+        <v>27.39456591700925</v>
       </c>
       <c r="H19" t="n">
-        <v>37.48990879068663</v>
+        <v>37.13104421003827</v>
       </c>
       <c r="I19" t="n">
-        <v>1.746161939518547</v>
+        <v>1.583899879463698</v>
       </c>
       <c r="J19" t="n">
-        <v>4.695240108459657</v>
+        <v>4.693780068876436</v>
       </c>
       <c r="K19" t="n">
-        <v>16.08659390504583</v>
+        <v>13.9453236222672</v>
       </c>
       <c r="L19" t="n">
-        <v>43.90085960180205</v>
+        <v>43.38210816693793</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94183494741723</v>
+        <v>99.9472357095425</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>81.38713363247811</v>
+        <v>83.857191221409</v>
       </c>
       <c r="C20" t="n">
-        <v>37.69834528541308</v>
+        <v>40.66845315740053</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3868124832278</v>
+        <v>1.545932594600281</v>
       </c>
       <c r="E20" t="n">
-        <v>11.88296376571993</v>
+        <v>12.42118514953251</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7516864018221832</v>
+        <v>0.7513990463603708</v>
       </c>
       <c r="G20" t="n">
-        <v>23.69936321176901</v>
+        <v>25.9712850203757</v>
       </c>
       <c r="H20" t="n">
-        <v>37.51226507130396</v>
+        <v>37.15053592251352</v>
       </c>
       <c r="I20" t="n">
-        <v>1.456002687246564</v>
+        <v>1.320609448274304</v>
       </c>
       <c r="J20" t="n">
-        <v>4.698040011388644</v>
+        <v>4.696244039752318</v>
       </c>
       <c r="K20" t="n">
-        <v>18.6128663675219</v>
+        <v>16.142808778591</v>
       </c>
       <c r="L20" t="n">
-        <v>43.64028384874508</v>
+        <v>43.14474084513445</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95149550168006</v>
+        <v>99.95600278112599</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>78.90708185191798</v>
+        <v>81.57807374347703</v>
       </c>
       <c r="C21" t="n">
-        <v>35.44299667742972</v>
+        <v>38.59410231186392</v>
       </c>
       <c r="D21" t="n">
-        <v>1.294442506234133</v>
+        <v>1.458368483555571</v>
       </c>
       <c r="E21" t="n">
-        <v>11.29381385425014</v>
+        <v>11.90112971953323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7520718828830788</v>
+        <v>0.7517370835073984</v>
       </c>
       <c r="G21" t="n">
-        <v>22.12084437010087</v>
+        <v>24.50022962414349</v>
       </c>
       <c r="H21" t="n">
-        <v>37.5315021729746</v>
+        <v>37.16724909407612</v>
       </c>
       <c r="I21" t="n">
-        <v>1.213957797455918</v>
+        <v>1.101002966739989</v>
       </c>
       <c r="J21" t="n">
-        <v>4.700449268019241</v>
+        <v>4.698356771921241</v>
       </c>
       <c r="K21" t="n">
-        <v>21.09291814808202</v>
+        <v>18.42192625652294</v>
       </c>
       <c r="L21" t="n">
-        <v>43.42364065539807</v>
+        <v>42.94728783582776</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95955548090981</v>
+        <v>99.96331640421462</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>85.64121333208925</v>
+        <v>85.69925425636433</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9393911412661</v>
+        <v>45.9734684222036</v>
       </c>
       <c r="D3" t="n">
-        <v>2.221669419383689</v>
+        <v>2.221787059091686</v>
       </c>
       <c r="E3" t="n">
-        <v>5.215292318095341</v>
+        <v>5.231904252271777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7405564731278964</v>
+        <v>0.7405956863638954</v>
       </c>
       <c r="G3" t="n">
-        <v>34.34837364091675</v>
+        <v>34.36540350311107</v>
       </c>
       <c r="H3" t="n">
-        <v>34.99636055490366</v>
+        <v>35.01342472867947</v>
       </c>
       <c r="I3" t="n">
-        <v>3.490482968612549</v>
+        <v>3.497415987072088</v>
       </c>
       <c r="J3" t="n">
-        <v>4.628477957049352</v>
+        <v>4.628723039774346</v>
       </c>
       <c r="K3" t="n">
-        <v>14.35878666791075</v>
+        <v>14.30074574363567</v>
       </c>
       <c r="L3" t="n">
-        <v>46.57613353748314</v>
+        <v>46.59985419826393</v>
       </c>
       <c r="M3" t="n">
-        <v>106.87431134666</v>
+        <v>106.8740683641032</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>84.91287434526264</v>
+        <v>84.79854982510309</v>
       </c>
       <c r="C4" t="n">
-        <v>42.28234216589324</v>
+        <v>42.14473829000387</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185440073783514</v>
+        <v>2.176427405491693</v>
       </c>
       <c r="E4" t="n">
-        <v>5.615588670353945</v>
+        <v>5.611399887998713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7414030450214336</v>
+        <v>0.7414451315955414</v>
       </c>
       <c r="G4" t="n">
-        <v>33.78824570802836</v>
+        <v>33.66380485424579</v>
       </c>
       <c r="H4" t="n">
-        <v>35.0363668694751</v>
+        <v>35.05358427487585</v>
       </c>
       <c r="I4" t="n">
-        <v>2.912060947216318</v>
+        <v>2.917856198423384</v>
       </c>
       <c r="J4" t="n">
-        <v>4.633769031383959</v>
+        <v>4.634032072472133</v>
       </c>
       <c r="K4" t="n">
-        <v>15.08712565473737</v>
+        <v>15.20145017489691</v>
       </c>
       <c r="L4" t="n">
-        <v>42.53357431913014</v>
+        <v>42.55666109101389</v>
       </c>
       <c r="M4" t="n">
-        <v>99.90304213976074</v>
+        <v>99.90284955591466</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>84.0977834057237</v>
+        <v>83.71471589404608</v>
       </c>
       <c r="C5" t="n">
-        <v>41.92003946698391</v>
+        <v>41.51450115361132</v>
       </c>
       <c r="D5" t="n">
-        <v>2.14467142125271</v>
+        <v>2.121574540048496</v>
       </c>
       <c r="E5" t="n">
-        <v>5.915674057081551</v>
+        <v>5.875625385381431</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7421168600852158</v>
+        <v>0.7421636853721918</v>
       </c>
       <c r="G5" t="n">
-        <v>33.15793730222006</v>
+        <v>32.81537032648868</v>
       </c>
       <c r="H5" t="n">
-        <v>35.07009951546242</v>
+        <v>35.08755561583218</v>
       </c>
       <c r="I5" t="n">
-        <v>2.429053874089135</v>
+        <v>2.433903307346919</v>
       </c>
       <c r="J5" t="n">
-        <v>4.638230375532598</v>
+        <v>4.638523033576198</v>
       </c>
       <c r="K5" t="n">
-        <v>15.90221659427631</v>
+        <v>16.28528410595391</v>
       </c>
       <c r="L5" t="n">
-        <v>42.09685335687266</v>
+        <v>42.11916317936746</v>
       </c>
       <c r="M5" t="n">
-        <v>99.91910941813288</v>
+        <v>99.91894843893269</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.28382824679005</v>
+        <v>82.72314777481166</v>
       </c>
       <c r="C6" t="n">
-        <v>41.4838130753294</v>
+        <v>40.90120794407677</v>
       </c>
       <c r="D6" t="n">
-        <v>2.104024280980073</v>
+        <v>2.07172268615616</v>
       </c>
       <c r="E6" t="n">
-        <v>6.141198680475807</v>
+        <v>6.075881074384929</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7427185853658077</v>
+        <v>0.7427707410929153</v>
       </c>
       <c r="G6" t="n">
-        <v>32.52950755054864</v>
+        <v>32.04428874719067</v>
       </c>
       <c r="H6" t="n">
-        <v>35.09853515222845</v>
+        <v>35.11625562067291</v>
       </c>
       <c r="I6" t="n">
-        <v>2.025852838654969</v>
+        <v>2.029911773483353</v>
       </c>
       <c r="J6" t="n">
-        <v>4.641991158536297</v>
+        <v>4.64231713183072</v>
       </c>
       <c r="K6" t="n">
-        <v>16.71617175320994</v>
+        <v>17.27685222518834</v>
       </c>
       <c r="L6" t="n">
-        <v>41.73254145273597</v>
+        <v>41.75433140553081</v>
       </c>
       <c r="M6" t="n">
-        <v>99.93252628127532</v>
+        <v>99.93239157479591</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.47667741631713</v>
+        <v>81.69308278893106</v>
       </c>
       <c r="C7" t="n">
-        <v>40.9916667167106</v>
+        <v>40.18653045370564</v>
       </c>
       <c r="D7" t="n">
-        <v>2.063782459349655</v>
+        <v>2.020021442028254</v>
       </c>
       <c r="E7" t="n">
-        <v>6.305301933461618</v>
+        <v>6.206380264345622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7432256869269835</v>
+        <v>0.7432837725888743</v>
       </c>
       <c r="G7" t="n">
-        <v>31.90734427400853</v>
+        <v>31.24460179753552</v>
       </c>
       <c r="H7" t="n">
-        <v>35.12249917079669</v>
+        <v>35.14051040637845</v>
       </c>
       <c r="I7" t="n">
-        <v>1.689363348480031</v>
+        <v>1.692761527373872</v>
       </c>
       <c r="J7" t="n">
-        <v>4.645160543293646</v>
+        <v>4.645523578680463</v>
       </c>
       <c r="K7" t="n">
-        <v>17.52332258368286</v>
+        <v>18.30691721106895</v>
       </c>
       <c r="L7" t="n">
-        <v>41.42873700964389</v>
+        <v>41.45016589707309</v>
       </c>
       <c r="M7" t="n">
-        <v>99.94372631003735</v>
+        <v>99.94361356184767</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81.67913913158358</v>
+        <v>80.68265853008785</v>
       </c>
       <c r="C8" t="n">
-        <v>40.45674986741324</v>
+        <v>39.43896878534588</v>
       </c>
       <c r="D8" t="n">
-        <v>2.024079121524704</v>
+        <v>1.969458387279799</v>
       </c>
       <c r="E8" t="n">
-        <v>6.41876832521441</v>
+        <v>6.286271538427527</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7436529346051369</v>
+        <v>0.7437172045245596</v>
       </c>
       <c r="G8" t="n">
-        <v>31.29350628780569</v>
+        <v>30.46251974711124</v>
       </c>
       <c r="H8" t="n">
-        <v>35.14268954699818</v>
+        <v>35.16100193331351</v>
       </c>
       <c r="I8" t="n">
-        <v>1.408612074153368</v>
+        <v>1.411457191152711</v>
       </c>
       <c r="J8" t="n">
-        <v>4.647830841282105</v>
+        <v>4.648232528278496</v>
       </c>
       <c r="K8" t="n">
-        <v>18.3208608684164</v>
+        <v>19.31734146991215</v>
       </c>
       <c r="L8" t="n">
-        <v>41.17546250449036</v>
+        <v>41.1966685912038</v>
       </c>
       <c r="M8" t="n">
-        <v>99.95307324032001</v>
+        <v>99.95297884646183</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80.89579531564141</v>
+        <v>79.68397834488019</v>
       </c>
       <c r="C9" t="n">
-        <v>39.8923034190624</v>
+        <v>38.6593224131289</v>
       </c>
       <c r="D9" t="n">
-        <v>1.985137558307495</v>
+        <v>1.919603619138916</v>
       </c>
       <c r="E9" t="n">
-        <v>6.491011914321879</v>
+        <v>6.32327340911229</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7440128027173392</v>
+        <v>0.7440833180464048</v>
       </c>
       <c r="G9" t="n">
-        <v>30.69144580487518</v>
+        <v>29.69139309178905</v>
       </c>
       <c r="H9" t="n">
-        <v>35.15969577766908</v>
+        <v>35.17831082192211</v>
       </c>
       <c r="I9" t="n">
-        <v>1.174411440767067</v>
+        <v>1.176793347081393</v>
       </c>
       <c r="J9" t="n">
-        <v>4.650080016983369</v>
+        <v>4.650520737790028</v>
       </c>
       <c r="K9" t="n">
-        <v>19.10420468435859</v>
+        <v>20.31602165511982</v>
       </c>
       <c r="L9" t="n">
-        <v>40.96436378340809</v>
+        <v>40.98544878755261</v>
       </c>
       <c r="M9" t="n">
-        <v>99.96087188682907</v>
+        <v>99.96079285580132</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>80.10189601799422</v>
+        <v>78.70260422559041</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28082148268124</v>
+        <v>37.86042283922487</v>
       </c>
       <c r="D10" t="n">
-        <v>1.945692640623322</v>
+        <v>1.870719730562706</v>
       </c>
       <c r="E10" t="n">
-        <v>6.52521389808281</v>
+        <v>6.325758790837885</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7443159350723454</v>
+        <v>0.7443924974733483</v>
       </c>
       <c r="G10" t="n">
-        <v>30.08160315275504</v>
+        <v>28.93528347775188</v>
       </c>
       <c r="H10" t="n">
-        <v>35.1740208556025</v>
+        <v>35.19292801561128</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9790749416560501</v>
+        <v>0.9810686041448872</v>
       </c>
       <c r="J10" t="n">
-        <v>4.651974594202159</v>
+        <v>4.652453109208426</v>
       </c>
       <c r="K10" t="n">
-        <v>19.89810398200578</v>
+        <v>21.29739577440957</v>
       </c>
       <c r="L10" t="n">
-        <v>40.78845199529167</v>
+        <v>40.80949268227997</v>
       </c>
       <c r="M10" t="n">
-        <v>99.96737745997868</v>
+        <v>99.96731129591441</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.31490528575131</v>
+        <v>77.74272206383914</v>
       </c>
       <c r="C11" t="n">
-        <v>38.64581752507615</v>
+        <v>37.05253186322798</v>
       </c>
       <c r="D11" t="n">
-        <v>1.906628059977844</v>
+        <v>1.822999343415904</v>
       </c>
       <c r="E11" t="n">
-        <v>6.530233402759948</v>
+        <v>6.30070165133816</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7445712433428711</v>
+        <v>0.7446535280517113</v>
       </c>
       <c r="G11" t="n">
-        <v>29.47764074483351</v>
+        <v>28.19717027607765</v>
       </c>
       <c r="H11" t="n">
-        <v>35.18608591831166</v>
+        <v>35.20526885782205</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8161756456325211</v>
+        <v>0.8178438568104706</v>
       </c>
       <c r="J11" t="n">
-        <v>4.653570270892944</v>
+        <v>4.654084550323194</v>
       </c>
       <c r="K11" t="n">
-        <v>20.68509471424871</v>
+        <v>22.25727793616087</v>
       </c>
       <c r="L11" t="n">
-        <v>40.64189123451803</v>
+        <v>40.66293829494044</v>
       </c>
       <c r="M11" t="n">
-        <v>99.97280347384289</v>
+        <v>99.97274809432929</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.5690791653512</v>
+        <v>76.78713529933181</v>
       </c>
       <c r="C12" t="n">
-        <v>38.02660505907416</v>
+        <v>36.22352745893311</v>
       </c>
       <c r="D12" t="n">
-        <v>1.869661780503369</v>
+        <v>1.775562311175201</v>
       </c>
       <c r="E12" t="n">
-        <v>6.517013717375234</v>
+        <v>6.250371485613926</v>
       </c>
       <c r="F12" t="n">
-        <v>0.744786155539251</v>
+        <v>0.7448739029821664</v>
       </c>
       <c r="G12" t="n">
-        <v>28.90611936166748</v>
+        <v>27.46343985521171</v>
       </c>
       <c r="H12" t="n">
-        <v>35.19624199011047</v>
+        <v>35.21568760746055</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6803426880350786</v>
+        <v>0.6817382432497061</v>
       </c>
       <c r="J12" t="n">
-        <v>4.654913472120318</v>
+        <v>4.655461893638539</v>
       </c>
       <c r="K12" t="n">
-        <v>21.4309208346488</v>
+        <v>23.2128647006682</v>
       </c>
       <c r="L12" t="n">
-        <v>40.51980256056504</v>
+        <v>40.5408899554873</v>
       </c>
       <c r="M12" t="n">
-        <v>99.977328454288</v>
+        <v>99.97728211508861</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.81072733249613</v>
+        <v>75.8660788960664</v>
       </c>
       <c r="C13" t="n">
-        <v>37.37372122223512</v>
+        <v>35.40787701883559</v>
       </c>
       <c r="D13" t="n">
-        <v>1.832087036487195</v>
+        <v>1.729912917117586</v>
       </c>
       <c r="E13" t="n">
-        <v>6.480555761107365</v>
+        <v>6.184385044276332</v>
       </c>
       <c r="F13" t="n">
-        <v>0.744967090643046</v>
+        <v>0.7450598797501649</v>
       </c>
       <c r="G13" t="n">
-        <v>28.32519074300406</v>
+        <v>26.7573596572724</v>
       </c>
       <c r="H13" t="n">
-        <v>35.20479241179905</v>
+        <v>35.22448010205307</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5670899729363674</v>
+        <v>0.5682570471583067</v>
       </c>
       <c r="J13" t="n">
-        <v>4.656044316519037</v>
+        <v>4.656624248438529</v>
       </c>
       <c r="K13" t="n">
-        <v>22.18927266750389</v>
+        <v>24.13392110393362</v>
       </c>
       <c r="L13" t="n">
-        <v>40.41810770226002</v>
+        <v>40.43926470380718</v>
       </c>
       <c r="M13" t="n">
-        <v>99.98110159199902</v>
+        <v>99.98106282657639</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>77.07358817249505</v>
+        <v>74.94727610163602</v>
       </c>
       <c r="C14" t="n">
-        <v>36.72442396748175</v>
+        <v>34.5768392938692</v>
       </c>
       <c r="D14" t="n">
-        <v>1.795593135897958</v>
+        <v>1.684424794669234</v>
       </c>
       <c r="E14" t="n">
-        <v>6.43024619111219</v>
+        <v>6.100707632821711</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7451193800686804</v>
+        <v>0.745216832573387</v>
       </c>
       <c r="G14" t="n">
-        <v>27.76097262751083</v>
+        <v>26.05377392157385</v>
       </c>
       <c r="H14" t="n">
-        <v>35.21198912918873</v>
+        <v>35.23190042053862</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4726715832874033</v>
+        <v>0.4736472958755338</v>
       </c>
       <c r="J14" t="n">
-        <v>4.656996125429252</v>
+        <v>4.657605203583667</v>
       </c>
       <c r="K14" t="n">
-        <v>22.92641182750495</v>
+        <v>25.05272389836399</v>
       </c>
       <c r="L14" t="n">
-        <v>40.33341170576506</v>
+        <v>40.35465188979019</v>
       </c>
       <c r="M14" t="n">
-        <v>99.98424750075176</v>
+        <v>99.98421508202338</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>76.36117914261085</v>
+        <v>74.05993339786816</v>
       </c>
       <c r="C15" t="n">
-        <v>36.08517113571759</v>
+        <v>33.76256482451972</v>
       </c>
       <c r="D15" t="n">
-        <v>1.760349550316426</v>
+        <v>1.640546312588551</v>
       </c>
       <c r="E15" t="n">
-        <v>6.369694573070151</v>
+        <v>6.007583073278167</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7452475201237718</v>
+        <v>0.7453492450962308</v>
       </c>
       <c r="G15" t="n">
-        <v>27.21608514990586</v>
+        <v>25.37508523462869</v>
       </c>
       <c r="H15" t="n">
-        <v>35.21804462358008</v>
+        <v>35.23816053788347</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3939607248409927</v>
+        <v>0.394776212541619</v>
       </c>
       <c r="J15" t="n">
-        <v>4.657797000773574</v>
+        <v>4.658432781851441</v>
       </c>
       <c r="K15" t="n">
-        <v>23.63882085738915</v>
+        <v>25.94006660213184</v>
       </c>
       <c r="L15" t="n">
-        <v>40.26287824069082</v>
+        <v>40.28421170401857</v>
       </c>
       <c r="M15" t="n">
-        <v>99.98687023379755</v>
+        <v>99.98684313067012</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>75.65987776142313</v>
+        <v>73.19915232022026</v>
       </c>
       <c r="C16" t="n">
-        <v>35.44479217956754</v>
+        <v>32.96261281746341</v>
       </c>
       <c r="D16" t="n">
-        <v>1.725672112277582</v>
+        <v>1.598023334251618</v>
       </c>
       <c r="E16" t="n">
-        <v>6.298941512483121</v>
+        <v>5.906704699284228</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7453553274193739</v>
+        <v>0.7454609230135809</v>
       </c>
       <c r="G16" t="n">
-        <v>26.67995066100499</v>
+        <v>24.71736274825316</v>
       </c>
       <c r="H16" t="n">
-        <v>35.22313925596025</v>
+        <v>35.24344037737617</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3283480959067395</v>
+        <v>0.3290294692066196</v>
       </c>
       <c r="J16" t="n">
-        <v>4.658470796371087</v>
+        <v>4.65913076883488</v>
       </c>
       <c r="K16" t="n">
-        <v>24.34012223857685</v>
+        <v>26.80084767977974</v>
       </c>
       <c r="L16" t="n">
-        <v>40.20414222838781</v>
+        <v>40.22557349685292</v>
       </c>
       <c r="M16" t="n">
-        <v>99.98905664653221</v>
+        <v>99.98903399409606</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>74.9849576402685</v>
+        <v>72.36847099486212</v>
       </c>
       <c r="C17" t="n">
-        <v>34.8206033942397</v>
+        <v>32.18256891683426</v>
       </c>
       <c r="D17" t="n">
-        <v>1.692317794108337</v>
+        <v>1.557023142512071</v>
       </c>
       <c r="E17" t="n">
-        <v>6.222803095084177</v>
+        <v>5.800861769195611</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7454459995956014</v>
+        <v>0.7455550821863011</v>
       </c>
       <c r="G17" t="n">
-        <v>26.16427241786968</v>
+        <v>24.08319390337273</v>
       </c>
       <c r="H17" t="n">
-        <v>35.22742413670426</v>
+        <v>35.24789197649734</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2736566994339449</v>
+        <v>0.2742258574336958</v>
       </c>
       <c r="J17" t="n">
-        <v>4.659037497472508</v>
+        <v>4.65971926366438</v>
       </c>
       <c r="K17" t="n">
-        <v>25.01504235973149</v>
+        <v>27.63152900513788</v>
       </c>
       <c r="L17" t="n">
-        <v>40.15523346558695</v>
+        <v>40.1767623705499</v>
       </c>
       <c r="M17" t="n">
-        <v>99.99087921955814</v>
+        <v>99.99086029252203</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>74.33683307634783</v>
+        <v>71.54623165151858</v>
       </c>
       <c r="C18" t="n">
-        <v>34.21472261765852</v>
+        <v>31.40248147856674</v>
       </c>
       <c r="D18" t="n">
-        <v>1.660302942241516</v>
+        <v>1.516465712162684</v>
       </c>
       <c r="E18" t="n">
-        <v>6.14309339834465</v>
+        <v>5.687851560928863</v>
       </c>
       <c r="F18" t="n">
-        <v>0.745522235600578</v>
+        <v>0.7456344684045664</v>
       </c>
       <c r="G18" t="n">
-        <v>25.66930314639039</v>
+        <v>23.45587345279102</v>
       </c>
       <c r="H18" t="n">
-        <v>35.23102680957829</v>
+        <v>35.2516451490163</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2280705716887918</v>
+        <v>0.2285458806865931</v>
       </c>
       <c r="J18" t="n">
-        <v>4.659513972503611</v>
+        <v>4.660215427528539</v>
       </c>
       <c r="K18" t="n">
-        <v>25.66316692365215</v>
+        <v>28.45376834848143</v>
       </c>
       <c r="L18" t="n">
-        <v>40.11450888370506</v>
+        <v>40.13613278802313</v>
       </c>
       <c r="M18" t="n">
-        <v>99.99239842501574</v>
+        <v>99.99238261507129</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>73.68915714428064</v>
+        <v>70.76924143496667</v>
       </c>
       <c r="C19" t="n">
-        <v>33.60222225880004</v>
+        <v>30.66057746116392</v>
       </c>
       <c r="D19" t="n">
-        <v>1.628317103828101</v>
+        <v>1.478168056773543</v>
       </c>
       <c r="E19" t="n">
-        <v>6.056425517624085</v>
+        <v>5.575952774608164</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7455863360540147</v>
+        <v>0.7457013630403688</v>
       </c>
       <c r="G19" t="n">
-        <v>25.17478244071909</v>
+        <v>22.86350598207176</v>
       </c>
       <c r="H19" t="n">
-        <v>35.23405599460551</v>
+        <v>35.25480775222687</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1900751511122545</v>
+        <v>0.1904719872436474</v>
       </c>
       <c r="J19" t="n">
-        <v>4.659914600337591</v>
+        <v>4.660633519002304</v>
       </c>
       <c r="K19" t="n">
-        <v>26.31084285571936</v>
+        <v>29.23075856503334</v>
       </c>
       <c r="L19" t="n">
-        <v>40.08059959182256</v>
+        <v>40.10231547711701</v>
       </c>
       <c r="M19" t="n">
-        <v>99.99366470634196</v>
+        <v>99.99365150331427</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>73.04715856896679</v>
+        <v>69.99546353292678</v>
       </c>
       <c r="C20" t="n">
-        <v>32.98951214945478</v>
+        <v>29.91600471712669</v>
       </c>
       <c r="D20" t="n">
-        <v>1.596618984676644</v>
+        <v>1.440046142857137</v>
       </c>
       <c r="E20" t="n">
-        <v>5.96492754397855</v>
+        <v>5.458605546938655</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7456402311002571</v>
+        <v>0.7457577341370933</v>
       </c>
       <c r="G20" t="n">
-        <v>24.68471005153772</v>
+        <v>22.27385678563448</v>
       </c>
       <c r="H20" t="n">
-        <v>35.23660290431309</v>
+        <v>35.25747283006675</v>
       </c>
       <c r="I20" t="n">
-        <v>0.158407408983921</v>
+        <v>0.15873865493583</v>
       </c>
       <c r="J20" t="n">
-        <v>4.660251444376606</v>
+        <v>4.660985838356832</v>
       </c>
       <c r="K20" t="n">
-        <v>26.95284143103323</v>
+        <v>30.00453646707322</v>
       </c>
       <c r="L20" t="n">
-        <v>40.05236655420331</v>
+        <v>40.07416792726554</v>
       </c>
       <c r="M20" t="n">
-        <v>99.99472013469131</v>
+        <v>99.99470911146545</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>72.43726809947198</v>
+        <v>69.26802759400428</v>
       </c>
       <c r="C21" t="n">
-        <v>32.40400737082394</v>
+        <v>29.2128773060526</v>
       </c>
       <c r="D21" t="n">
-        <v>1.566516445289592</v>
+        <v>1.404227021789386</v>
       </c>
       <c r="E21" t="n">
-        <v>5.874467595075227</v>
+        <v>5.344878855405532</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7456855278083512</v>
+        <v>0.7458052099912301</v>
       </c>
       <c r="G21" t="n">
-        <v>24.21930630542427</v>
+        <v>21.719825946548</v>
       </c>
       <c r="H21" t="n">
-        <v>35.2387434837097</v>
+        <v>35.25971736413014</v>
       </c>
       <c r="I21" t="n">
-        <v>0.13201419336265</v>
+        <v>0.1322906336947877</v>
       </c>
       <c r="J21" t="n">
-        <v>4.660534548802194</v>
+        <v>4.661282562445187</v>
       </c>
       <c r="K21" t="n">
-        <v>27.562731900528</v>
+        <v>30.73197240599574</v>
       </c>
       <c r="L21" t="n">
-        <v>40.02886052284296</v>
+        <v>40.0507408808701</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9955997941949</v>
+        <v>99.99559059291843</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>85.69925425636433</v>
+        <v>81.96581640355788</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9734684222036</v>
+        <v>43.72137195911344</v>
       </c>
       <c r="D3" t="n">
-        <v>2.221787059091686</v>
+        <v>2.191880984263353</v>
       </c>
       <c r="E3" t="n">
-        <v>5.231904252271777</v>
+        <v>4.43226179661159</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7405956863638954</v>
+        <v>0.7379761477687374</v>
       </c>
       <c r="G3" t="n">
-        <v>34.36540350311107</v>
+        <v>32.96954313829461</v>
       </c>
       <c r="H3" t="n">
-        <v>35.01342472867947</v>
+        <v>33.94690279736191</v>
       </c>
       <c r="I3" t="n">
-        <v>3.497415987072088</v>
+        <v>3.074900615703072</v>
       </c>
       <c r="J3" t="n">
-        <v>4.628723039774346</v>
+        <v>4.612350923554608</v>
       </c>
       <c r="K3" t="n">
-        <v>14.30074574363567</v>
+        <v>18.03418359644212</v>
       </c>
       <c r="L3" t="n">
-        <v>46.59985419826393</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.8740683641032</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>84.79854982510309</v>
+        <v>81.43817028471045</v>
       </c>
       <c r="C4" t="n">
-        <v>42.14473829000387</v>
+        <v>40.2310854780496</v>
       </c>
       <c r="D4" t="n">
-        <v>2.176427405491693</v>
+        <v>2.164064314977761</v>
       </c>
       <c r="E4" t="n">
-        <v>5.611399887998713</v>
+        <v>4.819375559243527</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7414451315955414</v>
+        <v>0.7387509638673616</v>
       </c>
       <c r="G4" t="n">
-        <v>33.66380485424579</v>
+        <v>32.55113407112382</v>
       </c>
       <c r="H4" t="n">
-        <v>35.05358427487585</v>
+        <v>33.98254433789862</v>
       </c>
       <c r="I4" t="n">
-        <v>2.917856198423384</v>
+        <v>2.565107513428339</v>
       </c>
       <c r="J4" t="n">
-        <v>4.634032072472133</v>
+        <v>4.617193524171009</v>
       </c>
       <c r="K4" t="n">
-        <v>15.20145017489691</v>
+        <v>18.56182971528956</v>
       </c>
       <c r="L4" t="n">
-        <v>42.55666109101389</v>
+        <v>41.12167090066908</v>
       </c>
       <c r="M4" t="n">
-        <v>99.90284955591466</v>
+        <v>99.91458609400824</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.71471589404608</v>
+        <v>80.89897559872335</v>
       </c>
       <c r="C5" t="n">
-        <v>41.51450115361132</v>
+        <v>40.09039515564598</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121574540048496</v>
+        <v>2.135010754294381</v>
       </c>
       <c r="E5" t="n">
-        <v>5.875625385381431</v>
+        <v>5.137203446483646</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7421636853721918</v>
+        <v>0.7394022034512863</v>
       </c>
       <c r="G5" t="n">
-        <v>32.81537032648868</v>
+        <v>32.11412009584464</v>
       </c>
       <c r="H5" t="n">
-        <v>35.08755561583218</v>
+        <v>34.01250135875916</v>
       </c>
       <c r="I5" t="n">
-        <v>2.433903307346919</v>
+        <v>2.139473968319693</v>
       </c>
       <c r="J5" t="n">
-        <v>4.638523033576198</v>
+        <v>4.621263771570538</v>
       </c>
       <c r="K5" t="n">
-        <v>16.28528410595391</v>
+        <v>19.10102440127665</v>
       </c>
       <c r="L5" t="n">
-        <v>42.11916317936746</v>
+        <v>40.73732745659325</v>
       </c>
       <c r="M5" t="n">
-        <v>99.91894843893269</v>
+        <v>99.92874701351587</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>82.72314777481166</v>
+        <v>80.35979870773939</v>
       </c>
       <c r="C6" t="n">
-        <v>40.90120794407677</v>
+        <v>39.8837087713566</v>
       </c>
       <c r="D6" t="n">
-        <v>2.07172268615616</v>
+        <v>2.10555036978022</v>
       </c>
       <c r="E6" t="n">
-        <v>6.075881074384929</v>
+        <v>5.3967398579239</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7427707410929153</v>
+        <v>0.7399494306892456</v>
       </c>
       <c r="G6" t="n">
-        <v>32.04428874719067</v>
+        <v>31.6709868121108</v>
       </c>
       <c r="H6" t="n">
-        <v>35.11625562067291</v>
+        <v>34.03767381170529</v>
       </c>
       <c r="I6" t="n">
-        <v>2.029911773483353</v>
+        <v>1.784214483722139</v>
       </c>
       <c r="J6" t="n">
-        <v>4.64231713183072</v>
+        <v>4.624683941807784</v>
       </c>
       <c r="K6" t="n">
-        <v>17.27685222518834</v>
+        <v>19.64020129226063</v>
       </c>
       <c r="L6" t="n">
-        <v>41.75433140553081</v>
+        <v>40.41666010392944</v>
       </c>
       <c r="M6" t="n">
-        <v>99.93239157479591</v>
+        <v>99.94057016754667</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.69308278893106</v>
+        <v>79.82383544462198</v>
       </c>
       <c r="C7" t="n">
-        <v>40.18653045370564</v>
+        <v>39.6250707745704</v>
       </c>
       <c r="D7" t="n">
-        <v>2.020021442028254</v>
+        <v>2.077126172124138</v>
       </c>
       <c r="E7" t="n">
-        <v>6.206380264345622</v>
+        <v>5.588713898642</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7432837725888743</v>
+        <v>0.740409140465899</v>
       </c>
       <c r="G7" t="n">
-        <v>31.24460179753552</v>
+        <v>31.24343950570057</v>
       </c>
       <c r="H7" t="n">
-        <v>35.14051040637845</v>
+        <v>34.05882046143135</v>
       </c>
       <c r="I7" t="n">
-        <v>1.692761527373872</v>
+        <v>1.487769138346151</v>
       </c>
       <c r="J7" t="n">
-        <v>4.645523578680463</v>
+        <v>4.627557127911868</v>
       </c>
       <c r="K7" t="n">
-        <v>18.30691721106895</v>
+        <v>20.17616455537802</v>
       </c>
       <c r="L7" t="n">
-        <v>41.45016589707309</v>
+        <v>40.14920315661485</v>
       </c>
       <c r="M7" t="n">
-        <v>99.94361356184767</v>
+        <v>99.95043848656329</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>80.68265853008785</v>
+        <v>79.27390319245447</v>
       </c>
       <c r="C8" t="n">
-        <v>39.43896878534588</v>
+        <v>39.30639106731319</v>
       </c>
       <c r="D8" t="n">
-        <v>1.969458387279799</v>
+        <v>2.047458850254742</v>
       </c>
       <c r="E8" t="n">
-        <v>6.286271538427527</v>
+        <v>5.7414451683694</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7437172045245596</v>
+        <v>0.7407953304793046</v>
       </c>
       <c r="G8" t="n">
-        <v>30.46251974711124</v>
+        <v>30.7971935392484</v>
       </c>
       <c r="H8" t="n">
-        <v>35.16100193331351</v>
+        <v>34.076585202048</v>
       </c>
       <c r="I8" t="n">
-        <v>1.411457191152711</v>
+        <v>1.240454286558978</v>
       </c>
       <c r="J8" t="n">
-        <v>4.648232528278496</v>
+        <v>4.629970815495653</v>
       </c>
       <c r="K8" t="n">
-        <v>19.31734146991215</v>
+        <v>20.72609680754552</v>
       </c>
       <c r="L8" t="n">
-        <v>41.1966685912038</v>
+        <v>39.92618520463168</v>
       </c>
       <c r="M8" t="n">
-        <v>99.95297884646183</v>
+        <v>99.9586730794904</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79.68397834488019</v>
+        <v>78.725483105118</v>
       </c>
       <c r="C9" t="n">
-        <v>38.6593224131289</v>
+        <v>38.950758118593</v>
       </c>
       <c r="D9" t="n">
-        <v>1.919603619138916</v>
+        <v>2.018217993092948</v>
       </c>
       <c r="E9" t="n">
-        <v>6.32327340911229</v>
+        <v>5.851113781621248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7440833180464048</v>
+        <v>0.7411197084044423</v>
       </c>
       <c r="G9" t="n">
-        <v>29.69139309178905</v>
+        <v>30.35736231277308</v>
       </c>
       <c r="H9" t="n">
-        <v>35.17831082192211</v>
+        <v>34.09150658660434</v>
       </c>
       <c r="I9" t="n">
-        <v>1.176793347081393</v>
+        <v>1.034164545094183</v>
       </c>
       <c r="J9" t="n">
-        <v>4.650520737790028</v>
+        <v>4.631998177527764</v>
       </c>
       <c r="K9" t="n">
-        <v>20.31602165511982</v>
+        <v>21.27451689488199</v>
       </c>
       <c r="L9" t="n">
-        <v>40.98544878755261</v>
+        <v>39.74026792300947</v>
       </c>
       <c r="M9" t="n">
-        <v>99.96079285580132</v>
+        <v>99.96554293648447</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>78.70260422559041</v>
+        <v>78.18863451275563</v>
       </c>
       <c r="C10" t="n">
-        <v>37.86042283922487</v>
+        <v>38.57459916812575</v>
       </c>
       <c r="D10" t="n">
-        <v>1.870719730562706</v>
+        <v>1.988864770740386</v>
       </c>
       <c r="E10" t="n">
-        <v>6.325758790837885</v>
+        <v>5.942679031274047</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7443924974733483</v>
+        <v>0.7413920985979934</v>
       </c>
       <c r="G10" t="n">
-        <v>28.93528347775188</v>
+        <v>29.9158409265533</v>
       </c>
       <c r="H10" t="n">
-        <v>35.19292801561128</v>
+        <v>34.10403653550769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9810686041448872</v>
+        <v>0.8621205338447632</v>
       </c>
       <c r="J10" t="n">
-        <v>4.652453109208426</v>
+        <v>4.633700616237459</v>
       </c>
       <c r="K10" t="n">
-        <v>21.29739577440957</v>
+        <v>21.81136548724437</v>
       </c>
       <c r="L10" t="n">
-        <v>40.80949268227997</v>
+        <v>39.58530855171059</v>
       </c>
       <c r="M10" t="n">
-        <v>99.96731129591441</v>
+        <v>99.97127320708071</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>77.74272206383914</v>
+        <v>77.64789093921749</v>
       </c>
       <c r="C11" t="n">
-        <v>37.05253186322798</v>
+        <v>38.16777221666158</v>
       </c>
       <c r="D11" t="n">
-        <v>1.822999343415904</v>
+        <v>1.959627726224749</v>
       </c>
       <c r="E11" t="n">
-        <v>6.30070165133816</v>
+        <v>6.002231770157953</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7446535280517113</v>
+        <v>0.7416208257599725</v>
       </c>
       <c r="G11" t="n">
-        <v>28.19717027607765</v>
+        <v>29.47606704863059</v>
       </c>
       <c r="H11" t="n">
-        <v>35.20526885782205</v>
+        <v>34.11455798495872</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8178438568104706</v>
+        <v>0.7186554224856784</v>
       </c>
       <c r="J11" t="n">
-        <v>4.654084550323194</v>
+        <v>4.635130160999828</v>
       </c>
       <c r="K11" t="n">
-        <v>22.25727793616087</v>
+        <v>22.35210906078252</v>
       </c>
       <c r="L11" t="n">
-        <v>40.66293829494044</v>
+        <v>39.45617092994911</v>
       </c>
       <c r="M11" t="n">
-        <v>99.97274809432929</v>
+        <v>99.9760522073932</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.78713529933181</v>
+        <v>77.12380641258609</v>
       </c>
       <c r="C12" t="n">
-        <v>36.22352745893311</v>
+        <v>37.75527609726492</v>
       </c>
       <c r="D12" t="n">
-        <v>1.775562311175201</v>
+        <v>1.931227117364436</v>
       </c>
       <c r="E12" t="n">
-        <v>6.250371485613926</v>
+        <v>6.043136655917723</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7448739029821664</v>
+        <v>0.7418128358689141</v>
       </c>
       <c r="G12" t="n">
-        <v>27.46343985521171</v>
+        <v>29.04887455702339</v>
       </c>
       <c r="H12" t="n">
-        <v>35.21568760746055</v>
+        <v>34.12339044997004</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6817382432497061</v>
+        <v>0.5990345722608922</v>
       </c>
       <c r="J12" t="n">
-        <v>4.655461893638539</v>
+        <v>4.636330224180713</v>
       </c>
       <c r="K12" t="n">
-        <v>23.2128647006682</v>
+        <v>22.87619358741388</v>
       </c>
       <c r="L12" t="n">
-        <v>40.5408899554873</v>
+        <v>39.34856766469662</v>
       </c>
       <c r="M12" t="n">
-        <v>99.97728211508861</v>
+        <v>99.98003734937542</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.8660788960664</v>
+        <v>76.61021062290001</v>
       </c>
       <c r="C13" t="n">
-        <v>35.40787701883559</v>
+        <v>37.3346546226357</v>
       </c>
       <c r="D13" t="n">
-        <v>1.729912917117586</v>
+        <v>1.903496446116509</v>
       </c>
       <c r="E13" t="n">
-        <v>6.184385044276332</v>
+        <v>6.065536042162863</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7450598797501649</v>
+        <v>0.7419739937000566</v>
       </c>
       <c r="G13" t="n">
-        <v>26.7573596572724</v>
+        <v>28.63175904366915</v>
       </c>
       <c r="H13" t="n">
-        <v>35.22448010205307</v>
+        <v>34.13080371020259</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5682570471583067</v>
+        <v>0.4993039264234765</v>
       </c>
       <c r="J13" t="n">
-        <v>4.656624248438529</v>
+        <v>4.637337460625353</v>
       </c>
       <c r="K13" t="n">
-        <v>24.13392110393362</v>
+        <v>23.38978937709998</v>
       </c>
       <c r="L13" t="n">
-        <v>40.43926470380718</v>
+        <v>39.25891615103482</v>
       </c>
       <c r="M13" t="n">
-        <v>99.98106282657639</v>
+        <v>99.98336015077052</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>74.94727610163602</v>
+        <v>76.0868813696237</v>
       </c>
       <c r="C14" t="n">
-        <v>34.5768392938692</v>
+        <v>36.88878403993105</v>
       </c>
       <c r="D14" t="n">
-        <v>1.684424794669234</v>
+        <v>1.875330567887687</v>
       </c>
       <c r="E14" t="n">
-        <v>6.100707632821711</v>
+        <v>6.069972435710014</v>
       </c>
       <c r="F14" t="n">
-        <v>0.745216832573387</v>
+        <v>0.7421092696377947</v>
       </c>
       <c r="G14" t="n">
-        <v>26.05377392157385</v>
+        <v>28.20809729197729</v>
       </c>
       <c r="H14" t="n">
-        <v>35.23190042053862</v>
+        <v>34.13702640333855</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4736472958755338</v>
+        <v>0.4161624658361449</v>
       </c>
       <c r="J14" t="n">
-        <v>4.657605203583667</v>
+        <v>4.638182935236217</v>
       </c>
       <c r="K14" t="n">
-        <v>25.05272389836399</v>
+        <v>23.91311863037632</v>
       </c>
       <c r="L14" t="n">
-        <v>40.35465188979019</v>
+        <v>39.18422777618084</v>
       </c>
       <c r="M14" t="n">
-        <v>99.98421508202338</v>
+        <v>99.9861304464882</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>74.05993339786816</v>
+        <v>75.58134445823194</v>
       </c>
       <c r="C15" t="n">
-        <v>33.76256482451972</v>
+        <v>36.44777299629827</v>
       </c>
       <c r="D15" t="n">
-        <v>1.640546312588551</v>
+        <v>1.847878057976292</v>
       </c>
       <c r="E15" t="n">
-        <v>6.007583073278167</v>
+        <v>6.068081850263307</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7453492450962308</v>
+        <v>0.74222279165003</v>
       </c>
       <c r="G15" t="n">
-        <v>25.37508523462869</v>
+        <v>27.79516578872672</v>
       </c>
       <c r="H15" t="n">
-        <v>35.23816053788347</v>
+        <v>34.14224841590137</v>
       </c>
       <c r="I15" t="n">
-        <v>0.394776212541619</v>
+        <v>0.3468551059015238</v>
       </c>
       <c r="J15" t="n">
-        <v>4.658432781851441</v>
+        <v>4.638892447812688</v>
       </c>
       <c r="K15" t="n">
-        <v>25.94006660213184</v>
+        <v>24.41865554176808</v>
       </c>
       <c r="L15" t="n">
-        <v>40.28421170401857</v>
+        <v>39.12201139343821</v>
       </c>
       <c r="M15" t="n">
-        <v>99.98684313067012</v>
+        <v>99.98843993150456</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>73.19915232022026</v>
+        <v>75.06515927498978</v>
       </c>
       <c r="C16" t="n">
-        <v>32.96261281746341</v>
+        <v>35.98533762563827</v>
       </c>
       <c r="D16" t="n">
-        <v>1.598023334251618</v>
+        <v>1.820172018453615</v>
       </c>
       <c r="E16" t="n">
-        <v>5.906704699284228</v>
+        <v>6.049046190219318</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7454609230135809</v>
+        <v>0.7423180706551478</v>
       </c>
       <c r="G16" t="n">
-        <v>24.71736274825316</v>
+        <v>27.37842077757311</v>
       </c>
       <c r="H16" t="n">
-        <v>35.24344037737617</v>
+        <v>34.14663125013679</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3290294692066196</v>
+        <v>0.2890830263571213</v>
       </c>
       <c r="J16" t="n">
-        <v>4.65913076883488</v>
+        <v>4.639487941594673</v>
       </c>
       <c r="K16" t="n">
-        <v>26.80084767977974</v>
+        <v>24.93484072501025</v>
       </c>
       <c r="L16" t="n">
-        <v>40.22557349685292</v>
+        <v>39.07018678529866</v>
       </c>
       <c r="M16" t="n">
-        <v>99.98903399409606</v>
+        <v>99.99036513594717</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>72.36847099486212</v>
+        <v>74.5502491509548</v>
       </c>
       <c r="C17" t="n">
-        <v>32.18256891683426</v>
+        <v>35.51519735319363</v>
       </c>
       <c r="D17" t="n">
-        <v>1.557023142512071</v>
+        <v>1.792280087017586</v>
       </c>
       <c r="E17" t="n">
-        <v>5.800861769195611</v>
+        <v>6.025465472688865</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7455550821863011</v>
+        <v>0.7423980371034946</v>
       </c>
       <c r="G17" t="n">
-        <v>24.08319390337273</v>
+        <v>26.95887964222284</v>
       </c>
       <c r="H17" t="n">
-        <v>35.24789197649734</v>
+        <v>34.15030970676074</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2742258574336958</v>
+        <v>0.240928473264446</v>
       </c>
       <c r="J17" t="n">
-        <v>4.65971926366438</v>
+        <v>4.639987731896841</v>
       </c>
       <c r="K17" t="n">
-        <v>27.63152900513788</v>
+        <v>25.44975084904519</v>
       </c>
       <c r="L17" t="n">
-        <v>40.1767623705499</v>
+        <v>39.02702171369572</v>
       </c>
       <c r="M17" t="n">
-        <v>99.99086029252203</v>
+        <v>99.99196991593453</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>71.54623165151858</v>
+        <v>74.04802063684519</v>
       </c>
       <c r="C18" t="n">
-        <v>31.40248147856674</v>
+        <v>35.05025701287656</v>
       </c>
       <c r="D18" t="n">
-        <v>1.516465712162684</v>
+        <v>1.765365750572512</v>
       </c>
       <c r="E18" t="n">
-        <v>5.687851560928863</v>
+        <v>5.991551083738646</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7456344684045664</v>
+        <v>0.7424651410777332</v>
       </c>
       <c r="G18" t="n">
-        <v>23.45587345279102</v>
+        <v>26.55404316486153</v>
       </c>
       <c r="H18" t="n">
-        <v>35.2516451490163</v>
+        <v>34.15339648957571</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2285458806865931</v>
+        <v>0.2007918752832414</v>
       </c>
       <c r="J18" t="n">
-        <v>4.660215427528539</v>
+        <v>4.640407131735832</v>
       </c>
       <c r="K18" t="n">
-        <v>28.45376834848143</v>
+        <v>25.95197936315481</v>
       </c>
       <c r="L18" t="n">
-        <v>40.13613278802313</v>
+        <v>38.99107116637795</v>
       </c>
       <c r="M18" t="n">
-        <v>99.99238261507129</v>
+        <v>99.99330754240933</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>70.76924143496667</v>
+        <v>73.55507952828069</v>
       </c>
       <c r="C19" t="n">
-        <v>30.66057746116392</v>
+        <v>34.58837179214193</v>
       </c>
       <c r="D19" t="n">
-        <v>1.478168056773543</v>
+        <v>1.738320311834127</v>
       </c>
       <c r="E19" t="n">
-        <v>5.575952774608164</v>
+        <v>5.962918318822741</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7457013630403688</v>
+        <v>0.7425214451707451</v>
       </c>
       <c r="G19" t="n">
-        <v>22.86350598207176</v>
+        <v>26.14723469050498</v>
       </c>
       <c r="H19" t="n">
-        <v>35.25480775222687</v>
+        <v>34.15598647785426</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1904719872436474</v>
+        <v>0.1673392517766782</v>
       </c>
       <c r="J19" t="n">
-        <v>4.660633519002304</v>
+        <v>4.640759032317156</v>
       </c>
       <c r="K19" t="n">
-        <v>29.23075856503334</v>
+        <v>26.44492047171931</v>
       </c>
       <c r="L19" t="n">
-        <v>40.10231547711701</v>
+        <v>38.96113018404758</v>
       </c>
       <c r="M19" t="n">
-        <v>99.99365150331427</v>
+        <v>99.99442244790882</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>69.99546353292678</v>
+        <v>73.0721948413771</v>
       </c>
       <c r="C20" t="n">
-        <v>29.91600471712669</v>
+        <v>34.13135164217577</v>
       </c>
       <c r="D20" t="n">
-        <v>1.440046142857137</v>
+        <v>1.712165991281202</v>
       </c>
       <c r="E20" t="n">
-        <v>5.458605546938655</v>
+        <v>5.924958172400697</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7457577341370933</v>
+        <v>0.7425686818977972</v>
       </c>
       <c r="G20" t="n">
-        <v>22.27385678563448</v>
+        <v>25.75383011885474</v>
       </c>
       <c r="H20" t="n">
-        <v>35.25747283006675</v>
+        <v>34.15815936729866</v>
       </c>
       <c r="I20" t="n">
-        <v>0.15873865493583</v>
+        <v>0.139458247782771</v>
       </c>
       <c r="J20" t="n">
-        <v>4.660985838356832</v>
+        <v>4.641054261861232</v>
       </c>
       <c r="K20" t="n">
-        <v>30.00453646707322</v>
+        <v>26.9278051586229</v>
       </c>
       <c r="L20" t="n">
-        <v>40.07416792726554</v>
+        <v>38.93619488665198</v>
       </c>
       <c r="M20" t="n">
-        <v>99.99470911146545</v>
+        <v>99.99535168745064</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>69.26802759400428</v>
+        <v>72.57571011473732</v>
       </c>
       <c r="C21" t="n">
-        <v>29.2128773060526</v>
+        <v>33.65640743887558</v>
       </c>
       <c r="D21" t="n">
-        <v>1.404227021789386</v>
+        <v>1.685741384617522</v>
       </c>
       <c r="E21" t="n">
-        <v>5.344878855405532</v>
+        <v>5.873494299312406</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7458052099912301</v>
+        <v>0.7426083197596854</v>
       </c>
       <c r="G21" t="n">
-        <v>21.719825946548</v>
+        <v>25.35635999362189</v>
       </c>
       <c r="H21" t="n">
-        <v>35.25971736413014</v>
+        <v>34.15998270894552</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1322906336947877</v>
+        <v>0.1162214099822567</v>
       </c>
       <c r="J21" t="n">
-        <v>4.661282562445187</v>
+        <v>4.641301998498033</v>
       </c>
       <c r="K21" t="n">
-        <v>30.73197240599574</v>
+        <v>27.4242898852627</v>
       </c>
       <c r="L21" t="n">
-        <v>40.0507408808701</v>
+        <v>38.91542883564553</v>
       </c>
       <c r="M21" t="n">
-        <v>99.99559059291843</v>
+        <v>99.9961261597838</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,34 +541,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>81.96581640355788</v>
+        <v>82.03487123480646</v>
       </c>
       <c r="C3" t="n">
-        <v>43.72137195911344</v>
+        <v>43.79042679036201</v>
       </c>
       <c r="D3" t="n">
-        <v>2.191880984263353</v>
+        <v>2.194540242564135</v>
       </c>
       <c r="E3" t="n">
-        <v>4.43226179661159</v>
+        <v>4.455892197081218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7379761477687374</v>
+        <v>0.7380243131481956</v>
       </c>
       <c r="G3" t="n">
-        <v>32.96954313829461</v>
+        <v>33.00954281523553</v>
       </c>
       <c r="H3" t="n">
-        <v>33.94690279736191</v>
+        <v>33.94911840481699</v>
       </c>
       <c r="I3" t="n">
-        <v>3.074900615703072</v>
+        <v>3.075101304784149</v>
       </c>
       <c r="J3" t="n">
-        <v>4.612350923554608</v>
+        <v>4.612651957176222</v>
       </c>
       <c r="K3" t="n">
-        <v>18.03418359644212</v>
+        <v>17.96512876519355</v>
       </c>
       <c r="L3" t="n">
         <v>45.13333333333333</v>
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>81.43817028471045</v>
+        <v>81.57356842190821</v>
       </c>
       <c r="C4" t="n">
-        <v>40.2310854780496</v>
+        <v>40.36379415857309</v>
       </c>
       <c r="D4" t="n">
-        <v>2.164064314977761</v>
+        <v>2.169529187058588</v>
       </c>
       <c r="E4" t="n">
-        <v>4.819375559243527</v>
+        <v>4.864443287017413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7387509638673616</v>
+        <v>0.7387979428647087</v>
       </c>
       <c r="G4" t="n">
-        <v>32.55113407112382</v>
+        <v>32.63333485533958</v>
       </c>
       <c r="H4" t="n">
-        <v>33.98254433789862</v>
+        <v>33.98470537177659</v>
       </c>
       <c r="I4" t="n">
-        <v>2.565107513428339</v>
+        <v>2.565270634946905</v>
       </c>
       <c r="J4" t="n">
-        <v>4.617193524171009</v>
+        <v>4.617487142904429</v>
       </c>
       <c r="K4" t="n">
-        <v>18.56182971528956</v>
+        <v>18.42643157809178</v>
       </c>
       <c r="L4" t="n">
-        <v>41.12167090066908</v>
+        <v>41.12435478264668</v>
       </c>
       <c r="M4" t="n">
-        <v>99.91458609400824</v>
+        <v>99.91458051931156</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>80.89897559872335</v>
+        <v>81.10759820600501</v>
       </c>
       <c r="C5" t="n">
-        <v>40.09039515564598</v>
+        <v>40.29642264456416</v>
       </c>
       <c r="D5" t="n">
-        <v>2.135010754294381</v>
+        <v>2.144198179071253</v>
       </c>
       <c r="E5" t="n">
-        <v>5.137203446483646</v>
+        <v>5.195896369972897</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7394022034512863</v>
+        <v>0.7394475885298136</v>
       </c>
       <c r="G5" t="n">
-        <v>32.11412009584464</v>
+        <v>32.25231427686342</v>
       </c>
       <c r="H5" t="n">
-        <v>34.01250135875916</v>
+        <v>34.01458907237142</v>
       </c>
       <c r="I5" t="n">
-        <v>2.139473968319693</v>
+        <v>2.139605290884877</v>
       </c>
       <c r="J5" t="n">
-        <v>4.621263771570538</v>
+        <v>4.621547428311335</v>
       </c>
       <c r="K5" t="n">
-        <v>19.10102440127665</v>
+        <v>18.89240179399498</v>
       </c>
       <c r="L5" t="n">
-        <v>40.73732745659325</v>
+        <v>40.73991804380344</v>
       </c>
       <c r="M5" t="n">
-        <v>99.92874701351587</v>
+        <v>99.92874248236258</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>80.35979870773939</v>
+        <v>80.65152322028045</v>
       </c>
       <c r="C6" t="n">
-        <v>39.8837087713566</v>
+        <v>40.17294883022461</v>
       </c>
       <c r="D6" t="n">
-        <v>2.10555036978022</v>
+        <v>2.119180382485761</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3967398579239</v>
+        <v>5.467396587641522</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7399494306892456</v>
+        <v>0.7399929018952979</v>
       </c>
       <c r="G6" t="n">
-        <v>31.6709868121108</v>
+        <v>31.87600491988998</v>
       </c>
       <c r="H6" t="n">
-        <v>34.03767381170529</v>
+        <v>34.0396734871837</v>
       </c>
       <c r="I6" t="n">
-        <v>1.784214483722139</v>
+        <v>1.784319304338585</v>
       </c>
       <c r="J6" t="n">
-        <v>4.624683941807784</v>
+        <v>4.624955636845612</v>
       </c>
       <c r="K6" t="n">
-        <v>19.64020129226063</v>
+        <v>19.34847677971955</v>
       </c>
       <c r="L6" t="n">
-        <v>40.41666010392944</v>
+        <v>40.41914090975349</v>
       </c>
       <c r="M6" t="n">
-        <v>99.94057016754667</v>
+        <v>99.94056651969764</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>79.82383544462198</v>
+        <v>80.19848456866467</v>
       </c>
       <c r="C7" t="n">
-        <v>39.6250707745704</v>
+        <v>39.99735826589937</v>
       </c>
       <c r="D7" t="n">
-        <v>2.077126172124138</v>
+        <v>2.094160811762888</v>
       </c>
       <c r="E7" t="n">
-        <v>5.588713898642</v>
+        <v>5.687812593106855</v>
       </c>
       <c r="F7" t="n">
-        <v>0.740409140465899</v>
+        <v>0.7404505165794384</v>
       </c>
       <c r="G7" t="n">
-        <v>31.24343950570057</v>
+        <v>31.49966887693344</v>
       </c>
       <c r="H7" t="n">
-        <v>34.05882046143135</v>
+        <v>34.06072376265416</v>
       </c>
       <c r="I7" t="n">
-        <v>1.487769138346151</v>
+        <v>1.487852279006395</v>
       </c>
       <c r="J7" t="n">
-        <v>4.627557127911868</v>
+        <v>4.62781572862149</v>
       </c>
       <c r="K7" t="n">
-        <v>20.17616455537802</v>
+        <v>19.80151543133532</v>
       </c>
       <c r="L7" t="n">
-        <v>40.14920315661485</v>
+        <v>40.1515618776448</v>
       </c>
       <c r="M7" t="n">
-        <v>99.95043848656329</v>
+        <v>99.95043557487949</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79.27390319245447</v>
+        <v>79.75946071279952</v>
       </c>
       <c r="C8" t="n">
-        <v>39.30639106731319</v>
+        <v>39.78971509237948</v>
       </c>
       <c r="D8" t="n">
-        <v>2.047458850254742</v>
+        <v>2.069763727826232</v>
       </c>
       <c r="E8" t="n">
-        <v>5.7414451683694</v>
+        <v>5.867049555279643</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7407953304793046</v>
+        <v>0.7408343972489131</v>
       </c>
       <c r="G8" t="n">
-        <v>30.7971935392484</v>
+        <v>31.13269607271958</v>
       </c>
       <c r="H8" t="n">
-        <v>34.076585202048</v>
+        <v>34.07838227345</v>
       </c>
       <c r="I8" t="n">
-        <v>1.240454286558978</v>
+        <v>1.240519703469465</v>
       </c>
       <c r="J8" t="n">
-        <v>4.629970815495653</v>
+        <v>4.630214982805707</v>
       </c>
       <c r="K8" t="n">
-        <v>20.72609680754552</v>
+        <v>20.24053928720046</v>
       </c>
       <c r="L8" t="n">
-        <v>39.92618520463168</v>
+        <v>39.92841639044765</v>
       </c>
       <c r="M8" t="n">
-        <v>99.9586730794904</v>
+        <v>99.9586707700276</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78.725483105118</v>
+        <v>79.32268684002479</v>
       </c>
       <c r="C9" t="n">
-        <v>38.950758118593</v>
+        <v>39.54586428355927</v>
       </c>
       <c r="D9" t="n">
-        <v>2.018217993092948</v>
+        <v>2.045697059653397</v>
       </c>
       <c r="E9" t="n">
-        <v>5.851113781621248</v>
+        <v>6.005504326455291</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7411197084044423</v>
+        <v>0.7411563659034621</v>
       </c>
       <c r="G9" t="n">
-        <v>30.35736231277308</v>
+        <v>30.77069327228653</v>
       </c>
       <c r="H9" t="n">
-        <v>34.09150658660434</v>
+        <v>34.09319283155925</v>
       </c>
       <c r="I9" t="n">
-        <v>1.034164545094183</v>
+        <v>1.034215697270233</v>
       </c>
       <c r="J9" t="n">
-        <v>4.631998177527764</v>
+        <v>4.632227286896638</v>
       </c>
       <c r="K9" t="n">
-        <v>21.27451689488199</v>
+        <v>20.67731315997521</v>
       </c>
       <c r="L9" t="n">
-        <v>39.74026792300947</v>
+        <v>39.74236367581359</v>
       </c>
       <c r="M9" t="n">
-        <v>99.96554293648447</v>
+        <v>99.96554111934806</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>78.18863451275563</v>
+        <v>78.88281242495911</v>
       </c>
       <c r="C10" t="n">
-        <v>38.57459916812575</v>
+        <v>39.26681767829832</v>
       </c>
       <c r="D10" t="n">
-        <v>1.988864770740386</v>
+        <v>2.021362978726669</v>
       </c>
       <c r="E10" t="n">
-        <v>5.942679031274047</v>
+        <v>6.113665910104301</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7413920985979934</v>
+        <v>0.7414263848728228</v>
       </c>
       <c r="G10" t="n">
-        <v>29.9158409265533</v>
+        <v>30.404668138347</v>
       </c>
       <c r="H10" t="n">
-        <v>34.10403653550769</v>
+        <v>34.10561370414984</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8621205338447632</v>
+        <v>0.8621604033033335</v>
       </c>
       <c r="J10" t="n">
-        <v>4.633700616237459</v>
+        <v>4.633914905455143</v>
       </c>
       <c r="K10" t="n">
-        <v>21.81136548724437</v>
+        <v>21.11718757504088</v>
       </c>
       <c r="L10" t="n">
-        <v>39.58530855171059</v>
+        <v>39.58726653284775</v>
       </c>
       <c r="M10" t="n">
-        <v>99.97127320708071</v>
+        <v>99.97127178618696</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>77.64789093921749</v>
+        <v>78.45411999026662</v>
       </c>
       <c r="C11" t="n">
-        <v>38.16777221666158</v>
+        <v>38.97217547781712</v>
       </c>
       <c r="D11" t="n">
-        <v>1.959627726224749</v>
+        <v>1.997324713677947</v>
       </c>
       <c r="E11" t="n">
-        <v>6.002231770157953</v>
+        <v>6.202005690833075</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7416208257599725</v>
+        <v>0.7416527817577191</v>
       </c>
       <c r="G11" t="n">
-        <v>29.47606704863059</v>
+        <v>30.04309256823914</v>
       </c>
       <c r="H11" t="n">
-        <v>34.11455798495872</v>
+        <v>34.11602796085507</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7186554224856784</v>
+        <v>0.7186863889179358</v>
       </c>
       <c r="J11" t="n">
-        <v>4.635130160999828</v>
+        <v>4.635329885985745</v>
       </c>
       <c r="K11" t="n">
-        <v>22.35210906078252</v>
+        <v>21.54588000973335</v>
       </c>
       <c r="L11" t="n">
-        <v>39.45617092994911</v>
+        <v>39.45799561235776</v>
       </c>
       <c r="M11" t="n">
-        <v>99.9760522073932</v>
+        <v>99.97605109990825</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.12380641258609</v>
+        <v>78.02459554767842</v>
       </c>
       <c r="C12" t="n">
-        <v>37.75527609726492</v>
+        <v>38.65436886593601</v>
       </c>
       <c r="D12" t="n">
-        <v>1.931227117364436</v>
+        <v>1.973580084022464</v>
       </c>
       <c r="E12" t="n">
-        <v>6.043136655917723</v>
+        <v>6.262905133407048</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7418128358689141</v>
+        <v>0.741842590913077</v>
       </c>
       <c r="G12" t="n">
-        <v>29.04887455702339</v>
+        <v>29.68593376383791</v>
       </c>
       <c r="H12" t="n">
-        <v>34.12339044997004</v>
+        <v>34.12475918200153</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5990345722608922</v>
+        <v>0.5990586002896493</v>
       </c>
       <c r="J12" t="n">
-        <v>4.636330224180713</v>
+        <v>4.636516193206732</v>
       </c>
       <c r="K12" t="n">
-        <v>22.87619358741388</v>
+        <v>21.97540445232159</v>
       </c>
       <c r="L12" t="n">
-        <v>39.34856766469662</v>
+        <v>39.3502631709391</v>
       </c>
       <c r="M12" t="n">
-        <v>99.98003734937542</v>
+        <v>99.98003648919669</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.61021062290001</v>
+        <v>77.61141754605487</v>
       </c>
       <c r="C13" t="n">
-        <v>37.3346546226357</v>
+        <v>38.33428615393052</v>
       </c>
       <c r="D13" t="n">
-        <v>1.903496446116509</v>
+        <v>1.950586437671646</v>
       </c>
       <c r="E13" t="n">
-        <v>6.065536042162863</v>
+        <v>6.309847978342005</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7419739937000566</v>
+        <v>0.742001682084889</v>
       </c>
       <c r="G13" t="n">
-        <v>28.63175904366915</v>
+        <v>29.34007099997769</v>
       </c>
       <c r="H13" t="n">
-        <v>34.13080371020259</v>
+        <v>34.13207737590488</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4993039264234765</v>
+        <v>0.4993225590431916</v>
       </c>
       <c r="J13" t="n">
-        <v>4.637337460625353</v>
+        <v>4.637510513030557</v>
       </c>
       <c r="K13" t="n">
-        <v>23.38978937709998</v>
+        <v>22.38858245394513</v>
       </c>
       <c r="L13" t="n">
-        <v>39.25891615103482</v>
+        <v>39.26049087544964</v>
       </c>
       <c r="M13" t="n">
-        <v>99.98336015077052</v>
+        <v>99.9833594833253</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>76.0868813696237</v>
+        <v>77.19680160075431</v>
       </c>
       <c r="C14" t="n">
-        <v>36.88878403993105</v>
+        <v>37.99724150819834</v>
       </c>
       <c r="D14" t="n">
-        <v>1.875330567887687</v>
+        <v>1.927416104728749</v>
       </c>
       <c r="E14" t="n">
-        <v>6.069972435710014</v>
+        <v>6.342968056666712</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7421092696377947</v>
+        <v>0.7421350226547715</v>
       </c>
       <c r="G14" t="n">
-        <v>28.20809729197729</v>
+        <v>28.99155057529495</v>
       </c>
       <c r="H14" t="n">
-        <v>34.13702640333855</v>
+        <v>34.13821104211948</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4161624658361449</v>
+        <v>0.4161769076973185</v>
       </c>
       <c r="J14" t="n">
-        <v>4.638182935236217</v>
+        <v>4.638343891592322</v>
       </c>
       <c r="K14" t="n">
-        <v>23.91311863037632</v>
+        <v>22.80319839924569</v>
       </c>
       <c r="L14" t="n">
-        <v>39.18422777618084</v>
+        <v>39.18569002147143</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9861304464882</v>
+        <v>99.98612992891546</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>75.58134445823194</v>
+        <v>76.79765252403124</v>
       </c>
       <c r="C15" t="n">
-        <v>36.44777299629827</v>
+        <v>37.66272303091343</v>
       </c>
       <c r="D15" t="n">
-        <v>1.847878057976292</v>
+        <v>1.904871648167056</v>
       </c>
       <c r="E15" t="n">
-        <v>6.068081850263307</v>
+        <v>6.3688305356497</v>
       </c>
       <c r="F15" t="n">
-        <v>0.74222279165003</v>
+        <v>0.7422467542090437</v>
       </c>
       <c r="G15" t="n">
-        <v>27.79516578872672</v>
+        <v>28.65244437451282</v>
       </c>
       <c r="H15" t="n">
-        <v>34.14224841590137</v>
+        <v>34.143350693616</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3468551059015238</v>
+        <v>0.3468663040701032</v>
       </c>
       <c r="J15" t="n">
-        <v>4.638892447812688</v>
+        <v>4.639042213806523</v>
       </c>
       <c r="K15" t="n">
-        <v>24.41865554176808</v>
+        <v>23.20234747596875</v>
       </c>
       <c r="L15" t="n">
-        <v>39.12201139343821</v>
+        <v>39.12336902345957</v>
       </c>
       <c r="M15" t="n">
-        <v>99.98843993150456</v>
+        <v>99.98843953034175</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>75.06515927498978</v>
+        <v>76.40976287905235</v>
       </c>
       <c r="C16" t="n">
-        <v>35.98533762563827</v>
+        <v>37.32867954312499</v>
       </c>
       <c r="D16" t="n">
-        <v>1.820172018453615</v>
+        <v>1.883178359957246</v>
       </c>
       <c r="E16" t="n">
-        <v>6.049046190219318</v>
+        <v>6.381727349646908</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7423180706551478</v>
+        <v>0.7423403623962137</v>
       </c>
       <c r="G16" t="n">
-        <v>27.37842077757311</v>
+        <v>28.32614116435692</v>
       </c>
       <c r="H16" t="n">
-        <v>34.14663125013679</v>
+        <v>34.14765667022582</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2890830263571213</v>
+        <v>0.2890917074929104</v>
       </c>
       <c r="J16" t="n">
-        <v>4.639487941594673</v>
+        <v>4.639627264976336</v>
       </c>
       <c r="K16" t="n">
-        <v>24.93484072501025</v>
+        <v>23.59023712094766</v>
       </c>
       <c r="L16" t="n">
-        <v>39.07018678529866</v>
+        <v>39.07144816081428</v>
       </c>
       <c r="M16" t="n">
-        <v>99.99036513594717</v>
+        <v>99.99036482488692</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>74.5502491509548</v>
+        <v>76.01712606761907</v>
       </c>
       <c r="C17" t="n">
-        <v>35.51519735319363</v>
+        <v>36.98090205096469</v>
       </c>
       <c r="D17" t="n">
-        <v>1.792280087017586</v>
+        <v>1.861525912694992</v>
       </c>
       <c r="E17" t="n">
-        <v>6.025465472688865</v>
+        <v>6.380412092747611</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7423980371034946</v>
+        <v>0.7424187903062807</v>
       </c>
       <c r="G17" t="n">
-        <v>26.95887964222284</v>
+        <v>28.00045227012051</v>
       </c>
       <c r="H17" t="n">
-        <v>34.15030970676074</v>
+        <v>34.1512643540889</v>
       </c>
       <c r="I17" t="n">
-        <v>0.240928473264446</v>
+        <v>0.2409352082465077</v>
       </c>
       <c r="J17" t="n">
-        <v>4.639987731896841</v>
+        <v>4.640117439414254</v>
       </c>
       <c r="K17" t="n">
-        <v>25.44975084904519</v>
+        <v>23.98287393238094</v>
       </c>
       <c r="L17" t="n">
-        <v>39.02702171369572</v>
+        <v>39.02819369144625</v>
       </c>
       <c r="M17" t="n">
-        <v>99.99196991593453</v>
+        <v>99.99196967479187</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>74.04802063684519</v>
+        <v>75.64123372556678</v>
       </c>
       <c r="C18" t="n">
-        <v>35.05025701287656</v>
+        <v>36.64237994718468</v>
       </c>
       <c r="D18" t="n">
-        <v>1.765365750572512</v>
+        <v>1.840262194684102</v>
       </c>
       <c r="E18" t="n">
-        <v>5.991551083738646</v>
+        <v>6.382265116603127</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7424651410777332</v>
+        <v>0.7424844844334804</v>
       </c>
       <c r="G18" t="n">
-        <v>26.55404316486153</v>
+        <v>27.6806105117067</v>
       </c>
       <c r="H18" t="n">
-        <v>34.15339648957571</v>
+        <v>34.15428628394009</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2007918752832414</v>
+        <v>0.2007971064900144</v>
       </c>
       <c r="J18" t="n">
-        <v>4.640407131735832</v>
+        <v>4.640528027709252</v>
       </c>
       <c r="K18" t="n">
-        <v>25.95197936315481</v>
+        <v>24.35876627443323</v>
       </c>
       <c r="L18" t="n">
-        <v>38.99107116637795</v>
+        <v>38.99216113370858</v>
       </c>
       <c r="M18" t="n">
-        <v>99.99330754240933</v>
+        <v>99.99330735532649</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>73.55507952828069</v>
+        <v>75.25696478025006</v>
       </c>
       <c r="C19" t="n">
-        <v>34.58837179214193</v>
+        <v>36.28924184912317</v>
       </c>
       <c r="D19" t="n">
-        <v>1.738320311834127</v>
+        <v>1.818569056826757</v>
       </c>
       <c r="E19" t="n">
-        <v>5.962918318822741</v>
+        <v>6.376513500927838</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7425214451707451</v>
+        <v>0.7425395180207772</v>
       </c>
       <c r="G19" t="n">
-        <v>26.14723469050498</v>
+        <v>27.35430956310248</v>
       </c>
       <c r="H19" t="n">
-        <v>34.15598647785426</v>
+        <v>34.15681782895575</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1673392517766782</v>
+        <v>0.1673433247865845</v>
       </c>
       <c r="J19" t="n">
-        <v>4.640759032317156</v>
+        <v>4.640871987629858</v>
       </c>
       <c r="K19" t="n">
-        <v>26.44492047171931</v>
+        <v>24.74303521974998</v>
       </c>
       <c r="L19" t="n">
-        <v>38.96113018404758</v>
+        <v>38.96214523372435</v>
       </c>
       <c r="M19" t="n">
-        <v>99.99442244790882</v>
+        <v>99.99442230259748</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>73.0721948413771</v>
+        <v>74.86806768629972</v>
       </c>
       <c r="C20" t="n">
-        <v>34.13135164217577</v>
+        <v>35.92627667337013</v>
       </c>
       <c r="D20" t="n">
-        <v>1.712165991281202</v>
+        <v>1.796832549054644</v>
       </c>
       <c r="E20" t="n">
-        <v>5.924958172400697</v>
+        <v>6.361732979147113</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7425686818977972</v>
+        <v>0.7425856238466182</v>
       </c>
       <c r="G20" t="n">
-        <v>25.75383011885474</v>
+        <v>27.02735625869695</v>
       </c>
       <c r="H20" t="n">
-        <v>34.15815936729866</v>
+        <v>34.15893869694443</v>
       </c>
       <c r="I20" t="n">
-        <v>0.139458247782771</v>
+        <v>0.1394614295685831</v>
       </c>
       <c r="J20" t="n">
-        <v>4.641054261861232</v>
+        <v>4.641160149041364</v>
       </c>
       <c r="K20" t="n">
-        <v>26.9278051586229</v>
+        <v>25.13193231370029</v>
       </c>
       <c r="L20" t="n">
-        <v>38.93619488665198</v>
+        <v>38.93714258724109</v>
       </c>
       <c r="M20" t="n">
-        <v>99.99535168745064</v>
+        <v>99.9953515743115</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>72.57571011473732</v>
+        <v>74.49165185037137</v>
       </c>
       <c r="C21" t="n">
-        <v>33.65640743887558</v>
+        <v>35.57146121781261</v>
       </c>
       <c r="D21" t="n">
-        <v>1.685741384617522</v>
+        <v>1.776192973743925</v>
       </c>
       <c r="E21" t="n">
-        <v>5.873494299312406</v>
+        <v>6.337591338804456</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7426083197596854</v>
+        <v>0.7426242439231703</v>
       </c>
       <c r="G21" t="n">
-        <v>25.35635999362189</v>
+        <v>26.71690264673155</v>
       </c>
       <c r="H21" t="n">
-        <v>34.15998270894552</v>
+        <v>34.16071522046582</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1162214099822567</v>
+        <v>0.1162239021826317</v>
       </c>
       <c r="J21" t="n">
-        <v>4.641301998498033</v>
+        <v>4.641401524519814</v>
       </c>
       <c r="K21" t="n">
-        <v>27.4242898852627</v>
+        <v>25.50834814962864</v>
       </c>
       <c r="L21" t="n">
-        <v>38.91542883564553</v>
+        <v>38.91631670395962</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9961261597838</v>
+        <v>99.99612607140085</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,34 +541,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>82.03487123480646</v>
+        <v>82.23116778099779</v>
       </c>
       <c r="C3" t="n">
-        <v>43.79042679036201</v>
+        <v>43.98672333655336</v>
       </c>
       <c r="D3" t="n">
-        <v>2.194540242564135</v>
+        <v>2.200579461364371</v>
       </c>
       <c r="E3" t="n">
-        <v>4.455892197081218</v>
+        <v>4.547471765913351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7380243131481956</v>
+        <v>0.7381608212893642</v>
       </c>
       <c r="G3" t="n">
-        <v>33.00954281523553</v>
+        <v>33.10038273135575</v>
       </c>
       <c r="H3" t="n">
-        <v>33.94911840481699</v>
+        <v>33.95539777931075</v>
       </c>
       <c r="I3" t="n">
-        <v>3.075101304784149</v>
+        <v>3.075670088705684</v>
       </c>
       <c r="J3" t="n">
-        <v>4.612651957176222</v>
+        <v>4.613505133058526</v>
       </c>
       <c r="K3" t="n">
-        <v>17.96512876519355</v>
+        <v>17.7688322190022</v>
       </c>
       <c r="L3" t="n">
         <v>45.13333333333333</v>
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>81.57356842190821</v>
+        <v>81.97344194586313</v>
       </c>
       <c r="C4" t="n">
-        <v>40.36379415857309</v>
+        <v>40.75604534599727</v>
       </c>
       <c r="D4" t="n">
-        <v>2.169529187058588</v>
+        <v>2.185386767735193</v>
       </c>
       <c r="E4" t="n">
-        <v>4.864443287017413</v>
+        <v>5.002389862101044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7387979428647087</v>
+        <v>0.7389309582019394</v>
       </c>
       <c r="G4" t="n">
-        <v>32.63333485533958</v>
+        <v>32.87185929801688</v>
       </c>
       <c r="H4" t="n">
-        <v>33.98470537177659</v>
+        <v>33.99082407728921</v>
       </c>
       <c r="I4" t="n">
-        <v>2.565270634946905</v>
+        <v>2.565732493756734</v>
       </c>
       <c r="J4" t="n">
-        <v>4.617487142904429</v>
+        <v>4.618318488762121</v>
       </c>
       <c r="K4" t="n">
-        <v>18.42643157809178</v>
+        <v>18.02655805413688</v>
       </c>
       <c r="L4" t="n">
-        <v>41.12435478264668</v>
+        <v>41.13196131962401</v>
       </c>
       <c r="M4" t="n">
-        <v>99.91458051931156</v>
+        <v>99.91456471975816</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>81.10759820600501</v>
+        <v>81.71958678328421</v>
       </c>
       <c r="C5" t="n">
-        <v>40.29642264456416</v>
+        <v>40.90106345872015</v>
       </c>
       <c r="D5" t="n">
-        <v>2.144198179071253</v>
+        <v>2.169843567307566</v>
       </c>
       <c r="E5" t="n">
-        <v>5.195896369972897</v>
+        <v>5.389282570032488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7394475885298136</v>
+        <v>0.7395759667965413</v>
       </c>
       <c r="G5" t="n">
-        <v>32.25231427686342</v>
+        <v>32.6380636582513</v>
       </c>
       <c r="H5" t="n">
-        <v>34.01458907237142</v>
+        <v>34.02049447264089</v>
       </c>
       <c r="I5" t="n">
-        <v>2.139605290884877</v>
+        <v>2.139976755777029</v>
       </c>
       <c r="J5" t="n">
-        <v>4.621547428311335</v>
+        <v>4.622349792478382</v>
       </c>
       <c r="K5" t="n">
-        <v>18.89240179399498</v>
+        <v>18.28041321671578</v>
       </c>
       <c r="L5" t="n">
-        <v>40.73991804380344</v>
+        <v>40.74725297751528</v>
       </c>
       <c r="M5" t="n">
-        <v>99.92874248236258</v>
+        <v>99.92872965295122</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>80.65152322028045</v>
+        <v>81.47943927661859</v>
       </c>
       <c r="C6" t="n">
-        <v>40.17294883022461</v>
+        <v>40.9938372495802</v>
       </c>
       <c r="D6" t="n">
-        <v>2.119180382485761</v>
+        <v>2.154875631050424</v>
       </c>
       <c r="E6" t="n">
-        <v>5.467396587641522</v>
+        <v>5.715853872810049</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7399929018952979</v>
+        <v>0.740115922672104</v>
       </c>
       <c r="G6" t="n">
-        <v>31.87600491988998</v>
+        <v>32.41292095038346</v>
       </c>
       <c r="H6" t="n">
-        <v>34.0396734871837</v>
+        <v>34.04533244291678</v>
       </c>
       <c r="I6" t="n">
-        <v>1.784319304338585</v>
+        <v>1.784615940085127</v>
       </c>
       <c r="J6" t="n">
-        <v>4.624955636845612</v>
+        <v>4.625724516700649</v>
       </c>
       <c r="K6" t="n">
-        <v>19.34847677971955</v>
+        <v>18.5205607233814</v>
       </c>
       <c r="L6" t="n">
-        <v>40.41914090975349</v>
+        <v>40.42615822826679</v>
       </c>
       <c r="M6" t="n">
-        <v>99.94056651969764</v>
+        <v>99.94055620122839</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80.19848456866467</v>
+        <v>81.26267126808534</v>
       </c>
       <c r="C7" t="n">
-        <v>39.99735826589937</v>
+        <v>41.05486169339459</v>
       </c>
       <c r="D7" t="n">
-        <v>2.094160811762888</v>
+        <v>2.14067702688588</v>
       </c>
       <c r="E7" t="n">
-        <v>5.687812593106855</v>
+        <v>5.999326679372833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7404505165794384</v>
+        <v>0.740567691159314</v>
       </c>
       <c r="G7" t="n">
-        <v>31.49966887693344</v>
+        <v>32.19935027940845</v>
       </c>
       <c r="H7" t="n">
-        <v>34.06072376265416</v>
+        <v>34.06611379332844</v>
       </c>
       <c r="I7" t="n">
-        <v>1.487852279006395</v>
+        <v>1.488087728184707</v>
       </c>
       <c r="J7" t="n">
-        <v>4.62781572862149</v>
+        <v>4.628548069745712</v>
       </c>
       <c r="K7" t="n">
-        <v>19.80151543133532</v>
+        <v>18.73732873191467</v>
       </c>
       <c r="L7" t="n">
-        <v>40.1515618776448</v>
+        <v>40.15823690968837</v>
       </c>
       <c r="M7" t="n">
-        <v>99.95043557487949</v>
+        <v>99.95042733499763</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79.75946071279952</v>
+        <v>81.03700535676896</v>
       </c>
       <c r="C8" t="n">
-        <v>39.78971509237948</v>
+        <v>41.06093461664685</v>
       </c>
       <c r="D8" t="n">
-        <v>2.069763727826232</v>
+        <v>2.126387446203829</v>
       </c>
       <c r="E8" t="n">
-        <v>5.867049555279643</v>
+        <v>6.230145624498614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7408343972489131</v>
+        <v>0.7409456364997974</v>
       </c>
       <c r="G8" t="n">
-        <v>31.13269607271958</v>
+        <v>31.98441116998259</v>
       </c>
       <c r="H8" t="n">
-        <v>34.07838227345</v>
+        <v>34.08349927899068</v>
       </c>
       <c r="I8" t="n">
-        <v>1.240519703469465</v>
+        <v>1.240705972469707</v>
       </c>
       <c r="J8" t="n">
-        <v>4.630214982805707</v>
+        <v>4.630910228123733</v>
       </c>
       <c r="K8" t="n">
-        <v>20.24053928720046</v>
+        <v>18.96299464323106</v>
       </c>
       <c r="L8" t="n">
-        <v>39.92841639044765</v>
+        <v>39.93473496989474</v>
       </c>
       <c r="M8" t="n">
-        <v>99.9586707700276</v>
+        <v>99.95866422977265</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79.32268684002479</v>
+        <v>80.84084775774119</v>
       </c>
       <c r="C9" t="n">
-        <v>39.54586428355927</v>
+        <v>41.05805255211121</v>
       </c>
       <c r="D9" t="n">
-        <v>2.045697059653397</v>
+        <v>2.113177696621558</v>
       </c>
       <c r="E9" t="n">
-        <v>6.005504326455291</v>
+        <v>6.435410011003407</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7411563659034621</v>
+        <v>0.7412616510254223</v>
       </c>
       <c r="G9" t="n">
-        <v>30.77069327228653</v>
+        <v>31.78571452001594</v>
       </c>
       <c r="H9" t="n">
-        <v>34.09319283155925</v>
+        <v>34.09803594716942</v>
       </c>
       <c r="I9" t="n">
-        <v>1.034215697270233</v>
+        <v>1.034362612996562</v>
       </c>
       <c r="J9" t="n">
-        <v>4.632227286896638</v>
+        <v>4.632885318908889</v>
       </c>
       <c r="K9" t="n">
-        <v>20.67731315997521</v>
+        <v>19.15915224225881</v>
       </c>
       <c r="L9" t="n">
-        <v>39.74236367581359</v>
+        <v>39.74833115083916</v>
       </c>
       <c r="M9" t="n">
-        <v>99.96554111934806</v>
+        <v>99.96553594520918</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>78.88281242495911</v>
+        <v>80.63848753532272</v>
       </c>
       <c r="C10" t="n">
-        <v>39.26681767829832</v>
+        <v>41.01686513027516</v>
       </c>
       <c r="D10" t="n">
-        <v>2.021362978726669</v>
+        <v>2.099769714816842</v>
       </c>
       <c r="E10" t="n">
-        <v>6.113665910104301</v>
+        <v>6.606153350413591</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7414263848728228</v>
+        <v>0.7415258640629349</v>
       </c>
       <c r="G10" t="n">
-        <v>30.404668138347</v>
+        <v>31.58403612703667</v>
       </c>
       <c r="H10" t="n">
-        <v>34.10561370414984</v>
+        <v>34.110189746895</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8621604033033335</v>
+        <v>0.8622760817043416</v>
       </c>
       <c r="J10" t="n">
-        <v>4.633914905455143</v>
+        <v>4.634536650393342</v>
       </c>
       <c r="K10" t="n">
-        <v>21.11718757504088</v>
+        <v>19.36151246467728</v>
       </c>
       <c r="L10" t="n">
-        <v>39.58726653284775</v>
+        <v>39.59289011024212</v>
       </c>
       <c r="M10" t="n">
-        <v>99.97127178618696</v>
+        <v>99.97126770519455</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>78.45411999026662</v>
+        <v>80.44852944387729</v>
       </c>
       <c r="C11" t="n">
-        <v>38.97217547781712</v>
+        <v>40.96128753178797</v>
       </c>
       <c r="D11" t="n">
-        <v>1.997324713677947</v>
+        <v>2.086926018925468</v>
       </c>
       <c r="E11" t="n">
-        <v>6.202005690833075</v>
+        <v>6.753968396435039</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7416527817577191</v>
+        <v>0.7417467059020877</v>
       </c>
       <c r="G11" t="n">
-        <v>30.04309256823914</v>
+        <v>31.39084553467058</v>
       </c>
       <c r="H11" t="n">
-        <v>34.11602796085507</v>
+        <v>34.12034847149602</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7186863889179358</v>
+        <v>0.7187774045600377</v>
       </c>
       <c r="J11" t="n">
-        <v>4.635329885985745</v>
+        <v>4.635916911888047</v>
       </c>
       <c r="K11" t="n">
-        <v>21.54588000973335</v>
+        <v>19.55147055612272</v>
       </c>
       <c r="L11" t="n">
-        <v>39.45799561235776</v>
+        <v>39.46328979870862</v>
       </c>
       <c r="M11" t="n">
-        <v>99.97605109990825</v>
+        <v>99.97604788661931</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.02459554767842</v>
+        <v>80.26927493835831</v>
       </c>
       <c r="C12" t="n">
-        <v>38.65436886593601</v>
+        <v>40.89406234549197</v>
       </c>
       <c r="D12" t="n">
-        <v>1.973580084022464</v>
+        <v>2.074496041542535</v>
       </c>
       <c r="E12" t="n">
-        <v>6.262905133407048</v>
+        <v>6.883931541460681</v>
       </c>
       <c r="F12" t="n">
-        <v>0.741842590913077</v>
+        <v>0.7419312525838327</v>
       </c>
       <c r="G12" t="n">
-        <v>29.68593376383791</v>
+        <v>31.20387795820228</v>
       </c>
       <c r="H12" t="n">
-        <v>34.12475918200153</v>
+        <v>34.12883761885629</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5990586002896493</v>
+        <v>0.5991301970637262</v>
       </c>
       <c r="J12" t="n">
-        <v>4.636516193206732</v>
+        <v>4.637070328648953</v>
       </c>
       <c r="K12" t="n">
-        <v>21.97540445232159</v>
+        <v>19.73072506164171</v>
       </c>
       <c r="L12" t="n">
-        <v>39.3502631709391</v>
+        <v>39.35524655385077</v>
       </c>
       <c r="M12" t="n">
-        <v>99.98003648919669</v>
+        <v>99.98003396098444</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.61141754605487</v>
+        <v>80.09577183928748</v>
       </c>
       <c r="C13" t="n">
-        <v>38.33428615393052</v>
+        <v>40.81394622208849</v>
       </c>
       <c r="D13" t="n">
-        <v>1.950586437671646</v>
+        <v>2.063017008572103</v>
       </c>
       <c r="E13" t="n">
-        <v>6.309847978342005</v>
+        <v>6.986111787072792</v>
       </c>
       <c r="F13" t="n">
-        <v>0.742001682084889</v>
+        <v>0.7420854450061926</v>
       </c>
       <c r="G13" t="n">
-        <v>29.34007099997769</v>
+        <v>31.03121417060537</v>
       </c>
       <c r="H13" t="n">
-        <v>34.13207737590488</v>
+        <v>34.13593047028485</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4993225590431916</v>
+        <v>0.4993789264574819</v>
       </c>
       <c r="J13" t="n">
-        <v>4.637510513030557</v>
+        <v>4.638034031288702</v>
       </c>
       <c r="K13" t="n">
-        <v>22.38858245394513</v>
+        <v>19.90422816071251</v>
       </c>
       <c r="L13" t="n">
-        <v>39.26049087544964</v>
+        <v>39.26518311172502</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9833594833253</v>
+        <v>99.98335749452602</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>77.19680160075431</v>
+        <v>79.93222225138422</v>
       </c>
       <c r="C14" t="n">
-        <v>37.99724150819834</v>
+        <v>40.7282370075834</v>
       </c>
       <c r="D14" t="n">
-        <v>1.927416104728749</v>
+        <v>2.051717493944456</v>
       </c>
       <c r="E14" t="n">
-        <v>6.342968056666712</v>
+        <v>7.080123931313675</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7421350226547715</v>
+        <v>0.742214250715053</v>
       </c>
       <c r="G14" t="n">
-        <v>28.99155057529495</v>
+        <v>30.86125063808118</v>
       </c>
       <c r="H14" t="n">
-        <v>34.13821104211948</v>
+        <v>34.14185553289243</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4161769076973185</v>
+        <v>0.4162213374683496</v>
       </c>
       <c r="J14" t="n">
-        <v>4.638343891592322</v>
+        <v>4.638839066969079</v>
       </c>
       <c r="K14" t="n">
-        <v>22.80319839924569</v>
+        <v>20.06777774861578</v>
       </c>
       <c r="L14" t="n">
-        <v>39.18569002147143</v>
+        <v>39.19011360695479</v>
       </c>
       <c r="M14" t="n">
-        <v>99.98612992891546</v>
+        <v>99.98612836315397</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>76.79765252403124</v>
+        <v>79.78626818779027</v>
       </c>
       <c r="C15" t="n">
-        <v>37.66272303091343</v>
+        <v>40.64716076955325</v>
       </c>
       <c r="D15" t="n">
-        <v>1.904871648167056</v>
+        <v>2.041273483703298</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3688305356497</v>
+        <v>7.165301119457578</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7422467542090437</v>
+        <v>0.7423218194133898</v>
       </c>
       <c r="G15" t="n">
-        <v>28.65244437451282</v>
+        <v>30.70415531737043</v>
       </c>
       <c r="H15" t="n">
-        <v>34.143350693616</v>
+        <v>34.14680369301593</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3468663040701032</v>
+        <v>0.3469013834959788</v>
       </c>
       <c r="J15" t="n">
-        <v>4.639042213806523</v>
+        <v>4.639511371333684</v>
       </c>
       <c r="K15" t="n">
-        <v>23.20234747596875</v>
+        <v>20.21373181220972</v>
       </c>
       <c r="L15" t="n">
-        <v>39.12336902345957</v>
+        <v>39.12754571441846</v>
       </c>
       <c r="M15" t="n">
-        <v>99.98843953034175</v>
+        <v>99.98843829618144</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>76.40976287905235</v>
+        <v>79.6437837391434</v>
       </c>
       <c r="C16" t="n">
-        <v>37.32867954312499</v>
+        <v>40.5587480390056</v>
       </c>
       <c r="D16" t="n">
-        <v>1.883178359957246</v>
+        <v>2.031197314822127</v>
       </c>
       <c r="E16" t="n">
-        <v>6.381727349646908</v>
+        <v>7.237453957398032</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7423403623962137</v>
+        <v>0.7424116442470362</v>
       </c>
       <c r="G16" t="n">
-        <v>28.32614116435692</v>
+        <v>30.55259294378282</v>
       </c>
       <c r="H16" t="n">
-        <v>34.14765667022582</v>
+        <v>34.15093563536366</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2890917074929104</v>
+        <v>0.2891194669857406</v>
       </c>
       <c r="J16" t="n">
-        <v>4.639627264976336</v>
+        <v>4.640072776543975</v>
       </c>
       <c r="K16" t="n">
-        <v>23.59023712094766</v>
+        <v>20.35621626085659</v>
       </c>
       <c r="L16" t="n">
-        <v>39.07144816081428</v>
+        <v>39.07539955059626</v>
       </c>
       <c r="M16" t="n">
-        <v>99.99036482488692</v>
+        <v>99.99036385045846</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>76.01712606761907</v>
+        <v>79.51310232892703</v>
       </c>
       <c r="C17" t="n">
-        <v>36.98090205096469</v>
+        <v>40.47312993155946</v>
       </c>
       <c r="D17" t="n">
-        <v>1.861525912694992</v>
+        <v>2.02174058904022</v>
       </c>
       <c r="E17" t="n">
-        <v>6.380412092747611</v>
+        <v>7.302643015763752</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7424187903062807</v>
+        <v>0.7424866379464391</v>
       </c>
       <c r="G17" t="n">
-        <v>28.00045227012051</v>
+        <v>30.4103480268133</v>
       </c>
       <c r="H17" t="n">
-        <v>34.1512643540889</v>
+        <v>34.15438534553619</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2409352082465077</v>
+        <v>0.2409572266618873</v>
       </c>
       <c r="J17" t="n">
-        <v>4.640117439414254</v>
+        <v>4.640541487165243</v>
       </c>
       <c r="K17" t="n">
-        <v>23.98287393238094</v>
+        <v>20.48689767107296</v>
       </c>
       <c r="L17" t="n">
-        <v>39.02819369144625</v>
+        <v>39.03194130106242</v>
       </c>
       <c r="M17" t="n">
-        <v>99.99196967479187</v>
+        <v>99.99196890369484</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>75.64123372556678</v>
+        <v>79.3990298450244</v>
       </c>
       <c r="C18" t="n">
-        <v>36.64237994718468</v>
+        <v>40.3966120671419</v>
       </c>
       <c r="D18" t="n">
-        <v>1.840262194684102</v>
+        <v>2.012871858185003</v>
       </c>
       <c r="E18" t="n">
-        <v>6.382265116603127</v>
+        <v>7.367649121156843</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7424844844334804</v>
+        <v>0.7425492340807486</v>
       </c>
       <c r="G18" t="n">
-        <v>27.6806105117067</v>
+        <v>30.27694753353275</v>
       </c>
       <c r="H18" t="n">
-        <v>34.15428628394009</v>
+        <v>34.15726476771443</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2007971064900144</v>
+        <v>0.2008146173499586</v>
       </c>
       <c r="J18" t="n">
-        <v>4.640528027709252</v>
+        <v>4.640932713004678</v>
       </c>
       <c r="K18" t="n">
-        <v>24.35876627443323</v>
+        <v>20.60097015497558</v>
       </c>
       <c r="L18" t="n">
-        <v>38.99216113370858</v>
+        <v>38.99572452158634</v>
       </c>
       <c r="M18" t="n">
-        <v>99.99330735532649</v>
+        <v>99.99330674370383</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>75.25696478025006</v>
+        <v>79.31138589658133</v>
       </c>
       <c r="C19" t="n">
-        <v>36.28924184912317</v>
+        <v>40.34026471758865</v>
       </c>
       <c r="D19" t="n">
-        <v>1.818569056826757</v>
+        <v>2.00490447597341</v>
       </c>
       <c r="E19" t="n">
-        <v>6.376513500927838</v>
+        <v>7.43849139152185</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7425395180207772</v>
+        <v>0.7426014632457877</v>
       </c>
       <c r="G19" t="n">
-        <v>27.35430956310248</v>
+        <v>30.15710482610005</v>
       </c>
       <c r="H19" t="n">
-        <v>34.15681782895575</v>
+        <v>34.15966730930623</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1673433247865845</v>
+        <v>0.1673572851478263</v>
       </c>
       <c r="J19" t="n">
-        <v>4.640871987629858</v>
+        <v>4.641259145286172</v>
       </c>
       <c r="K19" t="n">
-        <v>24.74303521974998</v>
+        <v>20.68861410341867</v>
       </c>
       <c r="L19" t="n">
-        <v>38.96214523372435</v>
+        <v>38.96554299517741</v>
       </c>
       <c r="M19" t="n">
-        <v>99.99442230259748</v>
+        <v>99.99442181618471</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.86806768629972</v>
+        <v>79.22702628120207</v>
       </c>
       <c r="C20" t="n">
-        <v>35.92627667337013</v>
+        <v>40.28198660884348</v>
       </c>
       <c r="D20" t="n">
-        <v>1.796832549054644</v>
+        <v>1.997210077509674</v>
       </c>
       <c r="E20" t="n">
-        <v>6.361732979147113</v>
+        <v>7.503127012143405</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7425856238466182</v>
+        <v>0.7426450395155266</v>
       </c>
       <c r="G20" t="n">
-        <v>27.02735625869695</v>
+        <v>30.04136824920802</v>
       </c>
       <c r="H20" t="n">
-        <v>34.15893869694443</v>
+        <v>34.16167181771422</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1394614295685831</v>
+        <v>0.1394725881392026</v>
       </c>
       <c r="J20" t="n">
-        <v>4.641160149041364</v>
+        <v>4.64153149697204</v>
       </c>
       <c r="K20" t="n">
-        <v>25.13193231370029</v>
+        <v>20.77297371879792</v>
       </c>
       <c r="L20" t="n">
-        <v>38.93714258724109</v>
+        <v>38.94039085888225</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9953515743115</v>
+        <v>99.99535118652366</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>74.49165185037137</v>
+        <v>79.13943242460755</v>
       </c>
       <c r="C21" t="n">
-        <v>35.57146121781261</v>
+        <v>40.21612771457921</v>
       </c>
       <c r="D21" t="n">
-        <v>1.776192973743925</v>
+        <v>1.98939484746213</v>
       </c>
       <c r="E21" t="n">
-        <v>6.337591338804456</v>
+        <v>7.562206166503123</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7426242439231703</v>
+        <v>0.7426813971796916</v>
       </c>
       <c r="G21" t="n">
-        <v>26.71690264673155</v>
+        <v>29.92381416390954</v>
       </c>
       <c r="H21" t="n">
-        <v>34.16071522046582</v>
+        <v>34.16334427026581</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1162239021826317</v>
+        <v>0.1162328469141695</v>
       </c>
       <c r="J21" t="n">
-        <v>4.641401524519814</v>
+        <v>4.641758732373071</v>
       </c>
       <c r="K21" t="n">
-        <v>25.50834814962864</v>
+        <v>20.86056757539244</v>
       </c>
       <c r="L21" t="n">
-        <v>38.91631670395962</v>
+        <v>38.91943047146894</v>
       </c>
       <c r="M21" t="n">
-        <v>99.99612607140085</v>
+        <v>99.9961257614406</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -527,13 +527,13 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>17.9</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
         <v>45.8</v>
       </c>
       <c r="M2" t="n">
-        <v>107</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>82.23116778099779</v>
+        <v>89.90883074992746</v>
       </c>
       <c r="C3" t="n">
-        <v>43.98672333655336</v>
+        <v>41.76438630548301</v>
       </c>
       <c r="D3" t="n">
-        <v>2.200579461364371</v>
+        <v>2.360981399746533</v>
       </c>
       <c r="E3" t="n">
-        <v>4.547471765913351</v>
+        <v>4.509775227223538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7381608212893642</v>
+        <v>0.8277209678102171</v>
       </c>
       <c r="G3" t="n">
-        <v>33.10038273135575</v>
+        <v>35.51309522118743</v>
       </c>
       <c r="H3" t="n">
-        <v>33.95539777931075</v>
+        <v>38.07516451926998</v>
       </c>
       <c r="I3" t="n">
-        <v>3.075670088705684</v>
+        <v>3.448837365875905</v>
       </c>
       <c r="J3" t="n">
-        <v>4.613505133058526</v>
+        <v>5.173256048813856</v>
       </c>
       <c r="K3" t="n">
-        <v>17.7688322190022</v>
+        <v>10.09116925007255</v>
       </c>
       <c r="L3" t="n">
         <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.8888888888889</v>
+        <v>96.98888888888888</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>81.97344194586313</v>
+        <v>86.17112146556322</v>
       </c>
       <c r="C4" t="n">
-        <v>40.75604534599727</v>
+        <v>39.95286872130846</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185386767735193</v>
+        <v>2.155169296878001</v>
       </c>
       <c r="E4" t="n">
-        <v>5.002389862101044</v>
+        <v>4.596186211426148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7389309582019394</v>
+        <v>0.8286422136150284</v>
       </c>
       <c r="G4" t="n">
-        <v>32.87185929801688</v>
+        <v>32.41733817387328</v>
       </c>
       <c r="H4" t="n">
-        <v>33.99082407728921</v>
+        <v>38.11754182629131</v>
       </c>
       <c r="I4" t="n">
-        <v>2.565732493756734</v>
+        <v>2.877229908385516</v>
       </c>
       <c r="J4" t="n">
-        <v>4.618318488762121</v>
+        <v>5.179013835093928</v>
       </c>
       <c r="K4" t="n">
-        <v>18.02655805413688</v>
+        <v>13.8288785344368</v>
       </c>
       <c r="L4" t="n">
-        <v>41.13196131962401</v>
+        <v>46.12245170631376</v>
       </c>
       <c r="M4" t="n">
-        <v>99.91456471975816</v>
+        <v>99.90419896205901</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>81.71958678328421</v>
+        <v>80.85035438711353</v>
       </c>
       <c r="C5" t="n">
-        <v>40.90106345872015</v>
+        <v>35.07618408239633</v>
       </c>
       <c r="D5" t="n">
-        <v>2.169843567307566</v>
+        <v>1.864248919614553</v>
       </c>
       <c r="E5" t="n">
-        <v>5.389282570032488</v>
+        <v>4.375770360869232</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7395759667965413</v>
+        <v>0.8294621623818205</v>
       </c>
       <c r="G5" t="n">
-        <v>32.6380636582513</v>
+        <v>28.04141083253559</v>
       </c>
       <c r="H5" t="n">
-        <v>34.02049447264089</v>
+        <v>38.15525946956374</v>
       </c>
       <c r="I5" t="n">
-        <v>2.139976755777029</v>
+        <v>2.400064127262213</v>
       </c>
       <c r="J5" t="n">
-        <v>4.622349792478382</v>
+        <v>5.184138514886378</v>
       </c>
       <c r="K5" t="n">
-        <v>18.28041321671578</v>
+        <v>19.14964561288648</v>
       </c>
       <c r="L5" t="n">
-        <v>40.74725297751528</v>
+        <v>45.6942472517065</v>
       </c>
       <c r="M5" t="n">
-        <v>99.92872965295122</v>
+        <v>99.9200769469893</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>81.47943927661859</v>
+        <v>73.23296383832343</v>
       </c>
       <c r="C6" t="n">
-        <v>40.9938372495802</v>
+        <v>27.82684396650863</v>
       </c>
       <c r="D6" t="n">
-        <v>2.154875631050424</v>
+        <v>1.451330957440093</v>
       </c>
       <c r="E6" t="n">
-        <v>5.715853872810049</v>
+        <v>3.740214125107397</v>
       </c>
       <c r="F6" t="n">
-        <v>0.740115922672104</v>
+        <v>0.8302179605909371</v>
       </c>
       <c r="G6" t="n">
-        <v>32.41292095038346</v>
+        <v>21.83043648482808</v>
       </c>
       <c r="H6" t="n">
-        <v>34.04533244291678</v>
+        <v>38.19002618718311</v>
       </c>
       <c r="I6" t="n">
-        <v>1.784615940085127</v>
+        <v>2.001875869480463</v>
       </c>
       <c r="J6" t="n">
-        <v>4.625724516700649</v>
+        <v>5.188862253693357</v>
       </c>
       <c r="K6" t="n">
-        <v>18.5205607233814</v>
+        <v>26.76703616167657</v>
       </c>
       <c r="L6" t="n">
-        <v>40.42615822826679</v>
+        <v>45.33945142383529</v>
       </c>
       <c r="M6" t="n">
-        <v>99.94055620122839</v>
+        <v>99.93333155202049</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.26267126808534</v>
+        <v>65.59803331346066</v>
       </c>
       <c r="C7" t="n">
-        <v>41.05486169339459</v>
+        <v>20.49530731830937</v>
       </c>
       <c r="D7" t="n">
-        <v>2.14067702688588</v>
+        <v>1.042147829386426</v>
       </c>
       <c r="E7" t="n">
-        <v>5.999326679372833</v>
+        <v>2.963985563910998</v>
       </c>
       <c r="F7" t="n">
-        <v>0.740567691159314</v>
+        <v>0.8309223361178585</v>
       </c>
       <c r="G7" t="n">
-        <v>32.19935027940845</v>
+        <v>15.67564026702082</v>
       </c>
       <c r="H7" t="n">
-        <v>34.06611379332844</v>
+        <v>38.2224274614215</v>
       </c>
       <c r="I7" t="n">
-        <v>1.488087728184707</v>
+        <v>1.669645254866454</v>
       </c>
       <c r="J7" t="n">
-        <v>4.628548069745712</v>
+        <v>5.193264600736616</v>
       </c>
       <c r="K7" t="n">
-        <v>18.73732873191467</v>
+        <v>34.40196668653932</v>
       </c>
       <c r="L7" t="n">
-        <v>40.15823690968837</v>
+        <v>45.04711833211019</v>
       </c>
       <c r="M7" t="n">
-        <v>99.95042733499763</v>
+        <v>99.94439233695888</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81.03700535676896</v>
+        <v>58.25334238541407</v>
       </c>
       <c r="C8" t="n">
-        <v>41.06093461664685</v>
+        <v>13.39990024267652</v>
       </c>
       <c r="D8" t="n">
-        <v>2.126387446203829</v>
+        <v>0.6537677274740138</v>
       </c>
       <c r="E8" t="n">
-        <v>6.230145624498614</v>
+        <v>2.091468847525101</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7409456364997974</v>
+        <v>0.8315844111304048</v>
       </c>
       <c r="G8" t="n">
-        <v>31.98441116998259</v>
+        <v>9.833756234088291</v>
       </c>
       <c r="H8" t="n">
-        <v>34.08349927899068</v>
+        <v>38.25288291199863</v>
       </c>
       <c r="I8" t="n">
-        <v>1.240705972469707</v>
+        <v>1.392479683632607</v>
       </c>
       <c r="J8" t="n">
-        <v>4.630910228123733</v>
+        <v>5.197402569565031</v>
       </c>
       <c r="K8" t="n">
-        <v>18.96299464323106</v>
+        <v>41.74665761458592</v>
       </c>
       <c r="L8" t="n">
-        <v>39.93473496989474</v>
+        <v>44.80706310788016</v>
       </c>
       <c r="M8" t="n">
-        <v>99.95866422977265</v>
+        <v>99.95362096514259</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80.84084775774119</v>
+        <v>52.67427197719729</v>
       </c>
       <c r="C9" t="n">
-        <v>41.05805255211121</v>
+        <v>8.024906768061111</v>
       </c>
       <c r="D9" t="n">
-        <v>2.113177696621558</v>
+        <v>0.3640741674948693</v>
       </c>
       <c r="E9" t="n">
-        <v>6.435410011003407</v>
+        <v>1.358252032245242</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7412616510254223</v>
+        <v>0.8321955124118939</v>
       </c>
       <c r="G9" t="n">
-        <v>31.78571452001594</v>
+        <v>5.476282269401993</v>
       </c>
       <c r="H9" t="n">
-        <v>34.09803594716942</v>
+        <v>38.28099357094712</v>
       </c>
       <c r="I9" t="n">
-        <v>1.034362612996562</v>
+        <v>1.161252472121829</v>
       </c>
       <c r="J9" t="n">
-        <v>4.632885318908889</v>
+        <v>5.201221952574338</v>
       </c>
       <c r="K9" t="n">
-        <v>19.15915224225881</v>
+        <v>47.32572802280271</v>
       </c>
       <c r="L9" t="n">
-        <v>39.74833115083916</v>
+        <v>44.61068521792416</v>
       </c>
       <c r="M9" t="n">
-        <v>99.96553594520918</v>
+        <v>99.96132000878798</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>80.63848753532272</v>
+        <v>49.30332726796919</v>
       </c>
       <c r="C10" t="n">
-        <v>41.01686513027516</v>
+        <v>4.821144337898365</v>
       </c>
       <c r="D10" t="n">
-        <v>2.099769714816842</v>
+        <v>0.1937132490111442</v>
       </c>
       <c r="E10" t="n">
-        <v>6.606153350413591</v>
+        <v>0.8840769594764873</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7415258640629349</v>
+        <v>0.8327403380351014</v>
       </c>
       <c r="G10" t="n">
-        <v>31.58403612703667</v>
+        <v>2.913770120542627</v>
       </c>
       <c r="H10" t="n">
-        <v>34.110189746895</v>
+        <v>38.30605554961467</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8622760817043416</v>
+        <v>0.9683439385697734</v>
       </c>
       <c r="J10" t="n">
-        <v>4.634536650393342</v>
+        <v>5.204627112719384</v>
       </c>
       <c r="K10" t="n">
-        <v>19.36151246467728</v>
+        <v>50.69667273203081</v>
       </c>
       <c r="L10" t="n">
-        <v>39.59289011024212</v>
+        <v>44.44992591695632</v>
       </c>
       <c r="M10" t="n">
-        <v>99.97126770519455</v>
+        <v>99.9677429868855</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.44852944387729</v>
+        <v>47.24419501509439</v>
       </c>
       <c r="C11" t="n">
-        <v>40.96128753178797</v>
+        <v>2.899660627880812</v>
       </c>
       <c r="D11" t="n">
-        <v>2.086926018925468</v>
+        <v>0.09383552797974576</v>
       </c>
       <c r="E11" t="n">
-        <v>6.753968396435039</v>
+        <v>0.562819498225783</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7417467059020877</v>
+        <v>0.8332147281405148</v>
       </c>
       <c r="G11" t="n">
-        <v>31.39084553467058</v>
+        <v>1.411442733362009</v>
       </c>
       <c r="H11" t="n">
-        <v>34.12034847149602</v>
+        <v>38.32787749446369</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7187774045600377</v>
+        <v>0.8074129820444297</v>
       </c>
       <c r="J11" t="n">
-        <v>4.635916911888047</v>
+        <v>5.207592050878218</v>
       </c>
       <c r="K11" t="n">
-        <v>19.55147055612272</v>
+        <v>52.75580498490561</v>
       </c>
       <c r="L11" t="n">
-        <v>39.46328979870862</v>
+        <v>44.31763594447553</v>
       </c>
       <c r="M11" t="n">
-        <v>99.97604788661931</v>
+        <v>99.97310155726196</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.26927493835831</v>
+        <v>46.24886092842179</v>
       </c>
       <c r="C12" t="n">
-        <v>40.89406234549197</v>
+        <v>2.018119092986066</v>
       </c>
       <c r="D12" t="n">
-        <v>2.074496041542535</v>
+        <v>0.04869798103825698</v>
       </c>
       <c r="E12" t="n">
-        <v>6.883931541460681</v>
+        <v>0.4042824775317044</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7419312525838327</v>
+        <v>0.8336189872213812</v>
       </c>
       <c r="G12" t="n">
-        <v>31.20387795820228</v>
+        <v>0.7324987981171154</v>
       </c>
       <c r="H12" t="n">
-        <v>34.12883761885629</v>
+        <v>38.34647341218354</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5991301970637262</v>
+        <v>0.6731706021961605</v>
       </c>
       <c r="J12" t="n">
-        <v>4.637070328648953</v>
+        <v>5.210118670133633</v>
       </c>
       <c r="K12" t="n">
-        <v>19.73072506164171</v>
+        <v>53.75113907157821</v>
       </c>
       <c r="L12" t="n">
-        <v>39.35524655385077</v>
+        <v>44.2083136970456</v>
       </c>
       <c r="M12" t="n">
-        <v>99.98003396098444</v>
+        <v>99.97757186160987</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>80.09577183928748</v>
+        <v>45.42706290163947</v>
       </c>
       <c r="C13" t="n">
-        <v>40.81394622208849</v>
+        <v>1.290796134097834</v>
       </c>
       <c r="D13" t="n">
-        <v>2.063017008572103</v>
+        <v>0.01494571477861799</v>
       </c>
       <c r="E13" t="n">
-        <v>6.986111787072792</v>
+        <v>0.2176112380453339</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7420854450061926</v>
+        <v>0.833962271873076</v>
       </c>
       <c r="G13" t="n">
-        <v>31.03121417060537</v>
+        <v>0.2248084597950455</v>
       </c>
       <c r="H13" t="n">
-        <v>34.13593047028485</v>
+        <v>38.36226450616151</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4993789264574819</v>
+        <v>0.5612065117791718</v>
       </c>
       <c r="J13" t="n">
-        <v>4.638034031288702</v>
+        <v>5.212264199206725</v>
       </c>
       <c r="K13" t="n">
-        <v>19.90422816071251</v>
+        <v>54.57293709836053</v>
       </c>
       <c r="L13" t="n">
-        <v>39.26518311172502</v>
+        <v>44.11756758414731</v>
       </c>
       <c r="M13" t="n">
-        <v>99.98335749452602</v>
+        <v>99.98130081660567</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>79.93222225138422</v>
+        <v>45.74164466305112</v>
       </c>
       <c r="C14" t="n">
-        <v>40.7282370075834</v>
+        <v>1.683854794761939</v>
       </c>
       <c r="D14" t="n">
-        <v>2.051717493944456</v>
+        <v>0.01495081011840726</v>
       </c>
       <c r="E14" t="n">
-        <v>7.080123931313675</v>
+        <v>0.6103463585876541</v>
       </c>
       <c r="F14" t="n">
-        <v>0.742214250715053</v>
+        <v>0.8342465888970236</v>
       </c>
       <c r="G14" t="n">
-        <v>30.86125063808118</v>
+        <v>0.2248851021977092</v>
       </c>
       <c r="H14" t="n">
-        <v>34.14185553289243</v>
+        <v>38.3753430892631</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4162213374683496</v>
+        <v>0.4678315333808312</v>
       </c>
       <c r="J14" t="n">
-        <v>4.638839066969079</v>
+        <v>5.214041180606397</v>
       </c>
       <c r="K14" t="n">
-        <v>20.06777774861578</v>
+        <v>54.25835533694888</v>
       </c>
       <c r="L14" t="n">
-        <v>39.19011360695479</v>
+        <v>44.04220079851754</v>
       </c>
       <c r="M14" t="n">
-        <v>99.98612836315397</v>
+        <v>99.98441093022836</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>79.78626818779027</v>
+        <v>46.02948981876743</v>
       </c>
       <c r="C15" t="n">
-        <v>40.64716076955325</v>
+        <v>2.037250617375546</v>
       </c>
       <c r="D15" t="n">
-        <v>2.041273483703298</v>
+        <v>0.0149550323124145</v>
       </c>
       <c r="E15" t="n">
-        <v>7.165301119457578</v>
+        <v>0.9634401203291241</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7423218194133898</v>
+        <v>0.8344821848895018</v>
       </c>
       <c r="G15" t="n">
-        <v>30.70415531737043</v>
+        <v>0.224948611032568</v>
       </c>
       <c r="H15" t="n">
-        <v>34.14680369301593</v>
+        <v>38.38618050491709</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3469013834959788</v>
+        <v>0.3899697097273469</v>
       </c>
       <c r="J15" t="n">
-        <v>4.639511371333684</v>
+        <v>5.215513655559386</v>
       </c>
       <c r="K15" t="n">
-        <v>20.21373181220972</v>
+        <v>53.97051018123257</v>
       </c>
       <c r="L15" t="n">
-        <v>39.12754571441846</v>
+        <v>43.97924388102018</v>
       </c>
       <c r="M15" t="n">
-        <v>99.98843829618144</v>
+        <v>99.9870046796283</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.6437837391434</v>
+        <v>45.25818787513555</v>
       </c>
       <c r="C16" t="n">
-        <v>40.5587480390056</v>
+        <v>1.320686464616082</v>
       </c>
       <c r="D16" t="n">
-        <v>2.031197314822127</v>
+        <v>0.005370656685602784</v>
       </c>
       <c r="E16" t="n">
-        <v>7.237453957398032</v>
+        <v>0.4001663956552317</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7424116442470362</v>
+        <v>0.8346819649973714</v>
       </c>
       <c r="G16" t="n">
-        <v>30.55259294378282</v>
+        <v>0.08078362764594187</v>
       </c>
       <c r="H16" t="n">
-        <v>34.15093563536366</v>
+        <v>38.3953703898791</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2891194669857406</v>
+        <v>0.3250525590387306</v>
       </c>
       <c r="J16" t="n">
-        <v>4.640072776543975</v>
+        <v>5.216762281233571</v>
       </c>
       <c r="K16" t="n">
-        <v>20.35621626085659</v>
+        <v>54.74181212486445</v>
       </c>
       <c r="L16" t="n">
-        <v>39.07539955059626</v>
+        <v>43.9266689185826</v>
       </c>
       <c r="M16" t="n">
-        <v>99.99036385045846</v>
+        <v>99.98916750806313</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>79.51310232892703</v>
+        <v>45.5948341884796</v>
       </c>
       <c r="C17" t="n">
-        <v>40.47312993155946</v>
+        <v>1.702795147083579</v>
       </c>
       <c r="D17" t="n">
-        <v>2.02174058904022</v>
+        <v>0.005371720458330853</v>
       </c>
       <c r="E17" t="n">
-        <v>7.302643015763752</v>
+        <v>0.7821137813375464</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7424866379464391</v>
+        <v>0.8348472915045294</v>
       </c>
       <c r="G17" t="n">
-        <v>30.4103480268133</v>
+        <v>0.08079962856072657</v>
       </c>
       <c r="H17" t="n">
-        <v>34.15438534553619</v>
+        <v>38.40297540920837</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2409572266618873</v>
+        <v>0.2709307855067838</v>
       </c>
       <c r="J17" t="n">
-        <v>4.640541487165243</v>
+        <v>5.217795571903308</v>
       </c>
       <c r="K17" t="n">
-        <v>20.48689767107296</v>
+        <v>54.4051658115204</v>
       </c>
       <c r="L17" t="n">
-        <v>39.03194130106242</v>
+        <v>43.88300980364495</v>
       </c>
       <c r="M17" t="n">
-        <v>99.99196890369484</v>
+        <v>99.99097076224893</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.3990298450244</v>
+        <v>45.86723648381587</v>
       </c>
       <c r="C18" t="n">
-        <v>40.3966120671419</v>
+        <v>2.013163992962236</v>
       </c>
       <c r="D18" t="n">
-        <v>2.012871858185003</v>
+        <v>0.005372601990061811</v>
       </c>
       <c r="E18" t="n">
-        <v>7.367649121156843</v>
+        <v>1.092324580079115</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7425492340807486</v>
+        <v>0.8349842949811015</v>
       </c>
       <c r="G18" t="n">
-        <v>30.27694753353275</v>
+        <v>0.08081288826717972</v>
       </c>
       <c r="H18" t="n">
-        <v>34.15726476771443</v>
+        <v>38.40927756913069</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2008146173499586</v>
+        <v>0.2258127057358476</v>
       </c>
       <c r="J18" t="n">
-        <v>4.640932713004678</v>
+        <v>5.218651843631885</v>
       </c>
       <c r="K18" t="n">
-        <v>20.60097015497558</v>
+        <v>54.13276351618413</v>
       </c>
       <c r="L18" t="n">
-        <v>38.99572452158634</v>
+        <v>43.84654663570066</v>
       </c>
       <c r="M18" t="n">
-        <v>99.99330674370383</v>
+        <v>99.99247414484702</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.31138589658133</v>
+        <v>45.08205419140362</v>
       </c>
       <c r="C19" t="n">
-        <v>40.34026471758865</v>
+        <v>1.259674948701849</v>
       </c>
       <c r="D19" t="n">
-        <v>2.00490447597341</v>
+        <v>0.00179335562728094</v>
       </c>
       <c r="E19" t="n">
-        <v>7.43849139152185</v>
+        <v>0.3959813388770469</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7426014632457877</v>
+        <v>0.8351004882352021</v>
       </c>
       <c r="G19" t="n">
-        <v>30.15710482610005</v>
+        <v>0.02697505756035081</v>
       </c>
       <c r="H19" t="n">
-        <v>34.15966730930623</v>
+        <v>38.41462245881932</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1673572851478263</v>
+        <v>0.1882034408144032</v>
       </c>
       <c r="J19" t="n">
-        <v>4.641259145286172</v>
+        <v>5.219378051470014</v>
       </c>
       <c r="K19" t="n">
-        <v>20.68861410341867</v>
+        <v>54.91794580859639</v>
       </c>
       <c r="L19" t="n">
-        <v>38.96554299517741</v>
+        <v>43.81610666754244</v>
       </c>
       <c r="M19" t="n">
-        <v>99.99442181618471</v>
+        <v>99.99372742484067</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>79.22702628120207</v>
+        <v>45.41729781170403</v>
       </c>
       <c r="C20" t="n">
-        <v>40.28198660884348</v>
+        <v>1.62123322738007</v>
       </c>
       <c r="D20" t="n">
-        <v>1.997210077509674</v>
+        <v>0.001793562079797074</v>
       </c>
       <c r="E20" t="n">
-        <v>7.503127012143405</v>
+        <v>0.757451514336577</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7426450395155266</v>
+        <v>0.8351966256629372</v>
       </c>
       <c r="G20" t="n">
-        <v>30.04136824920802</v>
+        <v>0.02697816295028099</v>
       </c>
       <c r="H20" t="n">
-        <v>34.16167181771422</v>
+        <v>38.41904478049513</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1394725881392026</v>
+        <v>0.1568542557859545</v>
       </c>
       <c r="J20" t="n">
-        <v>4.64153149697204</v>
+        <v>5.219978910393357</v>
       </c>
       <c r="K20" t="n">
-        <v>20.77297371879792</v>
+        <v>54.58270218829597</v>
       </c>
       <c r="L20" t="n">
-        <v>38.94039085888225</v>
+        <v>43.790836710968</v>
       </c>
       <c r="M20" t="n">
-        <v>99.99535118652366</v>
+        <v>99.99477212664404</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>79.13943242460755</v>
+        <v>45.7274990647843</v>
       </c>
       <c r="C21" t="n">
-        <v>40.21612771457921</v>
+        <v>1.953406431413465</v>
       </c>
       <c r="D21" t="n">
-        <v>1.98939484746213</v>
+        <v>0.001793732992425239</v>
       </c>
       <c r="E21" t="n">
-        <v>7.562206166503123</v>
+        <v>1.089541895764098</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7426813971796916</v>
+        <v>0.8352762134574913</v>
       </c>
       <c r="G21" t="n">
-        <v>29.92381416390954</v>
+        <v>0.02698073376106298</v>
       </c>
       <c r="H21" t="n">
-        <v>34.16334427026581</v>
+        <v>38.42270581904462</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1162328469141695</v>
+        <v>0.130724335655282</v>
       </c>
       <c r="J21" t="n">
-        <v>4.641758732373071</v>
+        <v>5.22047633410932</v>
       </c>
       <c r="K21" t="n">
-        <v>20.86056757539244</v>
+        <v>54.2725009352157</v>
       </c>
       <c r="L21" t="n">
-        <v>38.91943047146894</v>
+        <v>43.76973557071012</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9961257614406</v>
+        <v>99.99564293733928</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -527,13 +527,13 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>17.9</v>
       </c>
       <c r="L2" t="n">
         <v>45.8</v>
       </c>
       <c r="M2" t="n">
-        <v>97.09999999999999</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>89.90883074992746</v>
+        <v>82.33867158348323</v>
       </c>
       <c r="C3" t="n">
-        <v>41.76438630548301</v>
+        <v>44.09422713903879</v>
       </c>
       <c r="D3" t="n">
-        <v>2.360981399746533</v>
+        <v>2.206140852765119</v>
       </c>
       <c r="E3" t="n">
-        <v>4.509775227223538</v>
+        <v>4.561483722054656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8277209678102171</v>
+        <v>0.7382353268212736</v>
       </c>
       <c r="G3" t="n">
-        <v>35.51309522118743</v>
+        <v>33.18403532700867</v>
       </c>
       <c r="H3" t="n">
-        <v>38.07516451926998</v>
+        <v>33.95882503377858</v>
       </c>
       <c r="I3" t="n">
-        <v>3.448837365875905</v>
+        <v>3.075980528421973</v>
       </c>
       <c r="J3" t="n">
-        <v>5.173256048813856</v>
+        <v>4.61397079263296</v>
       </c>
       <c r="K3" t="n">
-        <v>10.09116925007255</v>
+        <v>17.66132841651676</v>
       </c>
       <c r="L3" t="n">
         <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>96.98888888888888</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.17112146556322</v>
+        <v>80.8652365529005</v>
       </c>
       <c r="C4" t="n">
-        <v>39.95286872130846</v>
+        <v>39.64367971590336</v>
       </c>
       <c r="D4" t="n">
-        <v>2.155169296878001</v>
+        <v>2.127024853488953</v>
       </c>
       <c r="E4" t="n">
-        <v>4.596186211426148</v>
+        <v>4.825572487390712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8286422136150284</v>
+        <v>0.7390161868112057</v>
       </c>
       <c r="G4" t="n">
-        <v>32.41733817387328</v>
+        <v>31.99399883789633</v>
       </c>
       <c r="H4" t="n">
-        <v>38.11754182629131</v>
+        <v>33.99474459331546</v>
       </c>
       <c r="I4" t="n">
-        <v>2.877229908385516</v>
+        <v>2.566028426427798</v>
       </c>
       <c r="J4" t="n">
-        <v>5.179013835093928</v>
+        <v>4.618851167570036</v>
       </c>
       <c r="K4" t="n">
-        <v>13.8288785344368</v>
+        <v>19.1347634470995</v>
       </c>
       <c r="L4" t="n">
-        <v>46.12245170631376</v>
+        <v>41.13611293342986</v>
       </c>
       <c r="M4" t="n">
-        <v>99.90419896205901</v>
+        <v>99.91455609643272</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>80.85035438711353</v>
+        <v>79.23145129340115</v>
       </c>
       <c r="C5" t="n">
-        <v>35.07618408239633</v>
+        <v>38.4082199430917</v>
       </c>
       <c r="D5" t="n">
-        <v>1.864248919614553</v>
+        <v>2.039632399808895</v>
       </c>
       <c r="E5" t="n">
-        <v>4.375770360869232</v>
+        <v>4.984019334681846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8294621623818205</v>
+        <v>0.7396816226391973</v>
       </c>
       <c r="G5" t="n">
-        <v>28.04141083253559</v>
+        <v>30.6794706804588</v>
       </c>
       <c r="H5" t="n">
-        <v>38.15525946956374</v>
+        <v>34.02535464140308</v>
       </c>
       <c r="I5" t="n">
-        <v>2.400064127262213</v>
+        <v>2.140282472914344</v>
       </c>
       <c r="J5" t="n">
-        <v>5.184138514886378</v>
+        <v>4.623010141494984</v>
       </c>
       <c r="K5" t="n">
-        <v>19.14964561288648</v>
+        <v>20.76854870659887</v>
       </c>
       <c r="L5" t="n">
-        <v>45.6942472517065</v>
+        <v>40.75195278290866</v>
       </c>
       <c r="M5" t="n">
-        <v>99.9200769469893</v>
+        <v>99.92872143259922</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.23296383832343</v>
+        <v>75.78283668026224</v>
       </c>
       <c r="C6" t="n">
-        <v>27.82684396650863</v>
+        <v>35.29145087902128</v>
       </c>
       <c r="D6" t="n">
-        <v>1.451330957440093</v>
+        <v>1.854526985089862</v>
       </c>
       <c r="E6" t="n">
-        <v>3.740214125107397</v>
+        <v>4.829192980808566</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8302179605909371</v>
+        <v>0.7402623648678723</v>
       </c>
       <c r="G6" t="n">
-        <v>21.83043648482808</v>
+        <v>27.89517673406001</v>
       </c>
       <c r="H6" t="n">
-        <v>38.19002618718311</v>
+        <v>34.05206878392213</v>
       </c>
       <c r="I6" t="n">
-        <v>2.001875869480463</v>
+        <v>1.784969051089584</v>
       </c>
       <c r="J6" t="n">
-        <v>5.188862253693357</v>
+        <v>4.626639780424203</v>
       </c>
       <c r="K6" t="n">
-        <v>26.76703616167657</v>
+        <v>24.21716331973777</v>
       </c>
       <c r="L6" t="n">
-        <v>45.33945142383529</v>
+        <v>40.43193351032669</v>
       </c>
       <c r="M6" t="n">
-        <v>99.93333155202049</v>
+        <v>99.94054770908572</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>65.59803331346066</v>
+        <v>73.1325007604005</v>
       </c>
       <c r="C7" t="n">
-        <v>20.49530731830937</v>
+        <v>32.91673551317146</v>
       </c>
       <c r="D7" t="n">
-        <v>1.042147829386426</v>
+        <v>1.713546565733215</v>
       </c>
       <c r="E7" t="n">
-        <v>2.963985563910998</v>
+        <v>4.710160172835537</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8309223361178585</v>
+        <v>0.7407645894650039</v>
       </c>
       <c r="G7" t="n">
-        <v>15.67564026702082</v>
+        <v>25.77459625957045</v>
       </c>
       <c r="H7" t="n">
-        <v>38.2224274614215</v>
+        <v>34.07517111539018</v>
       </c>
       <c r="I7" t="n">
-        <v>1.669645254866454</v>
+        <v>1.488483373249831</v>
       </c>
       <c r="J7" t="n">
-        <v>5.193264600736616</v>
+        <v>4.629778684156275</v>
       </c>
       <c r="K7" t="n">
-        <v>34.40196668653932</v>
+        <v>26.86749923959951</v>
       </c>
       <c r="L7" t="n">
-        <v>45.04711833211019</v>
+        <v>40.16618277358765</v>
       </c>
       <c r="M7" t="n">
-        <v>99.94439233695888</v>
+        <v>99.95041752635862</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58.25334238541407</v>
+        <v>70.42341705791662</v>
       </c>
       <c r="C8" t="n">
-        <v>13.39990024267652</v>
+        <v>30.43671768696061</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6537677274740138</v>
+        <v>1.570295041987104</v>
       </c>
       <c r="E8" t="n">
-        <v>2.091468847525101</v>
+        <v>4.523248696363733</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8315844111304048</v>
+        <v>0.7411997601816404</v>
       </c>
       <c r="G8" t="n">
-        <v>9.833756234088291</v>
+        <v>23.61985458988936</v>
       </c>
       <c r="H8" t="n">
-        <v>38.25288291199863</v>
+        <v>34.09518896835546</v>
       </c>
       <c r="I8" t="n">
-        <v>1.392479683632607</v>
+        <v>1.241131500004087</v>
       </c>
       <c r="J8" t="n">
-        <v>5.197402569565031</v>
+        <v>4.632498501135252</v>
       </c>
       <c r="K8" t="n">
-        <v>41.74665761458592</v>
+        <v>29.57658294208336</v>
       </c>
       <c r="L8" t="n">
-        <v>44.80706310788016</v>
+        <v>39.94535261058799</v>
       </c>
       <c r="M8" t="n">
-        <v>99.95362096514259</v>
+        <v>99.95865323963196</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52.67427197719729</v>
+        <v>66.830151738034</v>
       </c>
       <c r="C9" t="n">
-        <v>8.024906768061111</v>
+        <v>27.03371214353978</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3640741674948693</v>
+        <v>1.381110468719284</v>
       </c>
       <c r="E9" t="n">
-        <v>1.358252032245242</v>
+        <v>4.150769213892953</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8321955124118939</v>
+        <v>0.7415823225249653</v>
       </c>
       <c r="G9" t="n">
-        <v>5.476282269401993</v>
+        <v>20.77420330031924</v>
       </c>
       <c r="H9" t="n">
-        <v>38.28099357094712</v>
+        <v>34.1127868361484</v>
       </c>
       <c r="I9" t="n">
-        <v>1.161252472121829</v>
+        <v>1.034810080648129</v>
       </c>
       <c r="J9" t="n">
-        <v>5.201221952574338</v>
+        <v>4.634889515781032</v>
       </c>
       <c r="K9" t="n">
-        <v>47.32572802280271</v>
+        <v>33.16984826196598</v>
       </c>
       <c r="L9" t="n">
-        <v>44.61068521792416</v>
+        <v>39.76196371949412</v>
       </c>
       <c r="M9" t="n">
-        <v>99.96132000878798</v>
+        <v>99.96552412499989</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49.30332726796919</v>
+        <v>64.32089296327254</v>
       </c>
       <c r="C10" t="n">
-        <v>4.821144337898365</v>
+        <v>24.68213015300721</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1937132490111442</v>
+        <v>1.246913578888676</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8840769594764873</v>
+        <v>3.948679544889597</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8327403380351014</v>
+        <v>0.7419138805784934</v>
       </c>
       <c r="G10" t="n">
-        <v>2.913770120542627</v>
+        <v>18.75565841578384</v>
       </c>
       <c r="H10" t="n">
-        <v>38.30605554961467</v>
+        <v>34.1280385066107</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9683439385697734</v>
+        <v>0.8627272829056584</v>
       </c>
       <c r="J10" t="n">
-        <v>5.204627112719384</v>
+        <v>4.636961753615584</v>
       </c>
       <c r="K10" t="n">
-        <v>50.69667273203081</v>
+        <v>35.67910703672745</v>
       </c>
       <c r="L10" t="n">
-        <v>44.44992591695632</v>
+        <v>39.61001808580288</v>
       </c>
       <c r="M10" t="n">
-        <v>99.9677429868855</v>
+        <v>99.97125527553754</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47.24419501509439</v>
+        <v>62.56396708922949</v>
       </c>
       <c r="C11" t="n">
-        <v>2.899660627880812</v>
+        <v>23.05606277983444</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09383552797974576</v>
+        <v>1.139036872490601</v>
       </c>
       <c r="E11" t="n">
-        <v>0.562819498225783</v>
+        <v>4.050649608173879</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8332147281405148</v>
+        <v>0.742198173884708</v>
       </c>
       <c r="G11" t="n">
-        <v>1.411442733362009</v>
+        <v>17.13301295704613</v>
       </c>
       <c r="H11" t="n">
-        <v>38.32787749446369</v>
+        <v>34.14111599869657</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8074129820444297</v>
+        <v>0.7192148921581732</v>
       </c>
       <c r="J11" t="n">
-        <v>5.207592050878218</v>
+        <v>4.638738586779425</v>
       </c>
       <c r="K11" t="n">
-        <v>52.75580498490561</v>
+        <v>37.43603291077051</v>
       </c>
       <c r="L11" t="n">
-        <v>44.31763594447553</v>
+        <v>39.48393966264767</v>
       </c>
       <c r="M11" t="n">
-        <v>99.97310155726196</v>
+        <v>99.97603535325263</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>46.24886092842179</v>
+        <v>61.50799925854164</v>
       </c>
       <c r="C12" t="n">
-        <v>2.018119092986066</v>
+        <v>22.10882073815166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04869798103825698</v>
+        <v>1.050721823901903</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4042824775317044</v>
+        <v>4.518235576364098</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8336189872213812</v>
+        <v>0.7424393229240416</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7324987981171154</v>
+        <v>15.80460743452447</v>
       </c>
       <c r="H12" t="n">
-        <v>38.34647341218354</v>
+        <v>34.15220885450591</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6731706021961605</v>
+        <v>0.5995404780459488</v>
       </c>
       <c r="J12" t="n">
-        <v>5.210118670133633</v>
+        <v>4.64024576827526</v>
       </c>
       <c r="K12" t="n">
-        <v>53.75113907157821</v>
+        <v>38.49200074145836</v>
       </c>
       <c r="L12" t="n">
-        <v>44.2083136970456</v>
+        <v>39.37920032894114</v>
       </c>
       <c r="M12" t="n">
-        <v>99.97757186160987</v>
+        <v>99.98002180855116</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>45.42706290163947</v>
+        <v>59.591892811732</v>
       </c>
       <c r="C13" t="n">
-        <v>1.290796134097834</v>
+        <v>20.28316722174459</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01494571477861799</v>
+        <v>0.9368367902131387</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2176112380453339</v>
+        <v>4.51776688291015</v>
       </c>
       <c r="F13" t="n">
-        <v>0.833962271873076</v>
+        <v>0.7426468674018469</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2248084597950455</v>
+        <v>14.09158671945597</v>
       </c>
       <c r="H13" t="n">
-        <v>38.36226450616151</v>
+        <v>34.16175590048496</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5612065117791718</v>
+        <v>0.4997567300043886</v>
       </c>
       <c r="J13" t="n">
-        <v>5.212264199206725</v>
+        <v>4.641542921261543</v>
       </c>
       <c r="K13" t="n">
-        <v>54.57293709836053</v>
+        <v>40.408107188268</v>
       </c>
       <c r="L13" t="n">
-        <v>44.11756758414731</v>
+        <v>39.29207168781947</v>
       </c>
       <c r="M13" t="n">
-        <v>99.98130081660567</v>
+        <v>99.98334609783205</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>45.74164466305112</v>
+        <v>58.76146188114074</v>
       </c>
       <c r="C14" t="n">
-        <v>1.683854794761939</v>
+        <v>19.52781698633491</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01495081011840726</v>
+        <v>0.8687663394307504</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6103463585876541</v>
+        <v>4.853149051299265</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8342465888970236</v>
+        <v>0.7428223558463551</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2248851021977092</v>
+        <v>13.06769368893755</v>
       </c>
       <c r="H14" t="n">
-        <v>38.3753430892631</v>
+        <v>34.16982836893234</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4678315333808312</v>
+        <v>0.4165623526547709</v>
       </c>
       <c r="J14" t="n">
-        <v>5.214041180606397</v>
+        <v>4.64263972403972</v>
       </c>
       <c r="K14" t="n">
-        <v>54.25835533694888</v>
+        <v>41.23853811885925</v>
       </c>
       <c r="L14" t="n">
-        <v>44.04220079851754</v>
+        <v>39.21976276341682</v>
       </c>
       <c r="M14" t="n">
-        <v>99.98441093022836</v>
+        <v>99.98611786861099</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>46.02948981876743</v>
+        <v>57.48246060700209</v>
       </c>
       <c r="C15" t="n">
-        <v>2.037250617375546</v>
+        <v>18.31128604368843</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0149550323124145</v>
+        <v>0.764658201796553</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9634401203291241</v>
+        <v>5.305608931372659</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8344821848895018</v>
+        <v>0.742971915539011</v>
       </c>
       <c r="G15" t="n">
-        <v>0.224948611032568</v>
+        <v>11.50173378535649</v>
       </c>
       <c r="H15" t="n">
-        <v>38.38618050491709</v>
+        <v>34.1767081147945</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3899697097273469</v>
+        <v>0.3472051860240544</v>
       </c>
       <c r="J15" t="n">
-        <v>5.215513655559386</v>
+        <v>4.643574472118819</v>
       </c>
       <c r="K15" t="n">
-        <v>53.97051018123257</v>
+        <v>42.51753939299791</v>
       </c>
       <c r="L15" t="n">
-        <v>43.97924388102018</v>
+        <v>39.15960338685103</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9870046796283</v>
+        <v>99.98842882353736</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>45.25818787513555</v>
+        <v>57.36832261890635</v>
       </c>
       <c r="C16" t="n">
-        <v>1.320686464616082</v>
+        <v>18.24905778847232</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005370656685602784</v>
+        <v>0.7217463380815058</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4001663956552317</v>
+        <v>5.931015264497244</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8346819649973714</v>
+        <v>0.7430968427276942</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08078362764594187</v>
+        <v>10.85626783530932</v>
       </c>
       <c r="H16" t="n">
-        <v>38.3953703898791</v>
+        <v>34.18245476547393</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3250525590387306</v>
+        <v>0.2893863057685674</v>
       </c>
       <c r="J16" t="n">
-        <v>5.216762281233571</v>
+        <v>4.644355267048089</v>
       </c>
       <c r="K16" t="n">
-        <v>54.74181212486445</v>
+        <v>42.63167738109365</v>
       </c>
       <c r="L16" t="n">
-        <v>43.9266689185826</v>
+        <v>39.10962024193337</v>
       </c>
       <c r="M16" t="n">
-        <v>99.98916750806313</v>
+        <v>99.99035541149934</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>45.5948341884796</v>
+        <v>55.81777974725006</v>
       </c>
       <c r="C17" t="n">
-        <v>1.702795147083579</v>
+        <v>16.74177595142734</v>
       </c>
       <c r="D17" t="n">
-        <v>0.005371720458330853</v>
+        <v>0.6312663374219485</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7821137813375464</v>
+        <v>5.874419301993481</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8348472915045294</v>
+        <v>0.7432038740478405</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08079962856072657</v>
+        <v>9.49529782538848</v>
       </c>
       <c r="H17" t="n">
-        <v>38.40297540920837</v>
+        <v>34.18737820620066</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2709307855067838</v>
+        <v>0.2411899893986465</v>
       </c>
       <c r="J17" t="n">
-        <v>5.217795571903308</v>
+        <v>4.645024212799004</v>
       </c>
       <c r="K17" t="n">
-        <v>54.4051658115204</v>
+        <v>44.18222025274994</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88300980364495</v>
+        <v>39.06796528732916</v>
       </c>
       <c r="M17" t="n">
-        <v>99.99097076224893</v>
+        <v>99.99196149150643</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>45.86723648381587</v>
+        <v>55.79900873114487</v>
       </c>
       <c r="C18" t="n">
-        <v>2.013163992962236</v>
+        <v>16.75891493238526</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005372601990061811</v>
+        <v>0.5987663245216786</v>
       </c>
       <c r="E18" t="n">
-        <v>1.092324580079115</v>
+        <v>6.412424487809738</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8349842949811015</v>
+        <v>0.7432931203862725</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08081288826717972</v>
+        <v>9.006443464680252</v>
       </c>
       <c r="H18" t="n">
-        <v>38.40927756913069</v>
+        <v>34.19148353776853</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2258127057358476</v>
+        <v>0.201015793564194</v>
       </c>
       <c r="J18" t="n">
-        <v>5.218651843631885</v>
+        <v>4.645582002414204</v>
       </c>
       <c r="K18" t="n">
-        <v>54.13276351618413</v>
+        <v>44.20099126885512</v>
       </c>
       <c r="L18" t="n">
-        <v>43.84654663570066</v>
+        <v>39.03339407683187</v>
       </c>
       <c r="M18" t="n">
-        <v>99.99247414484702</v>
+        <v>99.99330027807225</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>45.08205419140362</v>
+        <v>54.93356867742018</v>
       </c>
       <c r="C19" t="n">
-        <v>1.259674948701849</v>
+        <v>15.92340620389049</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00179335562728094</v>
+        <v>0.5375787409076904</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3959813388770469</v>
+        <v>6.557997267892492</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8351004882352021</v>
+        <v>0.7433686807650639</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02697505756035081</v>
+        <v>8.086080227819846</v>
       </c>
       <c r="H19" t="n">
-        <v>38.41462245881932</v>
+        <v>34.19495931519294</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1882034408144032</v>
+        <v>0.1675301900604867</v>
       </c>
       <c r="J19" t="n">
-        <v>5.219378051470014</v>
+        <v>4.64605425478165</v>
       </c>
       <c r="K19" t="n">
-        <v>54.91794580859639</v>
+        <v>45.06643132257983</v>
       </c>
       <c r="L19" t="n">
-        <v>43.81610666754244</v>
+        <v>39.00457870148623</v>
       </c>
       <c r="M19" t="n">
-        <v>99.99372742484067</v>
+        <v>99.99441622795655</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>45.41729781170403</v>
+        <v>55.26906132039244</v>
       </c>
       <c r="C20" t="n">
-        <v>1.62123322738007</v>
+        <v>16.2837856423102</v>
       </c>
       <c r="D20" t="n">
-        <v>0.001793562079797074</v>
+        <v>0.5261130066967049</v>
       </c>
       <c r="E20" t="n">
-        <v>0.757451514336577</v>
+        <v>7.101996081564651</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8351966256629372</v>
+        <v>0.7434312771597558</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02697816295028099</v>
+        <v>7.913616475729606</v>
       </c>
       <c r="H20" t="n">
-        <v>38.41904478049513</v>
+        <v>34.19783874934877</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1568542557859545</v>
+        <v>0.1396202476444821</v>
       </c>
       <c r="J20" t="n">
-        <v>5.219978910393357</v>
+        <v>4.646445482248475</v>
       </c>
       <c r="K20" t="n">
-        <v>54.58270218829597</v>
+        <v>44.73093867960757</v>
       </c>
       <c r="L20" t="n">
-        <v>43.790836710968</v>
+        <v>38.98062206169166</v>
       </c>
       <c r="M20" t="n">
-        <v>99.99477212664404</v>
+        <v>99.99534638360942</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>45.7274990647843</v>
+        <v>55.3936254691073</v>
       </c>
       <c r="C21" t="n">
-        <v>1.953406431413465</v>
+        <v>16.4291126909273</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001793732992425239</v>
+        <v>0.512188565127377</v>
       </c>
       <c r="E21" t="n">
-        <v>1.089541895764098</v>
+        <v>7.470421478802614</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8352762134574913</v>
+        <v>0.7434833315482804</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02698073376106298</v>
+        <v>7.704169667124298</v>
       </c>
       <c r="H21" t="n">
-        <v>38.42270581904462</v>
+        <v>34.2002332512209</v>
       </c>
       <c r="I21" t="n">
-        <v>0.130724335655282</v>
+        <v>0.1163583531070719</v>
       </c>
       <c r="J21" t="n">
-        <v>5.22047633410932</v>
+        <v>4.646770822176753</v>
       </c>
       <c r="K21" t="n">
-        <v>54.2725009352157</v>
+        <v>44.60637453089272</v>
       </c>
       <c r="L21" t="n">
-        <v>43.76973557071012</v>
+        <v>38.96063443796764</v>
       </c>
       <c r="M21" t="n">
-        <v>99.99564293733928</v>
+        <v>99.99612165978766</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,40 +500,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>72.8</v>
+        <v>66</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8.4</v>
+        <v>14.3</v>
       </c>
       <c r="G2" t="n">
-        <v>62.4</v>
+        <v>51.7</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>22.4</v>
       </c>
       <c r="L2" t="n">
-        <v>7.5</v>
+        <v>14.4</v>
       </c>
       <c r="M2" t="n">
-        <v>116.3</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>65.3324662748814</v>
+        <v>76.70937726796173</v>
       </c>
       <c r="C3" t="n">
-        <v>71.90577596286629</v>
+        <v>65.2482661568506</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7877536914989848</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8989477149846714</v>
+        <v>0.1340446121422303</v>
       </c>
       <c r="F3" t="n">
-        <v>6.725014540414329</v>
+        <v>13.80123326616403</v>
       </c>
       <c r="G3" t="n">
-        <v>49.15583034953664</v>
+        <v>49.0372075373197</v>
       </c>
       <c r="H3" t="n">
-        <v>4.403283330033191</v>
+        <v>6.755848451968405</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6671641409141199</v>
+        <v>0.8042676728533816</v>
       </c>
       <c r="J3" t="n">
-        <v>2.694472507499459</v>
+        <v>6.176775727513971</v>
       </c>
       <c r="K3" t="n">
-        <v>34.6675337251186</v>
+        <v>23.29062273203828</v>
       </c>
       <c r="L3" t="n">
-        <v>9.698912534237335</v>
+        <v>14.23333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>116.2722222222222</v>
+        <v>102.7722222222222</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.91955450177647</v>
+        <v>75.22617598922707</v>
       </c>
       <c r="C4" t="n">
-        <v>55.68218270815623</v>
+        <v>61.60098798034318</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7573257603001678</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9569133408943202</v>
+        <v>0.2417769381581862</v>
       </c>
       <c r="F4" t="n">
-        <v>6.726964904168093</v>
+        <v>13.80533319217361</v>
       </c>
       <c r="G4" t="n">
-        <v>47.25712744273046</v>
+        <v>47.57217762713753</v>
       </c>
       <c r="H4" t="n">
-        <v>4.404560353919584</v>
+        <v>6.757855408756313</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5561313578181294</v>
+        <v>0.6704221635670946</v>
       </c>
       <c r="J4" t="n">
-        <v>3.260531341945706</v>
+        <v>6.178610659434344</v>
       </c>
       <c r="K4" t="n">
-        <v>36.08044549822354</v>
+        <v>24.77382401077291</v>
       </c>
       <c r="L4" t="n">
-        <v>8.218839456372606</v>
+        <v>13.60284724019353</v>
       </c>
       <c r="M4" t="n">
-        <v>99.98146766275238</v>
+        <v>99.97765923130963</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.0187601072906</v>
+        <v>73.93017879070143</v>
       </c>
       <c r="C5" t="n">
-        <v>55.05047269505407</v>
+        <v>60.41640474832798</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7462924286802906</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.020231366083166</v>
+        <v>0.3284204921841304</v>
       </c>
       <c r="F5" t="n">
-        <v>6.728588551101539</v>
+        <v>13.80881159928546</v>
       </c>
       <c r="G5" t="n">
-        <v>46.56864754965012</v>
+        <v>46.29439524142216</v>
       </c>
       <c r="H5" t="n">
-        <v>4.405623456078389</v>
+        <v>6.759558125524351</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4635546565739045</v>
+        <v>0.5588259032344868</v>
       </c>
       <c r="J5" t="n">
-        <v>4.085822099123204</v>
+        <v>6.180167429050836</v>
       </c>
       <c r="K5" t="n">
-        <v>35.9812398927094</v>
+        <v>26.06982120929857</v>
       </c>
       <c r="L5" t="n">
-        <v>8.952839318963813</v>
+        <v>13.49515120449657</v>
       </c>
       <c r="M5" t="n">
-        <v>99.98455190672728</v>
+        <v>99.98137716212312</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.66365375111871</v>
+        <v>71.98342246055502</v>
       </c>
       <c r="C6" t="n">
-        <v>53.68335347775111</v>
+        <v>58.56248571152793</v>
       </c>
       <c r="D6" t="n">
-        <v>0.724133764123577</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.054334822096337</v>
+        <v>0.3924064787008437</v>
       </c>
       <c r="F6" t="n">
-        <v>6.729971467595506</v>
+        <v>13.81179005745383</v>
       </c>
       <c r="G6" t="n">
-        <v>45.18594688131119</v>
+        <v>44.37092066887098</v>
       </c>
       <c r="H6" t="n">
-        <v>4.406528937116105</v>
+        <v>6.761016112040338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3863749418767629</v>
+        <v>0.4657886981950189</v>
       </c>
       <c r="J6" t="n">
-        <v>4.176362936999234</v>
+        <v>6.181500445294023</v>
       </c>
       <c r="K6" t="n">
-        <v>37.33634624888128</v>
+        <v>28.01657753944495</v>
       </c>
       <c r="L6" t="n">
-        <v>8.96742375512946</v>
+        <v>13.40541380727059</v>
       </c>
       <c r="M6" t="n">
-        <v>99.98712348176186</v>
+        <v>99.98447705824348</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64.7716231517693</v>
+        <v>70.29730683269915</v>
       </c>
       <c r="C7" t="n">
-        <v>53.74805012149838</v>
+        <v>56.95369445191907</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7242537727424628</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.108181633810985</v>
+        <v>0.4423998696893742</v>
       </c>
       <c r="F7" t="n">
-        <v>6.73108680653008</v>
+        <v>13.81433265526441</v>
       </c>
       <c r="G7" t="n">
-        <v>45.19343541912966</v>
+        <v>42.70744647228602</v>
       </c>
       <c r="H7" t="n">
-        <v>4.407259218561363</v>
+        <v>6.762260740339223</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3220324789095646</v>
+        <v>0.3882287039528232</v>
       </c>
       <c r="J7" t="n">
-        <v>6.285373822085189</v>
+        <v>6.18263839116729</v>
       </c>
       <c r="K7" t="n">
-        <v>35.2283768482307</v>
+        <v>29.70269316730085</v>
       </c>
       <c r="L7" t="n">
-        <v>11.01284039299656</v>
+        <v>13.33067380583021</v>
       </c>
       <c r="M7" t="n">
-        <v>99.98926736272564</v>
+        <v>99.98706142505013</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66.84364095149037</v>
+        <v>68.37550917417462</v>
       </c>
       <c r="C8" t="n">
-        <v>53.80168436539508</v>
+        <v>55.09630199204205</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7243507089369237</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.153062675543082</v>
+        <v>0.4766922056886039</v>
       </c>
       <c r="F8" t="n">
-        <v>6.731987714421993</v>
+        <v>13.81651178446173</v>
       </c>
       <c r="G8" t="n">
-        <v>45.19948423766402</v>
+        <v>40.81178911736804</v>
       </c>
       <c r="H8" t="n">
-        <v>4.407849098728686</v>
+        <v>6.763327446939311</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2683963172139439</v>
+        <v>0.3235749539438404</v>
       </c>
       <c r="J8" t="n">
-        <v>8.358510198981719</v>
+        <v>6.183613665773084</v>
       </c>
       <c r="K8" t="n">
-        <v>33.15635904850963</v>
+        <v>31.62449082582538</v>
       </c>
       <c r="L8" t="n">
-        <v>13.03301123945892</v>
+        <v>13.2684230514672</v>
       </c>
       <c r="M8" t="n">
-        <v>99.99105465336362</v>
+        <v>99.98921586933463</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65.76692879181175</v>
+        <v>66.07991700974334</v>
       </c>
       <c r="C9" t="n">
-        <v>52.34166369851862</v>
+        <v>52.85434190891264</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7012811703235481</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.153620763848183</v>
+        <v>0.4951969888126842</v>
       </c>
       <c r="F9" t="n">
-        <v>6.732750950761584</v>
+        <v>13.81839136265158</v>
       </c>
       <c r="G9" t="n">
-        <v>43.75994502818939</v>
+        <v>38.54794378533227</v>
       </c>
       <c r="H9" t="n">
-        <v>4.40834883680818</v>
+        <v>6.764247520179097</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2236889554467249</v>
+        <v>0.2696824771753911</v>
       </c>
       <c r="J9" t="n">
-        <v>8.787293086434145</v>
+        <v>6.184454875592317</v>
       </c>
       <c r="K9" t="n">
-        <v>34.23307120818824</v>
+        <v>33.92008299025666</v>
       </c>
       <c r="L9" t="n">
-        <v>13.41780964003719</v>
+        <v>13.2165869076656</v>
       </c>
       <c r="M9" t="n">
-        <v>99.99254454674406</v>
+        <v>99.99101180683489</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67.47969565411779</v>
+        <v>63.65734102305134</v>
       </c>
       <c r="C10" t="n">
-        <v>52.13054872630711</v>
+        <v>50.47641204971222</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6975308553332307</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.178522196390472</v>
+        <v>0.5019856343684916</v>
       </c>
       <c r="F10" t="n">
-        <v>6.73337096472082</v>
+        <v>13.82001769886729</v>
       </c>
       <c r="G10" t="n">
-        <v>43.52592537279358</v>
+        <v>36.16034946708921</v>
       </c>
       <c r="H10" t="n">
-        <v>4.408754798329108</v>
+        <v>6.765043628816155</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1864246289949941</v>
+        <v>0.2247618475639934</v>
       </c>
       <c r="J10" t="n">
-        <v>10.74916683755559</v>
+        <v>6.185182746346199</v>
       </c>
       <c r="K10" t="n">
-        <v>32.52030434588221</v>
+        <v>36.34265897694866</v>
       </c>
       <c r="L10" t="n">
-        <v>15.34293334571493</v>
+        <v>13.17343779341757</v>
       </c>
       <c r="M10" t="n">
-        <v>99.99378641790425</v>
+        <v>99.99250882007846</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>69.2359441222449</v>
+        <v>61.28641176665367</v>
       </c>
       <c r="C11" t="n">
-        <v>52.16124169882074</v>
+        <v>48.1426404672001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6975830306477095</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.20450459618938</v>
+        <v>0.5007904913105315</v>
       </c>
       <c r="F11" t="n">
-        <v>6.733874620931726</v>
+        <v>13.82142571860197</v>
       </c>
       <c r="G11" t="n">
-        <v>43.52918111241706</v>
+        <v>33.82532915606086</v>
       </c>
       <c r="H11" t="n">
-        <v>4.409084573229106</v>
+        <v>6.765732869245721</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1553654779658167</v>
+        <v>0.1873206224099175</v>
       </c>
       <c r="J11" t="n">
-        <v>12.5063507108641</v>
+        <v>6.18581290902466</v>
       </c>
       <c r="K11" t="n">
-        <v>30.7640558777551</v>
+        <v>38.71358823334634</v>
       </c>
       <c r="L11" t="n">
-        <v>17.06952396150764</v>
+        <v>13.13752791479902</v>
       </c>
       <c r="M11" t="n">
-        <v>99.99482153808349</v>
+        <v>99.99375661534545</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>71.37779363616905</v>
+        <v>58.91081515938782</v>
       </c>
       <c r="C12" t="n">
-        <v>52.18672189879224</v>
+        <v>45.79796551182001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6976252110844624</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.226157271808613</v>
+        <v>0.4921926729954461</v>
       </c>
       <c r="F12" t="n">
-        <v>6.734281795074546</v>
+        <v>13.82264661627044</v>
       </c>
       <c r="G12" t="n">
-        <v>43.53181317167044</v>
+        <v>31.48717172628523</v>
       </c>
       <c r="H12" t="n">
-        <v>4.409351175346429</v>
+        <v>6.766330511461053</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1294790603164275</v>
+        <v>0.1561143076112665</v>
       </c>
       <c r="J12" t="n">
-        <v>14.64908595086813</v>
+        <v>6.186359324764392</v>
       </c>
       <c r="K12" t="n">
-        <v>28.62220636383094</v>
+        <v>41.08918484061218</v>
       </c>
       <c r="L12" t="n">
-        <v>19.18675602965554</v>
+        <v>13.10764629694531</v>
       </c>
       <c r="M12" t="n">
-        <v>99.99568429227872</v>
+        <v>99.99479664937749</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>70.89776809617759</v>
+        <v>56.17969122094362</v>
       </c>
       <c r="C13" t="n">
-        <v>51.37705665774092</v>
+        <v>43.09256961983068</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6849092752297363</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.221791653943163</v>
+        <v>0.4718770586322212</v>
       </c>
       <c r="F13" t="n">
-        <v>6.73462344221674</v>
+        <v>13.82371366828051</v>
       </c>
       <c r="G13" t="n">
-        <v>42.73833877433554</v>
+        <v>28.80030546374832</v>
       </c>
       <c r="H13" t="n">
-        <v>4.409574872880008</v>
+        <v>6.766852844612839</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1079046909304398</v>
+        <v>0.1301052991665485</v>
       </c>
       <c r="J13" t="n">
-        <v>15.00062538664196</v>
+        <v>6.186836886503167</v>
       </c>
       <c r="K13" t="n">
-        <v>29.10223190382243</v>
+        <v>43.82030877905639</v>
       </c>
       <c r="L13" t="n">
-        <v>19.5171147978723</v>
+        <v>13.08278509256817</v>
       </c>
       <c r="M13" t="n">
-        <v>99.99640335943565</v>
+        <v>99.99566349145525</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>72.36956498447621</v>
+        <v>53.8045490000593</v>
       </c>
       <c r="C14" t="n">
-        <v>51.3946499083544</v>
+        <v>40.73882415021655</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6849376435027282</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.236829642726015</v>
+        <v>0.4516895174144771</v>
       </c>
       <c r="F14" t="n">
-        <v>6.734902383739677</v>
+        <v>13.82464226552702</v>
       </c>
       <c r="G14" t="n">
-        <v>42.74010895457023</v>
+        <v>26.46522896619771</v>
       </c>
       <c r="H14" t="n">
-        <v>4.409757513162884</v>
+        <v>6.767307402705533</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08992430019775859</v>
+        <v>0.1084283657409449</v>
       </c>
       <c r="J14" t="n">
-        <v>16.47310454657692</v>
+        <v>6.18725248247363</v>
       </c>
       <c r="K14" t="n">
-        <v>27.63043501552378</v>
+        <v>46.19545099994069</v>
       </c>
       <c r="L14" t="n">
-        <v>20.97191772359598</v>
+        <v>13.0621108137548</v>
       </c>
       <c r="M14" t="n">
-        <v>99.99700264747418</v>
+        <v>99.99638596391205</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>72.11593046508406</v>
+        <v>51.78165785545875</v>
       </c>
       <c r="C15" t="n">
-        <v>50.18779725200744</v>
+        <v>38.73372909978045</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6662281576808726</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.215534812045552</v>
+        <v>0.6315895949775642</v>
       </c>
       <c r="F15" t="n">
-        <v>6.735135670291077</v>
+        <v>13.82544642766981</v>
       </c>
       <c r="G15" t="n">
-        <v>41.57263703928645</v>
+        <v>24.27894616969005</v>
       </c>
       <c r="H15" t="n">
-        <v>4.409910260309633</v>
+        <v>6.767701048509699</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07493951252979993</v>
+        <v>0.09036222740275951</v>
       </c>
       <c r="J15" t="n">
-        <v>17.44154501294068</v>
+        <v>6.187612387208867</v>
       </c>
       <c r="K15" t="n">
-        <v>27.88406953491595</v>
+        <v>48.21834214454124</v>
       </c>
       <c r="L15" t="n">
-        <v>21.9256353158489</v>
+        <v>13.04491685662995</v>
       </c>
       <c r="M15" t="n">
-        <v>99.99750210277229</v>
+        <v>99.99698810095164</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>74.62133097136784</v>
+        <v>49.78281952961225</v>
       </c>
       <c r="C16" t="n">
-        <v>50.19994394493309</v>
+        <v>36.74969417585241</v>
       </c>
       <c r="D16" t="n">
-        <v>0.666246743447141</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.22597727780754</v>
+        <v>0.761618754631749</v>
       </c>
       <c r="F16" t="n">
-        <v>6.735323560364336</v>
+        <v>13.82614354519111</v>
       </c>
       <c r="G16" t="n">
-        <v>41.57379679110159</v>
+        <v>22.16378489798052</v>
       </c>
       <c r="H16" t="n">
-        <v>4.410033283571886</v>
+        <v>6.768042294848797</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06245133593109022</v>
+        <v>0.07530565309831654</v>
       </c>
       <c r="J16" t="n">
-        <v>19.94750197914425</v>
+        <v>6.187924383861757</v>
       </c>
       <c r="K16" t="n">
-        <v>25.37866902863216</v>
+        <v>50.21718047038775</v>
       </c>
       <c r="L16" t="n">
-        <v>24.41930537330892</v>
+        <v>13.03061529188753</v>
       </c>
       <c r="M16" t="n">
-        <v>99.99791834687417</v>
+        <v>99.9974899381277</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>73.85293667820793</v>
+        <v>47.79743114731394</v>
       </c>
       <c r="C17" t="n">
-        <v>49.07009127502265</v>
+        <v>34.77661793399093</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6487891947714997</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.202527206742378</v>
+        <v>0.748389227759735</v>
       </c>
       <c r="F17" t="n">
-        <v>6.73548177262213</v>
+        <v>13.82674866391435</v>
       </c>
       <c r="G17" t="n">
-        <v>40.48444575374157</v>
+        <v>20.20300208514636</v>
       </c>
       <c r="H17" t="n">
-        <v>4.410136874931156</v>
+        <v>6.768338506811223</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05204400242366949</v>
+        <v>0.06275745745484816</v>
       </c>
       <c r="J17" t="n">
-        <v>20.31951187297552</v>
+        <v>6.188195206227403</v>
       </c>
       <c r="K17" t="n">
-        <v>26.14706332179206</v>
+        <v>52.20256885268608</v>
       </c>
       <c r="L17" t="n">
-        <v>24.78111064385388</v>
+        <v>13.01872138962582</v>
       </c>
       <c r="M17" t="n">
-        <v>99.99826524066859</v>
+        <v>99.99790817630283</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>75.73606621963191</v>
+        <v>46.12914727348733</v>
       </c>
       <c r="C18" t="n">
-        <v>49.07847226154754</v>
+        <v>33.11857241652925</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6488015792391235</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.209778632933669</v>
+        <v>0.872493329588806</v>
       </c>
       <c r="F18" t="n">
-        <v>6.735610343437761</v>
+        <v>13.82727120915233</v>
       </c>
       <c r="G18" t="n">
-        <v>40.48521854452131</v>
+        <v>18.42005950626025</v>
       </c>
       <c r="H18" t="n">
-        <v>4.410221058203296</v>
+        <v>6.768594298186456</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04337082989169006</v>
+        <v>0.05229985767187584</v>
       </c>
       <c r="J18" t="n">
-        <v>22.20306523140505</v>
+        <v>6.188429072627616</v>
       </c>
       <c r="K18" t="n">
-        <v>24.26393378036808</v>
+        <v>53.87085272651267</v>
       </c>
       <c r="L18" t="n">
-        <v>26.65614829135038</v>
+        <v>13.008831594251</v>
       </c>
       <c r="M18" t="n">
-        <v>99.99855433326601</v>
+        <v>99.99825673729292</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.0750538844313</v>
+        <v>44.81605971905721</v>
       </c>
       <c r="C19" t="n">
-        <v>48.68775628394645</v>
+        <v>31.81400035969237</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6427184645916171</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.204459661531533</v>
+        <v>1.134234800126805</v>
       </c>
       <c r="F19" t="n">
-        <v>6.735717012087052</v>
+        <v>13.82771945357624</v>
       </c>
       <c r="G19" t="n">
-        <v>40.1056321905169</v>
+        <v>16.85307743372187</v>
       </c>
       <c r="H19" t="n">
-        <v>4.410290900771285</v>
+        <v>6.768813718533824</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03614293061236892</v>
+        <v>0.04358462758183173</v>
       </c>
       <c r="J19" t="n">
-        <v>22.94009272432054</v>
+        <v>6.188629685516638</v>
       </c>
       <c r="K19" t="n">
-        <v>23.9249461155687</v>
+        <v>55.18394028094279</v>
       </c>
       <c r="L19" t="n">
-        <v>27.38609285521006</v>
+        <v>13.00060658554064</v>
       </c>
       <c r="M19" t="n">
-        <v>99.99879525472521</v>
+        <v>99.99854722617579</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.46524629762172</v>
+        <v>43.74232225492246</v>
       </c>
       <c r="C20" t="n">
-        <v>48.69354718020104</v>
+        <v>30.74734764378766</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6427266883407698</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.209494988608974</v>
+        <v>1.456379068349395</v>
       </c>
       <c r="F20" t="n">
-        <v>6.735803197330084</v>
+        <v>13.82810218276335</v>
       </c>
       <c r="G20" t="n">
-        <v>40.10614535246403</v>
+        <v>15.46371743014417</v>
       </c>
       <c r="H20" t="n">
-        <v>4.410347331585175</v>
+        <v>6.769001068485554</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03011949422543619</v>
+        <v>0.0363215282789203</v>
       </c>
       <c r="J20" t="n">
-        <v>25.33060924506724</v>
+        <v>6.188800976901077</v>
       </c>
       <c r="K20" t="n">
-        <v>21.5347537023783</v>
+        <v>56.25767774507753</v>
       </c>
       <c r="L20" t="n">
-        <v>29.77069514712587</v>
+        <v>12.99376392703532</v>
       </c>
       <c r="M20" t="n">
-        <v>99.99899602970521</v>
+        <v>99.99878931590051</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,81 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.2949589464576</v>
+        <v>42.79640834188066</v>
       </c>
       <c r="C21" t="n">
-        <v>48.69835348983072</v>
+        <v>29.80732942492051</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6427333854557103</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.213690898039768</v>
+        <v>1.707001462983365</v>
       </c>
       <c r="F21" t="n">
-        <v>6.735873383381243</v>
+        <v>13.82842818990131</v>
       </c>
       <c r="G21" t="n">
-        <v>40.10656325243632</v>
+        <v>14.27260250058295</v>
       </c>
       <c r="H21" t="n">
-        <v>4.41039328673772</v>
+        <v>6.769160652399245</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02509984005501106</v>
+        <v>0.03026865382020122</v>
       </c>
       <c r="J21" t="n">
-        <v>27.16060490035183</v>
+        <v>6.188946882193594</v>
       </c>
       <c r="K21" t="n">
-        <v>19.70504105354238</v>
+        <v>57.20359165811934</v>
       </c>
       <c r="L21" t="n">
-        <v>31.59576880400952</v>
+        <v>12.98806998561906</v>
       </c>
       <c r="M21" t="n">
-        <v>99.99916334738263</v>
+        <v>99.99899106865891</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>41.8494145063642</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28.86524229764841</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.831929851389499</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13.82870602222008</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13.20518636682692</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.769296654233606</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.02522438496622916</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.189071226727867</v>
+      </c>
+      <c r="K22" t="n">
+        <v>58.1505854936358</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12.98333141277634</v>
+      </c>
+      <c r="M22" t="n">
+        <v>99.99915920406056</v>
       </c>
     </row>
   </sheetData>
